--- a/database/data/raw/metadata/bioprint_metadata_template_v2.xlsx
+++ b/database/data/raw/metadata/bioprint_metadata_template_v2.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="15300"/>
+    <workbookView windowWidth="25600" windowHeight="11430"/>
   </bookViews>
   <sheets>
     <sheet name="metadata" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="18">
   <si>
     <t>image_path</t>
   </si>
@@ -66,6 +66,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>运动速度为</t>
     </r>
     <r>
@@ -98,6 +104,18 @@
   </si>
   <si>
     <t>坍塌</t>
+  </si>
+  <si>
+    <t>成型效果不理想</t>
+  </si>
+  <si>
+    <t>作为上限</t>
+  </si>
+  <si>
+    <t>修改了预挤出</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -766,7 +784,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -788,9 +806,6 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="50">
@@ -1282,7 +1297,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:I201"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
     <col min="2" max="7" width="20" customWidth="1"/>
@@ -1290,7 +1305,7 @@
     <col min="9" max="9" width="27.6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.4" spans="1:9">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1319,7 +1334,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" ht="14.4" spans="1:9">
+    <row r="2" spans="1:9">
       <c r="A2" s="3"/>
       <c r="B2" s="4">
         <v>1</v>
@@ -1344,7 +1359,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" ht="14.4" spans="1:9">
+    <row r="3" spans="1:9">
       <c r="A3" s="3"/>
       <c r="B3" s="7">
         <v>2</v>
@@ -1365,7 +1380,7 @@
       <c r="H3" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="I3" s="9"/>
+      <c r="I3" s="6"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="3"/>
@@ -1390,7 +1405,7 @@
       </c>
       <c r="I4" s="3"/>
     </row>
-    <row r="5" ht="14.4" spans="1:9">
+    <row r="5" spans="1:9">
       <c r="A5" s="3"/>
       <c r="B5" s="8">
         <v>4</v>
@@ -1411,7 +1426,7 @@
       <c r="H5" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="10" t="s">
+      <c r="I5" s="9" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1461,7 +1476,7 @@
       </c>
       <c r="I7" s="3"/>
     </row>
-    <row r="8" ht="14.4" spans="1:9">
+    <row r="8" spans="1:9">
       <c r="A8" s="3"/>
       <c r="B8" s="8">
         <v>7</v>
@@ -1482,11 +1497,11 @@
       <c r="H8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="I8" s="10" t="s">
+      <c r="I8" s="9" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="9" ht="14.4" spans="1:9">
+    <row r="9" spans="1:9">
       <c r="A9" s="3"/>
       <c r="B9" s="8">
         <v>8</v>
@@ -1507,160 +1522,310 @@
       <c r="H9" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="I9" s="10" t="s">
+      <c r="I9" s="9" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="3"/>
-      <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
+      <c r="B10" s="8">
+        <v>9</v>
+      </c>
+      <c r="C10" s="8">
+        <v>5</v>
+      </c>
+      <c r="D10" s="8">
+        <v>0.05</v>
+      </c>
+      <c r="E10" s="8">
+        <v>3</v>
+      </c>
+      <c r="F10" s="8">
+        <v>2</v>
+      </c>
       <c r="G10" s="8"/>
-      <c r="H10" s="3"/>
+      <c r="H10" s="3" t="s">
+        <v>9</v>
+      </c>
       <c r="I10" s="3"/>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="3"/>
-      <c r="B11" s="8"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
+      <c r="B11" s="8">
+        <v>10</v>
+      </c>
+      <c r="C11" s="8">
+        <v>5</v>
+      </c>
+      <c r="D11" s="8">
+        <v>0.03</v>
+      </c>
+      <c r="E11" s="8">
+        <v>3</v>
+      </c>
+      <c r="F11" s="8">
+        <v>2</v>
+      </c>
       <c r="G11" s="8"/>
-      <c r="H11" s="3"/>
+      <c r="H11" s="3" t="s">
+        <v>9</v>
+      </c>
       <c r="I11" s="3"/>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="3"/>
-      <c r="B12" s="8"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
+      <c r="B12" s="8">
+        <v>11</v>
+      </c>
+      <c r="C12" s="8">
+        <v>5</v>
+      </c>
+      <c r="D12" s="8">
+        <v>0.1</v>
+      </c>
+      <c r="E12" s="8">
+        <v>3</v>
+      </c>
+      <c r="F12" s="8">
+        <v>2</v>
+      </c>
       <c r="G12" s="8"/>
       <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
+      <c r="I12" s="9" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="3"/>
-      <c r="B13" s="8"/>
-      <c r="C13" s="8"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
+      <c r="B13" s="8">
+        <v>12</v>
+      </c>
+      <c r="C13" s="8">
+        <v>5</v>
+      </c>
+      <c r="D13" s="8">
+        <v>0.1</v>
+      </c>
+      <c r="E13" s="8">
+        <v>3</v>
+      </c>
+      <c r="F13" s="8">
+        <v>2</v>
+      </c>
       <c r="G13" s="8"/>
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="3"/>
-      <c r="B14" s="8"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8"/>
+      <c r="B14" s="8">
+        <v>13</v>
+      </c>
+      <c r="C14" s="8">
+        <v>5</v>
+      </c>
+      <c r="D14" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="E14" s="8">
+        <v>3</v>
+      </c>
+      <c r="F14" s="8">
+        <v>2</v>
+      </c>
       <c r="G14" s="8"/>
       <c r="H14" s="3"/>
       <c r="I14" s="3"/>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="3"/>
-      <c r="B15" s="8"/>
-      <c r="C15" s="8"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
+      <c r="B15" s="8">
+        <v>14</v>
+      </c>
+      <c r="C15" s="8">
+        <v>5</v>
+      </c>
+      <c r="D15" s="8">
+        <v>0.05</v>
+      </c>
+      <c r="E15" s="8">
+        <v>3</v>
+      </c>
+      <c r="F15" s="8">
+        <v>2</v>
+      </c>
       <c r="G15" s="8"/>
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="3"/>
-      <c r="B16" s="8"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="8"/>
+      <c r="B16" s="8">
+        <v>15</v>
+      </c>
+      <c r="C16" s="8">
+        <v>5</v>
+      </c>
+      <c r="D16" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="E16" s="8">
+        <v>3</v>
+      </c>
+      <c r="F16" s="8">
+        <v>3</v>
+      </c>
       <c r="G16" s="8"/>
       <c r="H16" s="3"/>
       <c r="I16" s="3"/>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="3"/>
-      <c r="B17" s="8"/>
-      <c r="C17" s="8"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="8"/>
+      <c r="B17" s="8">
+        <v>16</v>
+      </c>
+      <c r="C17" s="8">
+        <v>5</v>
+      </c>
+      <c r="D17" s="8">
+        <v>1</v>
+      </c>
+      <c r="E17" s="8">
+        <v>3</v>
+      </c>
+      <c r="F17" s="8">
+        <v>3</v>
+      </c>
       <c r="G17" s="8"/>
       <c r="H17" s="3"/>
       <c r="I17" s="3"/>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="3"/>
-      <c r="B18" s="8"/>
-      <c r="C18" s="8"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="8"/>
+      <c r="B18" s="8">
+        <v>17</v>
+      </c>
+      <c r="C18" s="8">
+        <v>5</v>
+      </c>
+      <c r="D18" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="E18" s="8">
+        <v>3</v>
+      </c>
+      <c r="F18" s="8">
+        <v>3</v>
+      </c>
       <c r="G18" s="8"/>
       <c r="H18" s="3"/>
       <c r="I18" s="3"/>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="3"/>
-      <c r="B19" s="8"/>
-      <c r="C19" s="8"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="8"/>
+      <c r="B19" s="8">
+        <v>18</v>
+      </c>
+      <c r="C19" s="8">
+        <v>5</v>
+      </c>
+      <c r="D19" s="8">
+        <v>2</v>
+      </c>
+      <c r="E19" s="8">
+        <v>3</v>
+      </c>
+      <c r="F19" s="8">
+        <v>3</v>
+      </c>
       <c r="G19" s="8"/>
       <c r="H19" s="3"/>
-      <c r="I19" s="3"/>
+      <c r="I19" s="9" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="3"/>
-      <c r="B20" s="8"/>
-      <c r="C20" s="8"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="8"/>
+      <c r="B20" s="8">
+        <v>19</v>
+      </c>
+      <c r="C20" s="8">
+        <v>10</v>
+      </c>
+      <c r="D20" s="8">
+        <v>1</v>
+      </c>
+      <c r="E20" s="8">
+        <v>3</v>
+      </c>
+      <c r="F20" s="8">
+        <v>3</v>
+      </c>
       <c r="G20" s="8"/>
       <c r="H20" s="3"/>
       <c r="I20" s="3"/>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="3"/>
-      <c r="B21" s="8"/>
-      <c r="C21" s="8"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="8"/>
+      <c r="B21" s="8">
+        <v>20</v>
+      </c>
+      <c r="C21" s="8">
+        <v>10</v>
+      </c>
+      <c r="D21" s="8">
+        <v>2</v>
+      </c>
+      <c r="E21" s="8">
+        <v>3</v>
+      </c>
+      <c r="F21" s="8">
+        <v>3</v>
+      </c>
       <c r="G21" s="8"/>
       <c r="H21" s="3"/>
       <c r="I21" s="3"/>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="3"/>
-      <c r="B22" s="8"/>
-      <c r="C22" s="8"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="8"/>
+      <c r="B22" s="8">
+        <v>21</v>
+      </c>
+      <c r="C22" s="8">
+        <v>10</v>
+      </c>
+      <c r="D22" s="8">
+        <v>2</v>
+      </c>
+      <c r="E22" s="8">
+        <v>3</v>
+      </c>
+      <c r="F22" s="8">
+        <v>3</v>
+      </c>
       <c r="G22" s="8"/>
       <c r="H22" s="3"/>
-      <c r="I22" s="3"/>
+      <c r="I22" s="9" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" s="3"/>
-      <c r="B23" s="8"/>
-      <c r="C23" s="8"/>
-      <c r="D23" s="8"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="8"/>
+      <c r="B23" s="8">
+        <v>22</v>
+      </c>
+      <c r="C23" s="8">
+        <v>10</v>
+      </c>
+      <c r="D23" s="8">
+        <v>2.5</v>
+      </c>
+      <c r="E23" s="8">
+        <v>3</v>
+      </c>
+      <c r="F23" s="8">
+        <v>3</v>
+      </c>
       <c r="G23" s="8"/>
       <c r="H23" s="3"/>
       <c r="I23" s="3"/>
@@ -1715,7 +1880,9 @@
       <c r="C28" s="8"/>
       <c r="D28" s="8"/>
       <c r="E28" s="8"/>
-      <c r="F28" s="8"/>
+      <c r="F28" s="8" t="s">
+        <v>17</v>
+      </c>
       <c r="G28" s="8"/>
       <c r="H28" s="3"/>
       <c r="I28" s="3"/>

--- a/database/data/raw/metadata/bioprint_metadata_template_v2.xlsx
+++ b/database/data/raw/metadata/bioprint_metadata_template_v2.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="11430"/>
+    <workbookView windowWidth="29868" windowHeight="15300"/>
   </bookViews>
   <sheets>
     <sheet name="metadata" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="22">
   <si>
     <t>image_path</t>
   </si>
@@ -115,7 +115,77 @@
     <t>修改了预挤出</t>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
+    <t>添加了颜料</t>
+  </si>
+  <si>
+    <t>CH 7.19</t>
+  </si>
+  <si>
+    <r>
+      <t>补速度</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>15</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、高度</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>时挤出</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>修改高度为</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>4.5</t>
+    </r>
+  </si>
+  <si>
+    <t>挤出速度再小无法成型，高度是否还能增大，放大挤出速度？</t>
   </si>
 </sst>
 </file>
@@ -1297,15 +1367,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:I201"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
     <col min="2" max="7" width="20" customWidth="1"/>
     <col min="8" max="8" width="18" customWidth="1"/>
-    <col min="9" max="9" width="27.6" customWidth="1"/>
+    <col min="9" max="9" width="51.7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" ht="14.4" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1334,7 +1404,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" ht="14.4" spans="1:9">
       <c r="A2" s="3"/>
       <c r="B2" s="4">
         <v>1</v>
@@ -1359,7 +1429,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" ht="14.4" spans="1:9">
       <c r="A3" s="3"/>
       <c r="B3" s="7">
         <v>2</v>
@@ -1405,7 +1475,7 @@
       </c>
       <c r="I4" s="3"/>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" ht="14.4" spans="1:9">
       <c r="A5" s="3"/>
       <c r="B5" s="8">
         <v>4</v>
@@ -1476,7 +1546,7 @@
       </c>
       <c r="I7" s="3"/>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" ht="14.4" spans="1:9">
       <c r="A8" s="3"/>
       <c r="B8" s="8">
         <v>7</v>
@@ -1501,7 +1571,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" ht="14.4" spans="1:9">
       <c r="A9" s="3"/>
       <c r="B9" s="8">
         <v>8</v>
@@ -1572,7 +1642,7 @@
       </c>
       <c r="I11" s="3"/>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" ht="14.4" spans="1:9">
       <c r="A12" s="3"/>
       <c r="B12" s="8">
         <v>11</v>
@@ -1721,7 +1791,7 @@
       <c r="H18" s="3"/>
       <c r="I18" s="3"/>
     </row>
-    <row r="19" spans="1:9">
+    <row r="19" ht="14.4" spans="1:9">
       <c r="A19" s="3"/>
       <c r="B19" s="8">
         <v>18</v>
@@ -1786,7 +1856,7 @@
       <c r="H21" s="3"/>
       <c r="I21" s="3"/>
     </row>
-    <row r="22" spans="1:9">
+    <row r="22" ht="14.4" spans="1:9">
       <c r="A22" s="3"/>
       <c r="B22" s="8">
         <v>21</v>
@@ -1809,7 +1879,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="23" spans="1:9">
+    <row r="23" ht="14.4" spans="1:9">
       <c r="A23" s="3"/>
       <c r="B23" s="8">
         <v>22</v>
@@ -1828,60 +1898,110 @@
       </c>
       <c r="G23" s="8"/>
       <c r="H23" s="3"/>
-      <c r="I23" s="3"/>
-    </row>
-    <row r="24" spans="1:9">
+      <c r="I23" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="24" ht="14.4" spans="1:9">
       <c r="A24" s="3"/>
-      <c r="B24" s="8"/>
-      <c r="C24" s="8"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="8"/>
+      <c r="B24" s="8">
+        <v>23</v>
+      </c>
+      <c r="C24" s="8">
+        <v>10</v>
+      </c>
+      <c r="D24" s="8">
+        <v>1</v>
+      </c>
+      <c r="E24" s="8">
+        <v>3</v>
+      </c>
+      <c r="F24" s="8">
+        <v>2.5</v>
+      </c>
       <c r="G24" s="8"/>
       <c r="H24" s="3"/>
-      <c r="I24" s="3"/>
+      <c r="I24" s="9"/>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" s="3"/>
-      <c r="B25" s="8"/>
-      <c r="C25" s="8"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="8"/>
+      <c r="B25" s="8">
+        <v>24</v>
+      </c>
+      <c r="C25" s="8">
+        <v>10</v>
+      </c>
+      <c r="D25" s="8">
+        <v>2</v>
+      </c>
+      <c r="E25" s="8">
+        <v>3</v>
+      </c>
+      <c r="F25" s="8">
+        <v>2.5</v>
+      </c>
       <c r="G25" s="8"/>
       <c r="H25" s="3"/>
       <c r="I25" s="3"/>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" s="3"/>
-      <c r="B26" s="8"/>
-      <c r="C26" s="8"/>
-      <c r="D26" s="8"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="8"/>
+      <c r="B26" s="8">
+        <v>25</v>
+      </c>
+      <c r="C26" s="8">
+        <v>10</v>
+      </c>
+      <c r="D26" s="8">
+        <v>3</v>
+      </c>
+      <c r="E26" s="8">
+        <v>3</v>
+      </c>
+      <c r="F26" s="8">
+        <v>2.5</v>
+      </c>
       <c r="G26" s="8"/>
       <c r="H26" s="3"/>
       <c r="I26" s="3"/>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="3"/>
-      <c r="B27" s="8"/>
-      <c r="C27" s="8"/>
-      <c r="D27" s="8"/>
-      <c r="E27" s="8"/>
-      <c r="F27" s="8"/>
+      <c r="B27" s="8">
+        <v>26</v>
+      </c>
+      <c r="C27" s="8">
+        <v>15</v>
+      </c>
+      <c r="D27" s="8">
+        <v>1</v>
+      </c>
+      <c r="E27" s="8">
+        <v>3</v>
+      </c>
+      <c r="F27" s="8">
+        <v>2.5</v>
+      </c>
       <c r="G27" s="8"/>
       <c r="H27" s="3"/>
       <c r="I27" s="3"/>
     </row>
     <row r="28" spans="1:9">
       <c r="A28" s="3"/>
-      <c r="B28" s="8"/>
-      <c r="C28" s="8"/>
-      <c r="D28" s="8"/>
-      <c r="E28" s="8"/>
-      <c r="F28" s="8" t="s">
-        <v>17</v>
+      <c r="B28" s="8">
+        <v>27</v>
+      </c>
+      <c r="C28" s="8">
+        <v>15</v>
+      </c>
+      <c r="D28" s="8">
+        <v>1</v>
+      </c>
+      <c r="E28" s="8">
+        <v>3</v>
+      </c>
+      <c r="F28" s="8">
+        <v>2.5</v>
       </c>
       <c r="G28" s="8"/>
       <c r="H28" s="3"/>
@@ -1889,498 +2009,956 @@
     </row>
     <row r="29" spans="1:9">
       <c r="A29" s="3"/>
-      <c r="B29" s="8"/>
-      <c r="C29" s="8"/>
-      <c r="D29" s="8"/>
-      <c r="E29" s="8"/>
-      <c r="F29" s="8"/>
+      <c r="B29" s="8">
+        <v>28</v>
+      </c>
+      <c r="C29" s="8">
+        <v>15</v>
+      </c>
+      <c r="D29" s="8">
+        <v>1</v>
+      </c>
+      <c r="E29" s="8">
+        <v>3</v>
+      </c>
+      <c r="F29" s="8">
+        <v>2.5</v>
+      </c>
       <c r="G29" s="8"/>
       <c r="H29" s="3"/>
       <c r="I29" s="3"/>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" s="3"/>
-      <c r="B30" s="8"/>
-      <c r="C30" s="8"/>
-      <c r="D30" s="8"/>
-      <c r="E30" s="8"/>
-      <c r="F30" s="8"/>
+      <c r="B30" s="8">
+        <v>29</v>
+      </c>
+      <c r="C30" s="8">
+        <v>15</v>
+      </c>
+      <c r="D30" s="8">
+        <v>1</v>
+      </c>
+      <c r="E30" s="8">
+        <v>3</v>
+      </c>
+      <c r="F30" s="8">
+        <v>2.5</v>
+      </c>
       <c r="G30" s="8"/>
       <c r="H30" s="3"/>
       <c r="I30" s="3"/>
     </row>
     <row r="31" spans="1:9">
       <c r="A31" s="3"/>
-      <c r="B31" s="8"/>
-      <c r="C31" s="8"/>
-      <c r="D31" s="8"/>
-      <c r="E31" s="8"/>
-      <c r="F31" s="8"/>
+      <c r="B31" s="8">
+        <v>30</v>
+      </c>
+      <c r="C31" s="8">
+        <v>15</v>
+      </c>
+      <c r="D31" s="8">
+        <v>1</v>
+      </c>
+      <c r="E31" s="8">
+        <v>3</v>
+      </c>
+      <c r="F31" s="8">
+        <v>2.5</v>
+      </c>
       <c r="G31" s="8"/>
       <c r="H31" s="3"/>
       <c r="I31" s="3"/>
     </row>
     <row r="32" spans="1:9">
       <c r="A32" s="3"/>
-      <c r="B32" s="8"/>
-      <c r="C32" s="8"/>
-      <c r="D32" s="8"/>
-      <c r="E32" s="8"/>
-      <c r="F32" s="8"/>
+      <c r="B32" s="8">
+        <v>31</v>
+      </c>
+      <c r="C32" s="8">
+        <v>15</v>
+      </c>
+      <c r="D32" s="8">
+        <v>2</v>
+      </c>
+      <c r="E32" s="8">
+        <v>3</v>
+      </c>
+      <c r="F32" s="8">
+        <v>4</v>
+      </c>
       <c r="G32" s="8"/>
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
     </row>
     <row r="33" spans="1:9">
       <c r="A33" s="3"/>
-      <c r="B33" s="8"/>
-      <c r="C33" s="8"/>
-      <c r="D33" s="8"/>
-      <c r="E33" s="8"/>
-      <c r="F33" s="8"/>
+      <c r="B33" s="8">
+        <v>32</v>
+      </c>
+      <c r="C33" s="8">
+        <v>10</v>
+      </c>
+      <c r="D33" s="8">
+        <v>1</v>
+      </c>
+      <c r="E33" s="8">
+        <v>3</v>
+      </c>
+      <c r="F33" s="8">
+        <v>3</v>
+      </c>
       <c r="G33" s="8"/>
       <c r="H33" s="3"/>
       <c r="I33" s="3"/>
     </row>
     <row r="34" spans="1:9">
       <c r="A34" s="3"/>
-      <c r="B34" s="8"/>
-      <c r="C34" s="8"/>
-      <c r="D34" s="8"/>
-      <c r="E34" s="8"/>
-      <c r="F34" s="8"/>
+      <c r="B34" s="8">
+        <v>33</v>
+      </c>
+      <c r="C34" s="8">
+        <v>15</v>
+      </c>
+      <c r="D34" s="8">
+        <v>4</v>
+      </c>
+      <c r="E34" s="8">
+        <v>3</v>
+      </c>
+      <c r="F34" s="8">
+        <v>3</v>
+      </c>
       <c r="G34" s="8"/>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
     </row>
     <row r="35" spans="1:9">
       <c r="A35" s="3"/>
-      <c r="B35" s="8"/>
-      <c r="C35" s="8"/>
-      <c r="D35" s="8"/>
-      <c r="E35" s="8"/>
-      <c r="F35" s="8"/>
+      <c r="B35" s="8">
+        <v>34</v>
+      </c>
+      <c r="C35" s="8">
+        <v>15</v>
+      </c>
+      <c r="D35" s="8">
+        <v>5</v>
+      </c>
+      <c r="E35" s="8">
+        <v>3</v>
+      </c>
+      <c r="F35" s="8">
+        <v>3</v>
+      </c>
       <c r="G35" s="8"/>
       <c r="H35" s="3"/>
       <c r="I35" s="3"/>
     </row>
     <row r="36" spans="1:9">
       <c r="A36" s="3"/>
-      <c r="B36" s="8"/>
-      <c r="C36" s="8"/>
-      <c r="D36" s="8"/>
-      <c r="E36" s="8"/>
-      <c r="F36" s="8"/>
+      <c r="B36" s="8">
+        <v>35</v>
+      </c>
+      <c r="C36" s="8">
+        <v>15</v>
+      </c>
+      <c r="D36" s="8">
+        <v>6</v>
+      </c>
+      <c r="E36" s="8">
+        <v>3</v>
+      </c>
+      <c r="F36" s="8">
+        <v>3</v>
+      </c>
       <c r="G36" s="8"/>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
     </row>
     <row r="37" spans="1:9">
       <c r="A37" s="3"/>
-      <c r="B37" s="8"/>
-      <c r="C37" s="8"/>
-      <c r="D37" s="8"/>
-      <c r="E37" s="8"/>
-      <c r="F37" s="8"/>
+      <c r="B37" s="8">
+        <v>36</v>
+      </c>
+      <c r="C37" s="8">
+        <v>15</v>
+      </c>
+      <c r="D37" s="8">
+        <v>2</v>
+      </c>
+      <c r="E37" s="8">
+        <v>3</v>
+      </c>
+      <c r="F37" s="8">
+        <v>3</v>
+      </c>
       <c r="G37" s="8"/>
       <c r="H37" s="3"/>
       <c r="I37" s="3"/>
     </row>
     <row r="38" spans="1:9">
       <c r="A38" s="3"/>
-      <c r="B38" s="8"/>
-      <c r="C38" s="8"/>
-      <c r="D38" s="8"/>
-      <c r="E38" s="8"/>
-      <c r="F38" s="8"/>
+      <c r="B38" s="8">
+        <v>37</v>
+      </c>
+      <c r="C38" s="8">
+        <v>15</v>
+      </c>
+      <c r="D38" s="8">
+        <v>3</v>
+      </c>
+      <c r="E38" s="8">
+        <v>3</v>
+      </c>
+      <c r="F38" s="8">
+        <v>4</v>
+      </c>
       <c r="G38" s="8"/>
       <c r="H38" s="3"/>
       <c r="I38" s="3"/>
     </row>
     <row r="39" spans="1:9">
       <c r="A39" s="3"/>
-      <c r="B39" s="8"/>
-      <c r="C39" s="8"/>
-      <c r="D39" s="8"/>
-      <c r="E39" s="8"/>
-      <c r="F39" s="8"/>
+      <c r="B39" s="8">
+        <v>38</v>
+      </c>
+      <c r="C39" s="8">
+        <v>15</v>
+      </c>
+      <c r="D39" s="8">
+        <v>4</v>
+      </c>
+      <c r="E39" s="8">
+        <v>3</v>
+      </c>
+      <c r="F39" s="8">
+        <v>4</v>
+      </c>
       <c r="G39" s="8"/>
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
     </row>
     <row r="40" spans="1:9">
       <c r="A40" s="3"/>
-      <c r="B40" s="8"/>
-      <c r="C40" s="8"/>
-      <c r="D40" s="8"/>
-      <c r="E40" s="8"/>
-      <c r="F40" s="8"/>
+      <c r="B40" s="8">
+        <v>39</v>
+      </c>
+      <c r="C40" s="8">
+        <v>15</v>
+      </c>
+      <c r="D40" s="8">
+        <v>5</v>
+      </c>
+      <c r="E40" s="8">
+        <v>3</v>
+      </c>
+      <c r="F40" s="8">
+        <v>4</v>
+      </c>
       <c r="G40" s="8"/>
       <c r="H40" s="3"/>
       <c r="I40" s="3"/>
     </row>
     <row r="41" spans="1:9">
       <c r="A41" s="3"/>
-      <c r="B41" s="8"/>
-      <c r="C41" s="8"/>
-      <c r="D41" s="8"/>
-      <c r="E41" s="8"/>
-      <c r="F41" s="8"/>
+      <c r="B41" s="8">
+        <v>40</v>
+      </c>
+      <c r="C41" s="8">
+        <v>15</v>
+      </c>
+      <c r="D41" s="8">
+        <v>6</v>
+      </c>
+      <c r="E41" s="8">
+        <v>3</v>
+      </c>
+      <c r="F41" s="8">
+        <v>4</v>
+      </c>
       <c r="G41" s="8"/>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
     </row>
     <row r="42" spans="1:9">
       <c r="A42" s="3"/>
-      <c r="B42" s="8"/>
-      <c r="C42" s="8"/>
-      <c r="D42" s="8"/>
-      <c r="E42" s="8"/>
-      <c r="F42" s="8"/>
+      <c r="B42" s="8">
+        <v>41</v>
+      </c>
+      <c r="C42" s="8">
+        <v>20</v>
+      </c>
+      <c r="D42" s="8">
+        <v>1</v>
+      </c>
+      <c r="E42" s="8">
+        <v>3</v>
+      </c>
+      <c r="F42" s="8">
+        <v>3</v>
+      </c>
       <c r="G42" s="8"/>
       <c r="H42" s="3"/>
       <c r="I42" s="3"/>
     </row>
     <row r="43" spans="1:9">
       <c r="A43" s="3"/>
-      <c r="B43" s="8"/>
-      <c r="C43" s="8"/>
-      <c r="D43" s="8"/>
-      <c r="E43" s="8"/>
-      <c r="F43" s="8"/>
+      <c r="B43" s="8">
+        <v>42</v>
+      </c>
+      <c r="C43" s="8">
+        <v>20</v>
+      </c>
+      <c r="D43" s="8">
+        <v>2</v>
+      </c>
+      <c r="E43" s="8">
+        <v>3</v>
+      </c>
+      <c r="F43" s="8">
+        <v>3</v>
+      </c>
       <c r="G43" s="8"/>
       <c r="H43" s="3"/>
       <c r="I43" s="3"/>
     </row>
     <row r="44" spans="1:9">
       <c r="A44" s="3"/>
-      <c r="B44" s="8"/>
-      <c r="C44" s="8"/>
-      <c r="D44" s="8"/>
-      <c r="E44" s="8"/>
-      <c r="F44" s="8"/>
+      <c r="B44" s="8">
+        <v>43</v>
+      </c>
+      <c r="C44" s="8">
+        <v>20</v>
+      </c>
+      <c r="D44" s="8">
+        <v>3</v>
+      </c>
+      <c r="E44" s="8">
+        <v>3</v>
+      </c>
+      <c r="F44" s="8">
+        <v>3</v>
+      </c>
       <c r="G44" s="8"/>
       <c r="H44" s="3"/>
       <c r="I44" s="3"/>
     </row>
     <row r="45" spans="1:9">
       <c r="A45" s="3"/>
-      <c r="B45" s="8"/>
-      <c r="C45" s="8"/>
-      <c r="D45" s="8"/>
-      <c r="E45" s="8"/>
-      <c r="F45" s="8"/>
+      <c r="B45" s="8">
+        <v>44</v>
+      </c>
+      <c r="C45" s="8">
+        <v>20</v>
+      </c>
+      <c r="D45" s="8">
+        <v>4</v>
+      </c>
+      <c r="E45" s="8">
+        <v>3</v>
+      </c>
+      <c r="F45" s="8">
+        <v>3</v>
+      </c>
       <c r="G45" s="8"/>
       <c r="H45" s="3"/>
       <c r="I45" s="3"/>
     </row>
     <row r="46" spans="1:9">
       <c r="A46" s="3"/>
-      <c r="B46" s="8"/>
-      <c r="C46" s="8"/>
-      <c r="D46" s="8"/>
-      <c r="E46" s="8"/>
-      <c r="F46" s="8"/>
+      <c r="B46" s="8">
+        <v>45</v>
+      </c>
+      <c r="C46" s="8">
+        <v>20</v>
+      </c>
+      <c r="D46" s="8">
+        <v>5</v>
+      </c>
+      <c r="E46" s="8">
+        <v>3</v>
+      </c>
+      <c r="F46" s="8">
+        <v>3</v>
+      </c>
       <c r="G46" s="8"/>
       <c r="H46" s="3"/>
       <c r="I46" s="3"/>
     </row>
     <row r="47" spans="1:9">
       <c r="A47" s="3"/>
-      <c r="B47" s="8"/>
-      <c r="C47" s="8"/>
-      <c r="D47" s="8"/>
-      <c r="E47" s="8"/>
-      <c r="F47" s="8"/>
+      <c r="B47" s="8">
+        <v>46</v>
+      </c>
+      <c r="C47" s="8">
+        <v>20</v>
+      </c>
+      <c r="D47" s="8">
+        <v>6</v>
+      </c>
+      <c r="E47" s="8">
+        <v>3</v>
+      </c>
+      <c r="F47" s="8">
+        <v>3</v>
+      </c>
       <c r="G47" s="8"/>
       <c r="H47" s="3"/>
       <c r="I47" s="3"/>
     </row>
     <row r="48" spans="1:9">
       <c r="A48" s="3"/>
-      <c r="B48" s="8"/>
-      <c r="C48" s="8"/>
-      <c r="D48" s="8"/>
-      <c r="E48" s="8"/>
-      <c r="F48" s="8"/>
+      <c r="B48" s="8">
+        <v>47</v>
+      </c>
+      <c r="C48" s="8">
+        <v>20</v>
+      </c>
+      <c r="D48" s="8">
+        <v>7</v>
+      </c>
+      <c r="E48" s="8">
+        <v>3</v>
+      </c>
+      <c r="F48" s="8">
+        <v>3</v>
+      </c>
       <c r="G48" s="8"/>
       <c r="H48" s="3"/>
       <c r="I48" s="3"/>
     </row>
     <row r="49" spans="1:9">
       <c r="A49" s="3"/>
-      <c r="B49" s="8"/>
-      <c r="C49" s="8"/>
-      <c r="D49" s="8"/>
-      <c r="E49" s="8"/>
-      <c r="F49" s="8"/>
+      <c r="B49" s="8">
+        <v>48</v>
+      </c>
+      <c r="C49" s="8">
+        <v>20</v>
+      </c>
+      <c r="D49" s="8">
+        <v>8</v>
+      </c>
+      <c r="E49" s="8">
+        <v>3</v>
+      </c>
+      <c r="F49" s="8">
+        <v>3</v>
+      </c>
       <c r="G49" s="8"/>
       <c r="H49" s="3"/>
       <c r="I49" s="3"/>
     </row>
     <row r="50" spans="1:9">
       <c r="A50" s="3"/>
-      <c r="B50" s="8"/>
-      <c r="C50" s="8"/>
-      <c r="D50" s="8"/>
-      <c r="E50" s="8"/>
-      <c r="F50" s="8"/>
+      <c r="B50" s="8">
+        <v>49</v>
+      </c>
+      <c r="C50" s="8">
+        <v>20</v>
+      </c>
+      <c r="D50" s="8">
+        <v>9</v>
+      </c>
+      <c r="E50" s="8">
+        <v>3</v>
+      </c>
+      <c r="F50" s="8">
+        <v>3</v>
+      </c>
       <c r="G50" s="8"/>
       <c r="H50" s="3"/>
       <c r="I50" s="3"/>
     </row>
     <row r="51" spans="1:9">
       <c r="A51" s="3"/>
-      <c r="B51" s="8"/>
-      <c r="C51" s="8"/>
-      <c r="D51" s="8"/>
-      <c r="E51" s="8"/>
-      <c r="F51" s="8"/>
+      <c r="B51" s="8">
+        <v>50</v>
+      </c>
+      <c r="C51" s="8">
+        <v>20</v>
+      </c>
+      <c r="D51" s="8">
+        <v>1</v>
+      </c>
+      <c r="E51" s="8">
+        <v>3</v>
+      </c>
+      <c r="F51" s="8">
+        <v>3.5</v>
+      </c>
       <c r="G51" s="8"/>
       <c r="H51" s="3"/>
       <c r="I51" s="3"/>
     </row>
     <row r="52" spans="1:9">
       <c r="A52" s="3"/>
-      <c r="B52" s="8"/>
-      <c r="C52" s="8"/>
-      <c r="D52" s="8"/>
-      <c r="E52" s="8"/>
-      <c r="F52" s="8"/>
+      <c r="B52" s="8">
+        <v>51</v>
+      </c>
+      <c r="C52" s="8">
+        <v>20</v>
+      </c>
+      <c r="D52" s="8">
+        <v>2</v>
+      </c>
+      <c r="E52" s="8">
+        <v>3</v>
+      </c>
+      <c r="F52" s="8">
+        <v>3.5</v>
+      </c>
       <c r="G52" s="8"/>
       <c r="H52" s="3"/>
       <c r="I52" s="3"/>
     </row>
     <row r="53" spans="1:9">
       <c r="A53" s="3"/>
-      <c r="B53" s="8"/>
-      <c r="C53" s="8"/>
-      <c r="D53" s="8"/>
-      <c r="E53" s="8"/>
-      <c r="F53" s="8"/>
+      <c r="B53" s="8">
+        <v>52</v>
+      </c>
+      <c r="C53" s="8">
+        <v>20</v>
+      </c>
+      <c r="D53" s="8">
+        <v>3</v>
+      </c>
+      <c r="E53" s="8">
+        <v>3</v>
+      </c>
+      <c r="F53" s="8">
+        <v>3.5</v>
+      </c>
       <c r="G53" s="8"/>
       <c r="H53" s="3"/>
       <c r="I53" s="3"/>
     </row>
     <row r="54" spans="1:9">
       <c r="A54" s="3"/>
-      <c r="B54" s="8"/>
-      <c r="C54" s="8"/>
-      <c r="D54" s="8"/>
-      <c r="E54" s="8"/>
-      <c r="F54" s="8"/>
+      <c r="B54" s="8">
+        <v>53</v>
+      </c>
+      <c r="C54" s="8">
+        <v>20</v>
+      </c>
+      <c r="D54" s="8">
+        <v>4</v>
+      </c>
+      <c r="E54" s="8">
+        <v>3</v>
+      </c>
+      <c r="F54" s="8">
+        <v>3.5</v>
+      </c>
       <c r="G54" s="8"/>
       <c r="H54" s="3"/>
       <c r="I54" s="3"/>
     </row>
     <row r="55" spans="1:9">
       <c r="A55" s="3"/>
-      <c r="B55" s="8"/>
-      <c r="C55" s="8"/>
-      <c r="D55" s="8"/>
-      <c r="E55" s="8"/>
-      <c r="F55" s="8"/>
+      <c r="B55" s="8">
+        <v>54</v>
+      </c>
+      <c r="C55" s="8">
+        <v>20</v>
+      </c>
+      <c r="D55" s="8">
+        <v>5</v>
+      </c>
+      <c r="E55" s="8">
+        <v>3</v>
+      </c>
+      <c r="F55" s="8">
+        <v>3.5</v>
+      </c>
       <c r="G55" s="8"/>
       <c r="H55" s="3"/>
-      <c r="I55" s="3"/>
-    </row>
-    <row r="56" spans="1:9">
+      <c r="I55" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="56" ht="14.4" spans="1:9">
       <c r="A56" s="3"/>
-      <c r="B56" s="8"/>
-      <c r="C56" s="8"/>
-      <c r="D56" s="8"/>
-      <c r="E56" s="8"/>
-      <c r="F56" s="8"/>
+      <c r="B56" s="8">
+        <v>55</v>
+      </c>
+      <c r="C56" s="8">
+        <v>15</v>
+      </c>
+      <c r="D56" s="8">
+        <v>1</v>
+      </c>
+      <c r="E56" s="8">
+        <v>3</v>
+      </c>
+      <c r="F56" s="8">
+        <v>4</v>
+      </c>
       <c r="G56" s="8"/>
       <c r="H56" s="3"/>
-      <c r="I56" s="3"/>
+      <c r="I56" s="9" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="57" spans="1:9">
       <c r="A57" s="3"/>
-      <c r="B57" s="8"/>
-      <c r="C57" s="8"/>
-      <c r="D57" s="8"/>
-      <c r="E57" s="8"/>
-      <c r="F57" s="8"/>
+      <c r="B57" s="8">
+        <v>56</v>
+      </c>
+      <c r="C57" s="8">
+        <v>15</v>
+      </c>
+      <c r="D57" s="8">
+        <v>7</v>
+      </c>
+      <c r="E57" s="8">
+        <v>3</v>
+      </c>
+      <c r="F57" s="8">
+        <v>4</v>
+      </c>
       <c r="G57" s="8"/>
       <c r="H57" s="3"/>
       <c r="I57" s="3"/>
     </row>
     <row r="58" spans="1:9">
       <c r="A58" s="3"/>
-      <c r="B58" s="8"/>
-      <c r="C58" s="8"/>
-      <c r="D58" s="8"/>
-      <c r="E58" s="8"/>
-      <c r="F58" s="8"/>
+      <c r="B58" s="8">
+        <v>57</v>
+      </c>
+      <c r="C58" s="8">
+        <v>15</v>
+      </c>
+      <c r="D58" s="8">
+        <v>8</v>
+      </c>
+      <c r="E58" s="8">
+        <v>3</v>
+      </c>
+      <c r="F58" s="8">
+        <v>4</v>
+      </c>
       <c r="G58" s="8"/>
       <c r="H58" s="3"/>
       <c r="I58" s="3"/>
     </row>
     <row r="59" spans="1:9">
       <c r="A59" s="3"/>
-      <c r="B59" s="8"/>
-      <c r="C59" s="8"/>
-      <c r="D59" s="8"/>
-      <c r="E59" s="8"/>
-      <c r="F59" s="8"/>
+      <c r="B59" s="8">
+        <v>58</v>
+      </c>
+      <c r="C59" s="8">
+        <v>15</v>
+      </c>
+      <c r="D59" s="8">
+        <v>1</v>
+      </c>
+      <c r="E59" s="8">
+        <v>3</v>
+      </c>
+      <c r="F59" s="8">
+        <v>3.5</v>
+      </c>
       <c r="G59" s="8"/>
       <c r="H59" s="3"/>
       <c r="I59" s="3"/>
     </row>
     <row r="60" spans="1:9">
       <c r="A60" s="3"/>
-      <c r="B60" s="8"/>
-      <c r="C60" s="8"/>
-      <c r="D60" s="8"/>
-      <c r="E60" s="8"/>
-      <c r="F60" s="8"/>
+      <c r="B60" s="8">
+        <v>59</v>
+      </c>
+      <c r="C60" s="8">
+        <v>15</v>
+      </c>
+      <c r="D60" s="8">
+        <v>2</v>
+      </c>
+      <c r="E60" s="8">
+        <v>3</v>
+      </c>
+      <c r="F60" s="8">
+        <v>3.5</v>
+      </c>
       <c r="G60" s="8"/>
       <c r="H60" s="3"/>
       <c r="I60" s="3"/>
     </row>
     <row r="61" spans="1:9">
       <c r="A61" s="3"/>
-      <c r="B61" s="8"/>
-      <c r="C61" s="8"/>
-      <c r="D61" s="8"/>
-      <c r="E61" s="8"/>
-      <c r="F61" s="8"/>
+      <c r="B61" s="8">
+        <v>60</v>
+      </c>
+      <c r="C61" s="8">
+        <v>15</v>
+      </c>
+      <c r="D61" s="8">
+        <v>3</v>
+      </c>
+      <c r="E61" s="8">
+        <v>3</v>
+      </c>
+      <c r="F61" s="8">
+        <v>3.5</v>
+      </c>
       <c r="G61" s="8"/>
       <c r="H61" s="3"/>
       <c r="I61" s="3"/>
     </row>
     <row r="62" spans="1:9">
       <c r="A62" s="3"/>
-      <c r="B62" s="8"/>
-      <c r="C62" s="8"/>
-      <c r="D62" s="8"/>
-      <c r="E62" s="8"/>
-      <c r="F62" s="8"/>
+      <c r="B62" s="8">
+        <v>61</v>
+      </c>
+      <c r="C62" s="8">
+        <v>15</v>
+      </c>
+      <c r="D62" s="8">
+        <v>4</v>
+      </c>
+      <c r="E62" s="8">
+        <v>3</v>
+      </c>
+      <c r="F62" s="8">
+        <v>3.5</v>
+      </c>
       <c r="G62" s="8"/>
       <c r="H62" s="3"/>
       <c r="I62" s="3"/>
     </row>
     <row r="63" spans="1:9">
       <c r="A63" s="3"/>
-      <c r="B63" s="8"/>
-      <c r="C63" s="8"/>
-      <c r="D63" s="8"/>
-      <c r="E63" s="8"/>
-      <c r="F63" s="8"/>
+      <c r="B63" s="8">
+        <v>62</v>
+      </c>
+      <c r="C63" s="8">
+        <v>15</v>
+      </c>
+      <c r="D63" s="8">
+        <v>5</v>
+      </c>
+      <c r="E63" s="8">
+        <v>3</v>
+      </c>
+      <c r="F63" s="8">
+        <v>3.5</v>
+      </c>
       <c r="G63" s="8"/>
       <c r="H63" s="3"/>
       <c r="I63" s="3"/>
     </row>
     <row r="64" spans="1:9">
       <c r="A64" s="3"/>
-      <c r="B64" s="8"/>
-      <c r="C64" s="8"/>
-      <c r="D64" s="8"/>
-      <c r="E64" s="8"/>
-      <c r="F64" s="8"/>
+      <c r="B64" s="8">
+        <v>63</v>
+      </c>
+      <c r="C64" s="8">
+        <v>15</v>
+      </c>
+      <c r="D64" s="8">
+        <v>6</v>
+      </c>
+      <c r="E64" s="8">
+        <v>3</v>
+      </c>
+      <c r="F64" s="8">
+        <v>3.5</v>
+      </c>
       <c r="G64" s="8"/>
       <c r="H64" s="3"/>
       <c r="I64" s="3"/>
     </row>
     <row r="65" spans="1:9">
       <c r="A65" s="3"/>
-      <c r="B65" s="8"/>
-      <c r="C65" s="8"/>
-      <c r="D65" s="8"/>
-      <c r="E65" s="8"/>
-      <c r="F65" s="8"/>
+      <c r="B65" s="8">
+        <v>64</v>
+      </c>
+      <c r="C65" s="8">
+        <v>15</v>
+      </c>
+      <c r="D65" s="8">
+        <v>7</v>
+      </c>
+      <c r="E65" s="8">
+        <v>3</v>
+      </c>
+      <c r="F65" s="8">
+        <v>3.5</v>
+      </c>
       <c r="G65" s="8"/>
       <c r="H65" s="3"/>
       <c r="I65" s="3"/>
     </row>
     <row r="66" spans="1:9">
       <c r="A66" s="3"/>
-      <c r="B66" s="8"/>
-      <c r="C66" s="8"/>
-      <c r="D66" s="8"/>
-      <c r="E66" s="8"/>
-      <c r="F66" s="8"/>
+      <c r="B66" s="8">
+        <v>65</v>
+      </c>
+      <c r="C66" s="8">
+        <v>15</v>
+      </c>
+      <c r="D66" s="8">
+        <v>8</v>
+      </c>
+      <c r="E66" s="8">
+        <v>3</v>
+      </c>
+      <c r="F66" s="8">
+        <v>3.5</v>
+      </c>
       <c r="G66" s="8"/>
       <c r="H66" s="3"/>
       <c r="I66" s="3"/>
     </row>
-    <row r="67" spans="1:9">
+    <row r="67" ht="14.4" spans="1:9">
       <c r="A67" s="3"/>
-      <c r="B67" s="8"/>
-      <c r="C67" s="8"/>
-      <c r="D67" s="8"/>
-      <c r="E67" s="8"/>
-      <c r="F67" s="8"/>
+      <c r="B67" s="8">
+        <v>66</v>
+      </c>
+      <c r="C67" s="8">
+        <v>15</v>
+      </c>
+      <c r="D67" s="8">
+        <v>8</v>
+      </c>
+      <c r="E67" s="8">
+        <v>3</v>
+      </c>
+      <c r="F67" s="8">
+        <v>4.5</v>
+      </c>
       <c r="G67" s="8"/>
       <c r="H67" s="3"/>
-      <c r="I67" s="3"/>
+      <c r="I67" s="9" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="68" spans="1:9">
       <c r="A68" s="3"/>
-      <c r="B68" s="8"/>
-      <c r="C68" s="8"/>
-      <c r="D68" s="8"/>
-      <c r="E68" s="8"/>
-      <c r="F68" s="8"/>
+      <c r="B68" s="8">
+        <v>67</v>
+      </c>
+      <c r="C68" s="8">
+        <v>15</v>
+      </c>
+      <c r="D68" s="8">
+        <v>7</v>
+      </c>
+      <c r="E68" s="8">
+        <v>3</v>
+      </c>
+      <c r="F68" s="8">
+        <v>4.5</v>
+      </c>
       <c r="G68" s="8"/>
       <c r="H68" s="3"/>
       <c r="I68" s="3"/>
     </row>
     <row r="69" spans="1:9">
       <c r="A69" s="3"/>
-      <c r="B69" s="8"/>
-      <c r="C69" s="8"/>
-      <c r="D69" s="8"/>
-      <c r="E69" s="8"/>
-      <c r="F69" s="8"/>
+      <c r="B69" s="8">
+        <v>68</v>
+      </c>
+      <c r="C69" s="8">
+        <v>15</v>
+      </c>
+      <c r="D69" s="8">
+        <v>6</v>
+      </c>
+      <c r="E69" s="8">
+        <v>3</v>
+      </c>
+      <c r="F69" s="8">
+        <v>4.5</v>
+      </c>
       <c r="G69" s="8"/>
       <c r="H69" s="3"/>
       <c r="I69" s="3"/>
     </row>
     <row r="70" spans="1:9">
       <c r="A70" s="3"/>
-      <c r="B70" s="8"/>
-      <c r="C70" s="8"/>
-      <c r="D70" s="8"/>
-      <c r="E70" s="8"/>
-      <c r="F70" s="8"/>
+      <c r="B70" s="8">
+        <v>69</v>
+      </c>
+      <c r="C70" s="8">
+        <v>15</v>
+      </c>
+      <c r="D70" s="8">
+        <v>5</v>
+      </c>
+      <c r="E70" s="8">
+        <v>3</v>
+      </c>
+      <c r="F70" s="8">
+        <v>4.5</v>
+      </c>
       <c r="G70" s="8"/>
       <c r="H70" s="3"/>
       <c r="I70" s="3"/>
     </row>
     <row r="71" spans="1:9">
       <c r="A71" s="3"/>
-      <c r="B71" s="8"/>
-      <c r="C71" s="8"/>
-      <c r="D71" s="8"/>
-      <c r="E71" s="8"/>
-      <c r="F71" s="8"/>
+      <c r="B71" s="8">
+        <v>70</v>
+      </c>
+      <c r="C71" s="8">
+        <v>15</v>
+      </c>
+      <c r="D71" s="8">
+        <v>5</v>
+      </c>
+      <c r="E71" s="8">
+        <v>3</v>
+      </c>
+      <c r="F71" s="8">
+        <v>4.5</v>
+      </c>
       <c r="G71" s="8"/>
       <c r="H71" s="3"/>
       <c r="I71" s="3"/>
     </row>
     <row r="72" spans="1:9">
       <c r="A72" s="3"/>
-      <c r="B72" s="8"/>
-      <c r="C72" s="8"/>
-      <c r="D72" s="8"/>
-      <c r="E72" s="8"/>
-      <c r="F72" s="8"/>
+      <c r="B72" s="8">
+        <v>71</v>
+      </c>
+      <c r="C72" s="8">
+        <v>15</v>
+      </c>
+      <c r="D72" s="8">
+        <v>4</v>
+      </c>
+      <c r="E72" s="8">
+        <v>3</v>
+      </c>
+      <c r="F72" s="8">
+        <v>4.5</v>
+      </c>
       <c r="G72" s="8"/>
       <c r="H72" s="3"/>
       <c r="I72" s="3"/>
     </row>
-    <row r="73" spans="1:9">
+    <row r="73" ht="14.4" spans="1:9">
       <c r="A73" s="3"/>
-      <c r="B73" s="8"/>
-      <c r="C73" s="8"/>
-      <c r="D73" s="8"/>
-      <c r="E73" s="8"/>
-      <c r="F73" s="8"/>
+      <c r="B73" s="8">
+        <v>72</v>
+      </c>
+      <c r="C73" s="8">
+        <v>15</v>
+      </c>
+      <c r="D73" s="8">
+        <v>3</v>
+      </c>
+      <c r="E73" s="8">
+        <v>3</v>
+      </c>
+      <c r="F73" s="8">
+        <v>4.5</v>
+      </c>
       <c r="G73" s="8"/>
       <c r="H73" s="3"/>
-      <c r="I73" s="3"/>
+      <c r="I73" s="9" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="74" spans="1:9">
       <c r="A74" s="3"/>

--- a/database/data/raw/metadata/bioprint_metadata_template_v2.xlsx
+++ b/database/data/raw/metadata/bioprint_metadata_template_v2.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="24">
   <si>
     <t>image_path</t>
   </si>
@@ -122,6 +122,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>补速度</t>
     </r>
     <r>
@@ -172,6 +178,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>修改高度为</t>
     </r>
     <r>
@@ -186,6 +198,12 @@
   </si>
   <si>
     <t>挤出速度再小无法成型，高度是否还能增大，放大挤出速度？</t>
+  </si>
+  <si>
+    <t>忘记调速度了。。。</t>
+  </si>
+  <si>
+    <t>重新补上</t>
   </si>
 </sst>
 </file>
@@ -2962,968 +2980,1852 @@
     </row>
     <row r="74" spans="1:9">
       <c r="A74" s="3"/>
-      <c r="B74" s="8"/>
-      <c r="C74" s="8"/>
-      <c r="D74" s="8"/>
-      <c r="E74" s="8"/>
-      <c r="F74" s="8"/>
+      <c r="B74" s="8">
+        <v>73</v>
+      </c>
+      <c r="C74" s="8">
+        <v>15</v>
+      </c>
+      <c r="D74" s="8">
+        <v>8</v>
+      </c>
+      <c r="E74" s="8">
+        <v>3</v>
+      </c>
+      <c r="F74" s="8">
+        <v>5</v>
+      </c>
       <c r="G74" s="8"/>
       <c r="H74" s="3"/>
       <c r="I74" s="3"/>
     </row>
     <row r="75" spans="1:9">
       <c r="A75" s="3"/>
-      <c r="B75" s="8"/>
-      <c r="C75" s="8"/>
-      <c r="D75" s="8"/>
-      <c r="E75" s="8"/>
-      <c r="F75" s="8"/>
+      <c r="B75" s="8">
+        <v>74</v>
+      </c>
+      <c r="C75" s="8">
+        <v>15</v>
+      </c>
+      <c r="D75" s="8">
+        <v>7</v>
+      </c>
+      <c r="E75" s="8">
+        <v>3</v>
+      </c>
+      <c r="F75" s="8">
+        <v>5</v>
+      </c>
       <c r="G75" s="8"/>
       <c r="H75" s="3"/>
       <c r="I75" s="3"/>
     </row>
     <row r="76" spans="1:9">
       <c r="A76" s="3"/>
-      <c r="B76" s="8"/>
-      <c r="C76" s="8"/>
-      <c r="D76" s="8"/>
-      <c r="E76" s="8"/>
-      <c r="F76" s="8"/>
+      <c r="B76" s="8">
+        <v>75</v>
+      </c>
+      <c r="C76" s="8">
+        <v>15</v>
+      </c>
+      <c r="D76" s="8">
+        <v>6</v>
+      </c>
+      <c r="E76" s="8">
+        <v>3</v>
+      </c>
+      <c r="F76" s="8">
+        <v>5</v>
+      </c>
       <c r="G76" s="8"/>
       <c r="H76" s="3"/>
       <c r="I76" s="3"/>
     </row>
     <row r="77" spans="1:9">
       <c r="A77" s="3"/>
-      <c r="B77" s="8"/>
-      <c r="C77" s="8"/>
-      <c r="D77" s="8"/>
-      <c r="E77" s="8"/>
-      <c r="F77" s="8"/>
+      <c r="B77" s="8">
+        <v>76</v>
+      </c>
+      <c r="C77" s="8">
+        <v>15</v>
+      </c>
+      <c r="D77" s="8">
+        <v>5</v>
+      </c>
+      <c r="E77" s="8">
+        <v>3</v>
+      </c>
+      <c r="F77" s="8">
+        <v>5</v>
+      </c>
       <c r="G77" s="8"/>
       <c r="H77" s="3"/>
       <c r="I77" s="3"/>
     </row>
     <row r="78" spans="1:9">
       <c r="A78" s="3"/>
-      <c r="B78" s="8"/>
-      <c r="C78" s="8"/>
-      <c r="D78" s="8"/>
-      <c r="E78" s="8"/>
-      <c r="F78" s="8"/>
+      <c r="B78" s="8">
+        <v>77</v>
+      </c>
+      <c r="C78" s="8">
+        <v>15</v>
+      </c>
+      <c r="D78" s="8">
+        <v>4</v>
+      </c>
+      <c r="E78" s="8">
+        <v>3</v>
+      </c>
+      <c r="F78" s="8">
+        <v>5</v>
+      </c>
       <c r="G78" s="8"/>
       <c r="H78" s="3"/>
       <c r="I78" s="3"/>
     </row>
     <row r="79" spans="1:9">
       <c r="A79" s="3"/>
-      <c r="B79" s="8"/>
-      <c r="C79" s="8"/>
-      <c r="D79" s="8"/>
-      <c r="E79" s="8"/>
-      <c r="F79" s="8"/>
+      <c r="B79" s="8">
+        <v>78</v>
+      </c>
+      <c r="C79" s="8">
+        <v>15</v>
+      </c>
+      <c r="D79" s="8">
+        <v>3</v>
+      </c>
+      <c r="E79" s="8">
+        <v>3</v>
+      </c>
+      <c r="F79" s="8">
+        <v>5</v>
+      </c>
       <c r="G79" s="8"/>
       <c r="H79" s="3"/>
       <c r="I79" s="3"/>
     </row>
     <row r="80" spans="1:9">
       <c r="A80" s="3"/>
-      <c r="B80" s="8"/>
-      <c r="C80" s="8"/>
-      <c r="D80" s="8"/>
-      <c r="E80" s="8"/>
-      <c r="F80" s="8"/>
+      <c r="B80" s="8">
+        <v>79</v>
+      </c>
+      <c r="C80" s="8">
+        <v>15</v>
+      </c>
+      <c r="D80" s="8">
+        <v>2</v>
+      </c>
+      <c r="E80" s="8">
+        <v>3</v>
+      </c>
+      <c r="F80" s="8">
+        <v>5</v>
+      </c>
       <c r="G80" s="8"/>
       <c r="H80" s="3"/>
       <c r="I80" s="3"/>
     </row>
     <row r="81" spans="1:9">
       <c r="A81" s="3"/>
-      <c r="B81" s="8"/>
-      <c r="C81" s="8"/>
-      <c r="D81" s="8"/>
-      <c r="E81" s="8"/>
-      <c r="F81" s="8"/>
+      <c r="B81" s="8">
+        <v>80</v>
+      </c>
+      <c r="C81" s="8">
+        <v>20</v>
+      </c>
+      <c r="D81" s="8">
+        <v>6</v>
+      </c>
+      <c r="E81" s="8">
+        <v>3</v>
+      </c>
+      <c r="F81" s="8">
+        <v>3.5</v>
+      </c>
       <c r="G81" s="8"/>
       <c r="H81" s="3"/>
       <c r="I81" s="3"/>
     </row>
     <row r="82" spans="1:9">
       <c r="A82" s="3"/>
-      <c r="B82" s="8"/>
-      <c r="C82" s="8"/>
-      <c r="D82" s="8"/>
-      <c r="E82" s="8"/>
-      <c r="F82" s="8"/>
+      <c r="B82" s="8">
+        <v>81</v>
+      </c>
+      <c r="C82" s="8">
+        <v>20</v>
+      </c>
+      <c r="D82" s="8">
+        <v>7</v>
+      </c>
+      <c r="E82" s="8">
+        <v>3</v>
+      </c>
+      <c r="F82" s="8">
+        <v>3.5</v>
+      </c>
       <c r="G82" s="8"/>
       <c r="H82" s="3"/>
       <c r="I82" s="3"/>
     </row>
     <row r="83" spans="1:9">
       <c r="A83" s="3"/>
-      <c r="B83" s="8"/>
-      <c r="C83" s="8"/>
-      <c r="D83" s="8"/>
-      <c r="E83" s="8"/>
-      <c r="F83" s="8"/>
+      <c r="B83" s="8">
+        <v>82</v>
+      </c>
+      <c r="C83" s="8">
+        <v>20</v>
+      </c>
+      <c r="D83" s="8">
+        <v>8</v>
+      </c>
+      <c r="E83" s="8">
+        <v>3</v>
+      </c>
+      <c r="F83" s="8">
+        <v>3.5</v>
+      </c>
       <c r="G83" s="8"/>
       <c r="H83" s="3"/>
       <c r="I83" s="3"/>
     </row>
     <row r="84" spans="1:9">
       <c r="A84" s="3"/>
-      <c r="B84" s="8"/>
-      <c r="C84" s="8"/>
-      <c r="D84" s="8"/>
-      <c r="E84" s="8"/>
-      <c r="F84" s="8"/>
+      <c r="B84" s="8">
+        <v>83</v>
+      </c>
+      <c r="C84" s="8">
+        <v>20</v>
+      </c>
+      <c r="D84" s="8">
+        <v>9</v>
+      </c>
+      <c r="E84" s="8">
+        <v>3</v>
+      </c>
+      <c r="F84" s="8">
+        <v>3.5</v>
+      </c>
       <c r="G84" s="8"/>
       <c r="H84" s="3"/>
       <c r="I84" s="3"/>
     </row>
     <row r="85" spans="1:9">
       <c r="A85" s="3"/>
-      <c r="B85" s="8"/>
-      <c r="C85" s="8"/>
-      <c r="D85" s="8"/>
-      <c r="E85" s="8"/>
-      <c r="F85" s="8"/>
+      <c r="B85" s="8">
+        <v>84</v>
+      </c>
+      <c r="C85" s="8">
+        <v>20</v>
+      </c>
+      <c r="D85" s="8">
+        <v>1</v>
+      </c>
+      <c r="E85" s="8">
+        <v>3</v>
+      </c>
+      <c r="F85" s="8">
+        <v>4</v>
+      </c>
       <c r="G85" s="8"/>
       <c r="H85" s="3"/>
       <c r="I85" s="3"/>
     </row>
     <row r="86" spans="1:9">
       <c r="A86" s="3"/>
-      <c r="B86" s="8"/>
-      <c r="C86" s="8"/>
-      <c r="D86" s="8"/>
-      <c r="E86" s="8"/>
-      <c r="F86" s="8"/>
+      <c r="B86" s="8">
+        <v>85</v>
+      </c>
+      <c r="C86" s="8">
+        <v>20</v>
+      </c>
+      <c r="D86" s="8">
+        <v>2</v>
+      </c>
+      <c r="E86" s="8">
+        <v>3</v>
+      </c>
+      <c r="F86" s="8">
+        <v>4</v>
+      </c>
       <c r="G86" s="8"/>
       <c r="H86" s="3"/>
       <c r="I86" s="3"/>
     </row>
     <row r="87" spans="1:9">
       <c r="A87" s="3"/>
-      <c r="B87" s="8"/>
-      <c r="C87" s="8"/>
-      <c r="D87" s="8"/>
-      <c r="E87" s="8"/>
-      <c r="F87" s="8"/>
+      <c r="B87" s="8">
+        <v>86</v>
+      </c>
+      <c r="C87" s="8">
+        <v>20</v>
+      </c>
+      <c r="D87" s="8">
+        <v>3</v>
+      </c>
+      <c r="E87" s="8">
+        <v>3</v>
+      </c>
+      <c r="F87" s="8">
+        <v>4</v>
+      </c>
       <c r="G87" s="8"/>
       <c r="H87" s="3"/>
       <c r="I87" s="3"/>
     </row>
     <row r="88" spans="1:9">
       <c r="A88" s="3"/>
-      <c r="B88" s="8"/>
-      <c r="C88" s="8"/>
-      <c r="D88" s="8"/>
-      <c r="E88" s="8"/>
-      <c r="F88" s="8"/>
+      <c r="B88" s="8">
+        <v>87</v>
+      </c>
+      <c r="C88" s="8">
+        <v>20</v>
+      </c>
+      <c r="D88" s="8">
+        <v>4</v>
+      </c>
+      <c r="E88" s="8">
+        <v>3</v>
+      </c>
+      <c r="F88" s="8">
+        <v>4</v>
+      </c>
       <c r="G88" s="8"/>
       <c r="H88" s="3"/>
       <c r="I88" s="3"/>
     </row>
     <row r="89" spans="1:9">
       <c r="A89" s="3"/>
-      <c r="B89" s="8"/>
-      <c r="C89" s="8"/>
-      <c r="D89" s="8"/>
-      <c r="E89" s="8"/>
-      <c r="F89" s="8"/>
+      <c r="B89" s="8">
+        <v>88</v>
+      </c>
+      <c r="C89" s="8">
+        <v>20</v>
+      </c>
+      <c r="D89" s="8">
+        <v>5</v>
+      </c>
+      <c r="E89" s="8">
+        <v>3</v>
+      </c>
+      <c r="F89" s="8">
+        <v>4</v>
+      </c>
       <c r="G89" s="8"/>
       <c r="H89" s="3"/>
       <c r="I89" s="3"/>
     </row>
     <row r="90" spans="1:9">
       <c r="A90" s="3"/>
-      <c r="B90" s="8"/>
-      <c r="C90" s="8"/>
-      <c r="D90" s="8"/>
-      <c r="E90" s="8"/>
-      <c r="F90" s="8"/>
+      <c r="B90" s="8">
+        <v>89</v>
+      </c>
+      <c r="C90" s="8">
+        <v>20</v>
+      </c>
+      <c r="D90" s="8">
+        <v>6</v>
+      </c>
+      <c r="E90" s="8">
+        <v>3</v>
+      </c>
+      <c r="F90" s="8">
+        <v>4</v>
+      </c>
       <c r="G90" s="8"/>
       <c r="H90" s="3"/>
       <c r="I90" s="3"/>
     </row>
     <row r="91" spans="1:9">
       <c r="A91" s="3"/>
-      <c r="B91" s="8"/>
-      <c r="C91" s="8"/>
-      <c r="D91" s="8"/>
-      <c r="E91" s="8"/>
-      <c r="F91" s="8"/>
+      <c r="B91" s="8">
+        <v>90</v>
+      </c>
+      <c r="C91" s="8">
+        <v>20</v>
+      </c>
+      <c r="D91" s="8">
+        <v>7</v>
+      </c>
+      <c r="E91" s="8">
+        <v>3</v>
+      </c>
+      <c r="F91" s="8">
+        <v>4</v>
+      </c>
       <c r="G91" s="8"/>
       <c r="H91" s="3"/>
       <c r="I91" s="3"/>
     </row>
     <row r="92" spans="1:9">
       <c r="A92" s="3"/>
-      <c r="B92" s="8"/>
-      <c r="C92" s="8"/>
-      <c r="D92" s="8"/>
-      <c r="E92" s="8"/>
-      <c r="F92" s="8"/>
+      <c r="B92" s="8">
+        <v>91</v>
+      </c>
+      <c r="C92" s="8">
+        <v>20</v>
+      </c>
+      <c r="D92" s="8">
+        <v>8</v>
+      </c>
+      <c r="E92" s="8">
+        <v>3</v>
+      </c>
+      <c r="F92" s="8">
+        <v>4</v>
+      </c>
       <c r="G92" s="8"/>
       <c r="H92" s="3"/>
       <c r="I92" s="3"/>
     </row>
     <row r="93" spans="1:9">
       <c r="A93" s="3"/>
-      <c r="B93" s="8"/>
-      <c r="C93" s="8"/>
-      <c r="D93" s="8"/>
-      <c r="E93" s="8"/>
-      <c r="F93" s="8"/>
+      <c r="B93" s="8">
+        <v>92</v>
+      </c>
+      <c r="C93" s="8">
+        <v>20</v>
+      </c>
+      <c r="D93" s="8">
+        <v>9</v>
+      </c>
+      <c r="E93" s="8">
+        <v>3</v>
+      </c>
+      <c r="F93" s="8">
+        <v>4</v>
+      </c>
       <c r="G93" s="8"/>
       <c r="H93" s="3"/>
       <c r="I93" s="3"/>
     </row>
     <row r="94" spans="1:9">
       <c r="A94" s="3"/>
-      <c r="B94" s="8"/>
-      <c r="C94" s="8"/>
-      <c r="D94" s="8"/>
-      <c r="E94" s="8"/>
-      <c r="F94" s="8"/>
+      <c r="B94" s="8">
+        <v>93</v>
+      </c>
+      <c r="C94" s="8">
+        <v>20</v>
+      </c>
+      <c r="D94" s="8">
+        <v>10</v>
+      </c>
+      <c r="E94" s="8">
+        <v>3</v>
+      </c>
+      <c r="F94" s="8">
+        <v>4</v>
+      </c>
       <c r="G94" s="8"/>
       <c r="H94" s="3"/>
       <c r="I94" s="3"/>
     </row>
     <row r="95" spans="1:9">
       <c r="A95" s="3"/>
-      <c r="B95" s="8"/>
-      <c r="C95" s="8"/>
-      <c r="D95" s="8"/>
-      <c r="E95" s="8"/>
-      <c r="F95" s="8"/>
+      <c r="B95" s="8">
+        <v>94</v>
+      </c>
+      <c r="C95" s="8">
+        <v>20</v>
+      </c>
+      <c r="D95" s="8">
+        <v>11</v>
+      </c>
+      <c r="E95" s="8">
+        <v>3</v>
+      </c>
+      <c r="F95" s="8">
+        <v>4</v>
+      </c>
       <c r="G95" s="8"/>
       <c r="H95" s="3"/>
       <c r="I95" s="3"/>
     </row>
     <row r="96" spans="1:9">
       <c r="A96" s="3"/>
-      <c r="B96" s="8"/>
-      <c r="C96" s="8"/>
-      <c r="D96" s="8"/>
-      <c r="E96" s="8"/>
-      <c r="F96" s="8"/>
+      <c r="B96" s="8">
+        <v>95</v>
+      </c>
+      <c r="C96" s="8">
+        <v>20</v>
+      </c>
+      <c r="D96" s="8">
+        <v>1</v>
+      </c>
+      <c r="E96" s="8">
+        <v>3</v>
+      </c>
+      <c r="F96" s="8">
+        <v>2.5</v>
+      </c>
       <c r="G96" s="8"/>
       <c r="H96" s="3"/>
       <c r="I96" s="3"/>
     </row>
     <row r="97" spans="1:9">
       <c r="A97" s="3"/>
-      <c r="B97" s="8"/>
-      <c r="C97" s="8"/>
-      <c r="D97" s="8"/>
-      <c r="E97" s="8"/>
-      <c r="F97" s="8"/>
+      <c r="B97" s="8">
+        <v>96</v>
+      </c>
+      <c r="C97" s="8">
+        <v>20</v>
+      </c>
+      <c r="D97" s="8">
+        <v>2</v>
+      </c>
+      <c r="E97" s="8">
+        <v>3</v>
+      </c>
+      <c r="F97" s="8">
+        <v>2.5</v>
+      </c>
       <c r="G97" s="8"/>
       <c r="H97" s="3"/>
       <c r="I97" s="3"/>
     </row>
     <row r="98" spans="1:9">
       <c r="A98" s="3"/>
-      <c r="B98" s="8"/>
-      <c r="C98" s="8"/>
-      <c r="D98" s="8"/>
-      <c r="E98" s="8"/>
-      <c r="F98" s="8"/>
+      <c r="B98" s="8">
+        <v>97</v>
+      </c>
+      <c r="C98" s="8">
+        <v>20</v>
+      </c>
+      <c r="D98" s="8">
+        <v>3</v>
+      </c>
+      <c r="E98" s="8">
+        <v>3</v>
+      </c>
+      <c r="F98" s="8">
+        <v>2.5</v>
+      </c>
       <c r="G98" s="8"/>
       <c r="H98" s="3"/>
       <c r="I98" s="3"/>
     </row>
     <row r="99" spans="1:9">
       <c r="A99" s="3"/>
-      <c r="B99" s="8"/>
-      <c r="C99" s="8"/>
-      <c r="D99" s="8"/>
-      <c r="E99" s="8"/>
-      <c r="F99" s="8"/>
+      <c r="B99" s="8">
+        <v>98</v>
+      </c>
+      <c r="C99" s="8">
+        <v>20</v>
+      </c>
+      <c r="D99" s="8">
+        <v>4</v>
+      </c>
+      <c r="E99" s="8">
+        <v>3</v>
+      </c>
+      <c r="F99" s="8">
+        <v>2.5</v>
+      </c>
       <c r="G99" s="8"/>
       <c r="H99" s="3"/>
       <c r="I99" s="3"/>
     </row>
     <row r="100" spans="1:9">
       <c r="A100" s="3"/>
-      <c r="B100" s="8"/>
-      <c r="C100" s="8"/>
-      <c r="D100" s="8"/>
-      <c r="E100" s="8"/>
-      <c r="F100" s="8"/>
+      <c r="B100" s="8">
+        <v>99</v>
+      </c>
+      <c r="C100" s="8">
+        <v>20</v>
+      </c>
+      <c r="D100" s="8">
+        <v>5</v>
+      </c>
+      <c r="E100" s="8">
+        <v>3</v>
+      </c>
+      <c r="F100" s="8">
+        <v>2.5</v>
+      </c>
       <c r="G100" s="8"/>
       <c r="H100" s="3"/>
       <c r="I100" s="3"/>
     </row>
     <row r="101" spans="1:9">
       <c r="A101" s="3"/>
-      <c r="B101" s="8"/>
-      <c r="C101" s="8"/>
-      <c r="D101" s="8"/>
-      <c r="E101" s="8"/>
-      <c r="F101" s="8"/>
+      <c r="B101" s="8">
+        <v>100</v>
+      </c>
+      <c r="C101" s="8">
+        <v>20</v>
+      </c>
+      <c r="D101" s="8">
+        <v>6</v>
+      </c>
+      <c r="E101" s="8">
+        <v>3</v>
+      </c>
+      <c r="F101" s="8">
+        <v>2.5</v>
+      </c>
       <c r="G101" s="8"/>
       <c r="H101" s="3"/>
       <c r="I101" s="3"/>
     </row>
     <row r="102" spans="1:9">
       <c r="A102" s="3"/>
-      <c r="B102" s="8"/>
-      <c r="C102" s="8"/>
-      <c r="D102" s="8"/>
-      <c r="E102" s="8"/>
-      <c r="F102" s="8"/>
+      <c r="B102" s="8">
+        <v>101</v>
+      </c>
+      <c r="C102" s="8">
+        <v>20</v>
+      </c>
+      <c r="D102" s="8">
+        <v>7</v>
+      </c>
+      <c r="E102" s="8">
+        <v>3</v>
+      </c>
+      <c r="F102" s="8">
+        <v>2.5</v>
+      </c>
       <c r="G102" s="8"/>
       <c r="H102" s="3"/>
       <c r="I102" s="3"/>
     </row>
     <row r="103" spans="1:9">
       <c r="A103" s="3"/>
-      <c r="B103" s="8"/>
-      <c r="C103" s="8"/>
-      <c r="D103" s="8"/>
-      <c r="E103" s="8"/>
-      <c r="F103" s="8"/>
+      <c r="B103" s="8">
+        <v>102</v>
+      </c>
+      <c r="C103" s="8">
+        <v>20</v>
+      </c>
+      <c r="D103" s="8">
+        <v>8</v>
+      </c>
+      <c r="E103" s="8">
+        <v>3</v>
+      </c>
+      <c r="F103" s="8">
+        <v>2.5</v>
+      </c>
       <c r="G103" s="8"/>
       <c r="H103" s="3"/>
       <c r="I103" s="3"/>
     </row>
     <row r="104" spans="1:9">
       <c r="A104" s="3"/>
-      <c r="B104" s="8"/>
-      <c r="C104" s="8"/>
-      <c r="D104" s="8"/>
-      <c r="E104" s="8"/>
-      <c r="F104" s="8"/>
+      <c r="B104" s="8">
+        <v>103</v>
+      </c>
+      <c r="C104" s="8">
+        <v>20</v>
+      </c>
+      <c r="D104" s="8">
+        <v>9</v>
+      </c>
+      <c r="E104" s="8">
+        <v>3</v>
+      </c>
+      <c r="F104" s="8">
+        <v>2.5</v>
+      </c>
       <c r="G104" s="8"/>
       <c r="H104" s="3"/>
       <c r="I104" s="3"/>
     </row>
     <row r="105" spans="1:9">
       <c r="A105" s="3"/>
-      <c r="B105" s="8"/>
-      <c r="C105" s="8"/>
-      <c r="D105" s="8"/>
-      <c r="E105" s="8"/>
-      <c r="F105" s="8"/>
+      <c r="B105" s="8">
+        <v>104</v>
+      </c>
+      <c r="C105" s="8">
+        <v>20</v>
+      </c>
+      <c r="D105" s="8">
+        <v>10</v>
+      </c>
+      <c r="E105" s="8">
+        <v>3</v>
+      </c>
+      <c r="F105" s="8">
+        <v>2.5</v>
+      </c>
       <c r="G105" s="8"/>
       <c r="H105" s="3"/>
       <c r="I105" s="3"/>
     </row>
     <row r="106" spans="1:9">
       <c r="A106" s="3"/>
-      <c r="B106" s="8"/>
-      <c r="C106" s="8"/>
-      <c r="D106" s="8"/>
-      <c r="E106" s="8"/>
-      <c r="F106" s="8"/>
+      <c r="B106" s="8">
+        <v>105</v>
+      </c>
+      <c r="C106" s="8">
+        <v>20</v>
+      </c>
+      <c r="D106" s="8">
+        <v>1</v>
+      </c>
+      <c r="E106" s="8">
+        <v>3</v>
+      </c>
+      <c r="F106" s="8">
+        <v>4.5</v>
+      </c>
       <c r="G106" s="8"/>
       <c r="H106" s="3"/>
       <c r="I106" s="3"/>
     </row>
     <row r="107" spans="1:9">
       <c r="A107" s="3"/>
-      <c r="B107" s="8"/>
-      <c r="C107" s="8"/>
-      <c r="D107" s="8"/>
-      <c r="E107" s="8"/>
-      <c r="F107" s="8"/>
+      <c r="B107" s="8">
+        <v>106</v>
+      </c>
+      <c r="C107" s="8">
+        <v>20</v>
+      </c>
+      <c r="D107" s="8">
+        <v>2</v>
+      </c>
+      <c r="E107" s="8">
+        <v>3</v>
+      </c>
+      <c r="F107" s="8">
+        <v>4.5</v>
+      </c>
       <c r="G107" s="8"/>
       <c r="H107" s="3"/>
       <c r="I107" s="3"/>
     </row>
     <row r="108" spans="1:9">
       <c r="A108" s="3"/>
-      <c r="B108" s="8"/>
-      <c r="C108" s="8"/>
-      <c r="D108" s="8"/>
-      <c r="E108" s="8"/>
-      <c r="F108" s="8"/>
+      <c r="B108" s="8">
+        <v>107</v>
+      </c>
+      <c r="C108" s="8">
+        <v>20</v>
+      </c>
+      <c r="D108" s="8">
+        <v>3</v>
+      </c>
+      <c r="E108" s="8">
+        <v>3</v>
+      </c>
+      <c r="F108" s="8">
+        <v>4.5</v>
+      </c>
       <c r="G108" s="8"/>
       <c r="H108" s="3"/>
       <c r="I108" s="3"/>
     </row>
     <row r="109" spans="1:9">
       <c r="A109" s="3"/>
-      <c r="B109" s="8"/>
-      <c r="C109" s="8"/>
-      <c r="D109" s="8"/>
-      <c r="E109" s="8"/>
-      <c r="F109" s="8"/>
+      <c r="B109" s="8">
+        <v>108</v>
+      </c>
+      <c r="C109" s="8">
+        <v>20</v>
+      </c>
+      <c r="D109" s="8">
+        <v>4</v>
+      </c>
+      <c r="E109" s="8">
+        <v>3</v>
+      </c>
+      <c r="F109" s="8">
+        <v>4.5</v>
+      </c>
       <c r="G109" s="8"/>
       <c r="H109" s="3"/>
       <c r="I109" s="3"/>
     </row>
     <row r="110" spans="1:9">
       <c r="A110" s="3"/>
-      <c r="B110" s="8"/>
-      <c r="C110" s="8"/>
-      <c r="D110" s="8"/>
-      <c r="E110" s="8"/>
-      <c r="F110" s="8"/>
+      <c r="B110" s="8">
+        <v>109</v>
+      </c>
+      <c r="C110" s="8">
+        <v>20</v>
+      </c>
+      <c r="D110" s="8">
+        <v>5</v>
+      </c>
+      <c r="E110" s="8">
+        <v>3</v>
+      </c>
+      <c r="F110" s="8">
+        <v>4.5</v>
+      </c>
       <c r="G110" s="8"/>
       <c r="H110" s="3"/>
       <c r="I110" s="3"/>
     </row>
     <row r="111" spans="1:9">
       <c r="A111" s="3"/>
-      <c r="B111" s="8"/>
-      <c r="C111" s="8"/>
-      <c r="D111" s="8"/>
-      <c r="E111" s="8"/>
-      <c r="F111" s="8"/>
+      <c r="B111" s="8">
+        <v>110</v>
+      </c>
+      <c r="C111" s="8">
+        <v>20</v>
+      </c>
+      <c r="D111" s="8">
+        <v>6</v>
+      </c>
+      <c r="E111" s="8">
+        <v>3</v>
+      </c>
+      <c r="F111" s="8">
+        <v>4.5</v>
+      </c>
       <c r="G111" s="8"/>
       <c r="H111" s="3"/>
       <c r="I111" s="3"/>
     </row>
     <row r="112" spans="1:9">
       <c r="A112" s="3"/>
-      <c r="B112" s="8"/>
-      <c r="C112" s="8"/>
-      <c r="D112" s="8"/>
-      <c r="E112" s="8"/>
-      <c r="F112" s="8"/>
+      <c r="B112" s="8">
+        <v>111</v>
+      </c>
+      <c r="C112" s="8">
+        <v>20</v>
+      </c>
+      <c r="D112" s="8">
+        <v>7</v>
+      </c>
+      <c r="E112" s="8">
+        <v>3</v>
+      </c>
+      <c r="F112" s="8">
+        <v>4.5</v>
+      </c>
       <c r="G112" s="8"/>
       <c r="H112" s="3"/>
       <c r="I112" s="3"/>
     </row>
     <row r="113" spans="1:9">
       <c r="A113" s="3"/>
-      <c r="B113" s="8"/>
-      <c r="C113" s="8"/>
-      <c r="D113" s="8"/>
-      <c r="E113" s="8"/>
-      <c r="F113" s="8"/>
+      <c r="B113" s="8">
+        <v>112</v>
+      </c>
+      <c r="C113" s="8">
+        <v>20</v>
+      </c>
+      <c r="D113" s="8">
+        <v>8</v>
+      </c>
+      <c r="E113" s="8">
+        <v>3</v>
+      </c>
+      <c r="F113" s="8">
+        <v>4.5</v>
+      </c>
       <c r="G113" s="8"/>
       <c r="H113" s="3"/>
       <c r="I113" s="3"/>
     </row>
     <row r="114" spans="1:9">
       <c r="A114" s="3"/>
-      <c r="B114" s="8"/>
-      <c r="C114" s="8"/>
-      <c r="D114" s="8"/>
-      <c r="E114" s="8"/>
-      <c r="F114" s="8"/>
+      <c r="B114" s="8">
+        <v>113</v>
+      </c>
+      <c r="C114" s="8">
+        <v>20</v>
+      </c>
+      <c r="D114" s="8">
+        <v>9</v>
+      </c>
+      <c r="E114" s="8">
+        <v>3</v>
+      </c>
+      <c r="F114" s="8">
+        <v>4.5</v>
+      </c>
       <c r="G114" s="8"/>
       <c r="H114" s="3"/>
       <c r="I114" s="3"/>
     </row>
     <row r="115" spans="1:9">
       <c r="A115" s="3"/>
-      <c r="B115" s="8"/>
-      <c r="C115" s="8"/>
-      <c r="D115" s="8"/>
-      <c r="E115" s="8"/>
-      <c r="F115" s="8"/>
+      <c r="B115" s="8">
+        <v>114</v>
+      </c>
+      <c r="C115" s="8">
+        <v>20</v>
+      </c>
+      <c r="D115" s="8">
+        <v>10</v>
+      </c>
+      <c r="E115" s="8">
+        <v>3</v>
+      </c>
+      <c r="F115" s="8">
+        <v>4.5</v>
+      </c>
       <c r="G115" s="8"/>
       <c r="H115" s="3"/>
       <c r="I115" s="3"/>
     </row>
     <row r="116" spans="1:9">
       <c r="A116" s="3"/>
-      <c r="B116" s="8"/>
-      <c r="C116" s="8"/>
-      <c r="D116" s="8"/>
-      <c r="E116" s="8"/>
-      <c r="F116" s="8"/>
+      <c r="B116" s="8">
+        <v>115</v>
+      </c>
+      <c r="C116" s="8">
+        <v>20</v>
+      </c>
+      <c r="D116" s="8">
+        <v>11</v>
+      </c>
+      <c r="E116" s="8">
+        <v>3</v>
+      </c>
+      <c r="F116" s="8">
+        <v>4.5</v>
+      </c>
       <c r="G116" s="8"/>
       <c r="H116" s="3"/>
       <c r="I116" s="3"/>
     </row>
     <row r="117" spans="1:9">
       <c r="A117" s="3"/>
-      <c r="B117" s="8"/>
-      <c r="C117" s="8"/>
-      <c r="D117" s="8"/>
-      <c r="E117" s="8"/>
-      <c r="F117" s="8"/>
+      <c r="B117" s="8">
+        <v>116</v>
+      </c>
+      <c r="C117" s="8">
+        <v>20</v>
+      </c>
+      <c r="D117" s="8">
+        <v>12</v>
+      </c>
+      <c r="E117" s="8">
+        <v>3</v>
+      </c>
+      <c r="F117" s="8">
+        <v>4.5</v>
+      </c>
       <c r="G117" s="8"/>
       <c r="H117" s="3"/>
       <c r="I117" s="3"/>
     </row>
     <row r="118" spans="1:9">
       <c r="A118" s="3"/>
-      <c r="B118" s="8"/>
-      <c r="C118" s="8"/>
-      <c r="D118" s="8"/>
-      <c r="E118" s="8"/>
-      <c r="F118" s="8"/>
+      <c r="B118" s="8">
+        <v>117</v>
+      </c>
+      <c r="C118" s="8">
+        <v>20</v>
+      </c>
+      <c r="D118" s="8">
+        <v>12</v>
+      </c>
+      <c r="E118" s="8">
+        <v>3</v>
+      </c>
+      <c r="F118" s="8">
+        <v>5</v>
+      </c>
       <c r="G118" s="8"/>
       <c r="H118" s="3"/>
       <c r="I118" s="3"/>
     </row>
     <row r="119" spans="1:9">
       <c r="A119" s="3"/>
-      <c r="B119" s="8"/>
-      <c r="C119" s="8"/>
-      <c r="D119" s="8"/>
-      <c r="E119" s="8"/>
-      <c r="F119" s="8"/>
+      <c r="B119" s="8">
+        <v>118</v>
+      </c>
+      <c r="C119" s="8">
+        <v>20</v>
+      </c>
+      <c r="D119" s="8">
+        <v>11</v>
+      </c>
+      <c r="E119" s="8">
+        <v>3</v>
+      </c>
+      <c r="F119" s="8">
+        <v>5</v>
+      </c>
       <c r="G119" s="8"/>
       <c r="H119" s="3"/>
       <c r="I119" s="3"/>
     </row>
     <row r="120" spans="1:9">
       <c r="A120" s="3"/>
-      <c r="B120" s="8"/>
-      <c r="C120" s="8"/>
-      <c r="D120" s="8"/>
-      <c r="E120" s="8"/>
-      <c r="F120" s="8"/>
+      <c r="B120" s="8">
+        <v>119</v>
+      </c>
+      <c r="C120" s="8">
+        <v>20</v>
+      </c>
+      <c r="D120" s="8">
+        <v>10</v>
+      </c>
+      <c r="E120" s="8">
+        <v>3</v>
+      </c>
+      <c r="F120" s="8">
+        <v>5</v>
+      </c>
       <c r="G120" s="8"/>
       <c r="H120" s="3"/>
       <c r="I120" s="3"/>
     </row>
     <row r="121" spans="1:9">
       <c r="A121" s="3"/>
-      <c r="B121" s="8"/>
-      <c r="C121" s="8"/>
-      <c r="D121" s="8"/>
-      <c r="E121" s="8"/>
-      <c r="F121" s="8"/>
+      <c r="B121" s="8">
+        <v>120</v>
+      </c>
+      <c r="C121" s="8">
+        <v>20</v>
+      </c>
+      <c r="D121" s="8">
+        <v>9</v>
+      </c>
+      <c r="E121" s="8">
+        <v>3</v>
+      </c>
+      <c r="F121" s="8">
+        <v>5</v>
+      </c>
       <c r="G121" s="8"/>
       <c r="H121" s="3"/>
       <c r="I121" s="3"/>
     </row>
     <row r="122" spans="1:9">
       <c r="A122" s="3"/>
-      <c r="B122" s="8"/>
-      <c r="C122" s="8"/>
-      <c r="D122" s="8"/>
-      <c r="E122" s="8"/>
-      <c r="F122" s="8"/>
+      <c r="B122" s="8">
+        <v>121</v>
+      </c>
+      <c r="C122" s="8">
+        <v>20</v>
+      </c>
+      <c r="D122" s="8">
+        <v>8</v>
+      </c>
+      <c r="E122" s="8">
+        <v>3</v>
+      </c>
+      <c r="F122" s="8">
+        <v>5</v>
+      </c>
       <c r="G122" s="8"/>
       <c r="H122" s="3"/>
       <c r="I122" s="3"/>
     </row>
     <row r="123" spans="1:9">
       <c r="A123" s="3"/>
-      <c r="B123" s="8"/>
-      <c r="C123" s="8"/>
-      <c r="D123" s="8"/>
-      <c r="E123" s="8"/>
-      <c r="F123" s="8"/>
+      <c r="B123" s="8">
+        <v>122</v>
+      </c>
+      <c r="C123" s="8">
+        <v>20</v>
+      </c>
+      <c r="D123" s="8">
+        <v>7</v>
+      </c>
+      <c r="E123" s="8">
+        <v>3</v>
+      </c>
+      <c r="F123" s="8">
+        <v>5</v>
+      </c>
       <c r="G123" s="8"/>
       <c r="H123" s="3"/>
       <c r="I123" s="3"/>
     </row>
-    <row r="124" spans="1:9">
+    <row r="124" ht="14.4" spans="1:9">
       <c r="A124" s="3"/>
-      <c r="B124" s="8"/>
-      <c r="C124" s="8"/>
-      <c r="D124" s="8"/>
-      <c r="E124" s="8"/>
-      <c r="F124" s="8"/>
+      <c r="B124" s="8">
+        <v>123</v>
+      </c>
+      <c r="C124" s="8">
+        <v>10</v>
+      </c>
+      <c r="D124" s="8">
+        <v>6</v>
+      </c>
+      <c r="E124" s="8">
+        <v>3</v>
+      </c>
+      <c r="F124" s="8">
+        <v>5</v>
+      </c>
       <c r="G124" s="8"/>
       <c r="H124" s="3"/>
-      <c r="I124" s="3"/>
+      <c r="I124" s="9" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="125" spans="1:9">
       <c r="A125" s="3"/>
-      <c r="B125" s="8"/>
-      <c r="C125" s="8"/>
-      <c r="D125" s="8"/>
-      <c r="E125" s="8"/>
-      <c r="F125" s="8"/>
+      <c r="B125" s="8">
+        <v>124</v>
+      </c>
+      <c r="C125" s="8">
+        <v>10</v>
+      </c>
+      <c r="D125" s="8">
+        <v>5</v>
+      </c>
+      <c r="E125" s="8">
+        <v>3</v>
+      </c>
+      <c r="F125" s="8">
+        <v>5</v>
+      </c>
       <c r="G125" s="8"/>
       <c r="H125" s="3"/>
       <c r="I125" s="3"/>
     </row>
     <row r="126" spans="1:9">
       <c r="A126" s="3"/>
-      <c r="B126" s="8"/>
-      <c r="C126" s="8"/>
-      <c r="D126" s="8"/>
-      <c r="E126" s="8"/>
-      <c r="F126" s="8"/>
+      <c r="B126" s="8">
+        <v>125</v>
+      </c>
+      <c r="C126" s="8">
+        <v>10</v>
+      </c>
+      <c r="D126" s="8">
+        <v>4</v>
+      </c>
+      <c r="E126" s="8">
+        <v>3</v>
+      </c>
+      <c r="F126" s="8">
+        <v>5</v>
+      </c>
       <c r="G126" s="8"/>
       <c r="H126" s="3"/>
       <c r="I126" s="3"/>
     </row>
     <row r="127" spans="1:9">
       <c r="A127" s="3"/>
-      <c r="B127" s="8"/>
-      <c r="C127" s="8"/>
-      <c r="D127" s="8"/>
-      <c r="E127" s="8"/>
-      <c r="F127" s="8"/>
+      <c r="B127" s="8">
+        <v>126</v>
+      </c>
+      <c r="C127" s="8">
+        <v>10</v>
+      </c>
+      <c r="D127" s="8">
+        <v>3</v>
+      </c>
+      <c r="E127" s="8">
+        <v>3</v>
+      </c>
+      <c r="F127" s="8">
+        <v>5</v>
+      </c>
       <c r="G127" s="8"/>
       <c r="H127" s="3"/>
       <c r="I127" s="3"/>
     </row>
     <row r="128" spans="1:9">
       <c r="A128" s="3"/>
-      <c r="B128" s="8"/>
-      <c r="C128" s="8"/>
-      <c r="D128" s="8"/>
-      <c r="E128" s="8"/>
-      <c r="F128" s="8"/>
+      <c r="B128" s="8">
+        <v>127</v>
+      </c>
+      <c r="C128" s="8">
+        <v>10</v>
+      </c>
+      <c r="D128" s="8">
+        <v>2</v>
+      </c>
+      <c r="E128" s="8">
+        <v>3</v>
+      </c>
+      <c r="F128" s="8">
+        <v>5</v>
+      </c>
       <c r="G128" s="8"/>
       <c r="H128" s="3"/>
       <c r="I128" s="3"/>
     </row>
-    <row r="129" spans="1:9">
+    <row r="129" ht="14.4" spans="1:9">
       <c r="A129" s="3"/>
-      <c r="B129" s="8"/>
-      <c r="C129" s="8"/>
-      <c r="D129" s="8"/>
-      <c r="E129" s="8"/>
-      <c r="F129" s="8"/>
+      <c r="B129" s="8">
+        <v>128</v>
+      </c>
+      <c r="C129" s="8">
+        <v>20</v>
+      </c>
+      <c r="D129" s="8">
+        <v>6</v>
+      </c>
+      <c r="E129" s="8">
+        <v>3</v>
+      </c>
+      <c r="F129" s="8">
+        <v>5</v>
+      </c>
       <c r="G129" s="8"/>
       <c r="H129" s="3"/>
-      <c r="I129" s="3"/>
+      <c r="I129" s="9" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="130" spans="1:9">
       <c r="A130" s="3"/>
-      <c r="B130" s="8"/>
-      <c r="C130" s="8"/>
-      <c r="D130" s="8"/>
-      <c r="E130" s="8"/>
-      <c r="F130" s="8"/>
+      <c r="B130" s="8">
+        <v>129</v>
+      </c>
+      <c r="C130" s="8">
+        <v>20</v>
+      </c>
+      <c r="D130" s="8">
+        <v>5</v>
+      </c>
+      <c r="E130" s="8">
+        <v>3</v>
+      </c>
+      <c r="F130" s="8">
+        <v>5</v>
+      </c>
       <c r="G130" s="8"/>
       <c r="H130" s="3"/>
       <c r="I130" s="3"/>
     </row>
     <row r="131" spans="1:9">
       <c r="A131" s="3"/>
-      <c r="B131" s="8"/>
-      <c r="C131" s="8"/>
-      <c r="D131" s="8"/>
-      <c r="E131" s="8"/>
-      <c r="F131" s="8"/>
+      <c r="B131" s="8">
+        <v>130</v>
+      </c>
+      <c r="C131" s="8">
+        <v>20</v>
+      </c>
+      <c r="D131" s="8">
+        <v>4</v>
+      </c>
+      <c r="E131" s="8">
+        <v>3</v>
+      </c>
+      <c r="F131" s="8">
+        <v>5</v>
+      </c>
       <c r="G131" s="8"/>
       <c r="H131" s="3"/>
       <c r="I131" s="3"/>
     </row>
     <row r="132" spans="1:9">
       <c r="A132" s="3"/>
-      <c r="B132" s="8"/>
-      <c r="C132" s="8"/>
-      <c r="D132" s="8"/>
-      <c r="E132" s="8"/>
-      <c r="F132" s="8"/>
+      <c r="B132" s="8">
+        <v>131</v>
+      </c>
+      <c r="C132" s="8">
+        <v>20</v>
+      </c>
+      <c r="D132" s="8">
+        <v>3</v>
+      </c>
+      <c r="E132" s="8">
+        <v>3</v>
+      </c>
+      <c r="F132" s="8">
+        <v>5</v>
+      </c>
       <c r="G132" s="8"/>
       <c r="H132" s="3"/>
       <c r="I132" s="3"/>
     </row>
     <row r="133" spans="1:9">
       <c r="A133" s="3"/>
-      <c r="B133" s="8"/>
-      <c r="C133" s="8"/>
-      <c r="D133" s="8"/>
-      <c r="E133" s="8"/>
-      <c r="F133" s="8"/>
+      <c r="B133" s="8">
+        <v>132</v>
+      </c>
+      <c r="C133" s="8">
+        <v>10</v>
+      </c>
+      <c r="D133" s="8">
+        <v>7</v>
+      </c>
+      <c r="E133" s="8">
+        <v>3</v>
+      </c>
+      <c r="F133" s="8">
+        <v>5</v>
+      </c>
       <c r="G133" s="8"/>
       <c r="H133" s="3"/>
       <c r="I133" s="3"/>
     </row>
     <row r="134" spans="1:9">
       <c r="A134" s="3"/>
-      <c r="B134" s="8"/>
-      <c r="C134" s="8"/>
-      <c r="D134" s="8"/>
-      <c r="E134" s="8"/>
-      <c r="F134" s="8"/>
+      <c r="B134" s="8">
+        <v>133</v>
+      </c>
+      <c r="C134" s="8">
+        <v>10</v>
+      </c>
+      <c r="D134" s="8">
+        <v>8</v>
+      </c>
+      <c r="E134" s="8">
+        <v>3</v>
+      </c>
+      <c r="F134" s="8">
+        <v>5</v>
+      </c>
       <c r="G134" s="8"/>
       <c r="H134" s="3"/>
       <c r="I134" s="3"/>
     </row>
     <row r="135" spans="1:9">
       <c r="A135" s="3"/>
-      <c r="B135" s="8"/>
-      <c r="C135" s="8"/>
-      <c r="D135" s="8"/>
-      <c r="E135" s="8"/>
-      <c r="F135" s="8"/>
+      <c r="B135" s="8">
+        <v>134</v>
+      </c>
+      <c r="C135" s="8">
+        <v>10</v>
+      </c>
+      <c r="D135" s="8">
+        <v>8</v>
+      </c>
+      <c r="E135" s="8">
+        <v>3</v>
+      </c>
+      <c r="F135" s="8">
+        <v>4.5</v>
+      </c>
       <c r="G135" s="8"/>
       <c r="H135" s="3"/>
       <c r="I135" s="3"/>
     </row>
     <row r="136" spans="1:9">
       <c r="A136" s="3"/>
-      <c r="B136" s="8"/>
-      <c r="C136" s="8"/>
-      <c r="D136" s="8"/>
-      <c r="E136" s="8"/>
-      <c r="F136" s="8"/>
+      <c r="B136" s="8">
+        <v>135</v>
+      </c>
+      <c r="C136" s="8">
+        <v>10</v>
+      </c>
+      <c r="D136" s="8">
+        <v>7</v>
+      </c>
+      <c r="E136" s="8">
+        <v>3</v>
+      </c>
+      <c r="F136" s="8">
+        <v>4.5</v>
+      </c>
       <c r="G136" s="8"/>
       <c r="H136" s="3"/>
       <c r="I136" s="3"/>
     </row>
     <row r="137" spans="1:9">
       <c r="A137" s="3"/>
-      <c r="B137" s="8"/>
-      <c r="C137" s="8"/>
-      <c r="D137" s="8"/>
-      <c r="E137" s="8"/>
-      <c r="F137" s="8"/>
+      <c r="B137" s="8">
+        <v>136</v>
+      </c>
+      <c r="C137" s="8">
+        <v>10</v>
+      </c>
+      <c r="D137" s="8">
+        <v>6</v>
+      </c>
+      <c r="E137" s="8">
+        <v>3</v>
+      </c>
+      <c r="F137" s="8">
+        <v>4.5</v>
+      </c>
       <c r="G137" s="8"/>
       <c r="H137" s="3"/>
       <c r="I137" s="3"/>
     </row>
     <row r="138" spans="1:9">
       <c r="A138" s="3"/>
-      <c r="B138" s="8"/>
-      <c r="C138" s="8"/>
-      <c r="D138" s="8"/>
-      <c r="E138" s="8"/>
-      <c r="F138" s="8"/>
+      <c r="B138" s="8">
+        <v>137</v>
+      </c>
+      <c r="C138" s="8">
+        <v>10</v>
+      </c>
+      <c r="D138" s="8">
+        <v>5</v>
+      </c>
+      <c r="E138" s="8">
+        <v>3</v>
+      </c>
+      <c r="F138" s="8">
+        <v>4.5</v>
+      </c>
       <c r="G138" s="8"/>
       <c r="H138" s="3"/>
       <c r="I138" s="3"/>
     </row>
     <row r="139" spans="1:9">
       <c r="A139" s="3"/>
-      <c r="B139" s="8"/>
-      <c r="C139" s="8"/>
-      <c r="D139" s="8"/>
-      <c r="E139" s="8"/>
-      <c r="F139" s="8"/>
+      <c r="B139" s="8">
+        <v>138</v>
+      </c>
+      <c r="C139" s="8">
+        <v>10</v>
+      </c>
+      <c r="D139" s="8">
+        <v>4</v>
+      </c>
+      <c r="E139" s="8">
+        <v>3</v>
+      </c>
+      <c r="F139" s="8">
+        <v>4.5</v>
+      </c>
       <c r="G139" s="8"/>
       <c r="H139" s="3"/>
       <c r="I139" s="3"/>
     </row>
     <row r="140" spans="1:9">
       <c r="A140" s="3"/>
-      <c r="B140" s="8"/>
-      <c r="C140" s="8"/>
-      <c r="D140" s="8"/>
-      <c r="E140" s="8"/>
-      <c r="F140" s="8"/>
+      <c r="B140" s="8">
+        <v>139</v>
+      </c>
+      <c r="C140" s="8">
+        <v>10</v>
+      </c>
+      <c r="D140" s="8">
+        <v>3</v>
+      </c>
+      <c r="E140" s="8">
+        <v>3</v>
+      </c>
+      <c r="F140" s="8">
+        <v>4.5</v>
+      </c>
       <c r="G140" s="8"/>
       <c r="H140" s="3"/>
       <c r="I140" s="3"/>
     </row>
     <row r="141" spans="1:9">
       <c r="A141" s="3"/>
-      <c r="B141" s="8"/>
-      <c r="C141" s="8"/>
-      <c r="D141" s="8"/>
-      <c r="E141" s="8"/>
-      <c r="F141" s="8"/>
+      <c r="B141" s="8">
+        <v>140</v>
+      </c>
+      <c r="C141" s="8">
+        <v>10</v>
+      </c>
+      <c r="D141" s="8">
+        <v>2</v>
+      </c>
+      <c r="E141" s="8">
+        <v>3</v>
+      </c>
+      <c r="F141" s="8">
+        <v>4.5</v>
+      </c>
       <c r="G141" s="8"/>
       <c r="H141" s="3"/>
       <c r="I141" s="3"/>
     </row>
     <row r="142" spans="1:9">
       <c r="A142" s="3"/>
-      <c r="B142" s="8"/>
-      <c r="C142" s="8"/>
-      <c r="D142" s="8"/>
-      <c r="E142" s="8"/>
-      <c r="F142" s="8"/>
+      <c r="B142" s="8">
+        <v>141</v>
+      </c>
+      <c r="C142" s="8">
+        <v>10</v>
+      </c>
+      <c r="D142" s="8">
+        <v>8</v>
+      </c>
+      <c r="E142" s="8">
+        <v>3</v>
+      </c>
+      <c r="F142" s="8">
+        <v>4</v>
+      </c>
       <c r="G142" s="8"/>
       <c r="H142" s="3"/>
       <c r="I142" s="3"/>
     </row>
     <row r="143" spans="1:9">
       <c r="A143" s="3"/>
-      <c r="B143" s="8"/>
-      <c r="C143" s="8"/>
-      <c r="D143" s="8"/>
-      <c r="E143" s="8"/>
-      <c r="F143" s="8"/>
+      <c r="B143" s="8">
+        <v>142</v>
+      </c>
+      <c r="C143" s="8">
+        <v>10</v>
+      </c>
+      <c r="D143" s="8">
+        <v>7</v>
+      </c>
+      <c r="E143" s="8">
+        <v>3</v>
+      </c>
+      <c r="F143" s="8">
+        <v>4</v>
+      </c>
       <c r="G143" s="8"/>
       <c r="H143" s="3"/>
       <c r="I143" s="3"/>
     </row>
     <row r="144" spans="1:9">
       <c r="A144" s="3"/>
-      <c r="B144" s="8"/>
-      <c r="C144" s="8"/>
-      <c r="D144" s="8"/>
-      <c r="E144" s="8"/>
-      <c r="F144" s="8"/>
+      <c r="B144" s="8">
+        <v>143</v>
+      </c>
+      <c r="C144" s="8">
+        <v>10</v>
+      </c>
+      <c r="D144" s="8">
+        <v>6</v>
+      </c>
+      <c r="E144" s="8">
+        <v>3</v>
+      </c>
+      <c r="F144" s="8">
+        <v>4</v>
+      </c>
       <c r="G144" s="8"/>
       <c r="H144" s="3"/>
       <c r="I144" s="3"/>
     </row>
     <row r="145" spans="1:9">
       <c r="A145" s="3"/>
-      <c r="B145" s="8"/>
-      <c r="C145" s="8"/>
-      <c r="D145" s="8"/>
-      <c r="E145" s="8"/>
-      <c r="F145" s="8"/>
+      <c r="B145" s="8">
+        <v>144</v>
+      </c>
+      <c r="C145" s="8">
+        <v>10</v>
+      </c>
+      <c r="D145" s="8">
+        <v>5</v>
+      </c>
+      <c r="E145" s="8">
+        <v>3</v>
+      </c>
+      <c r="F145" s="8">
+        <v>4</v>
+      </c>
       <c r="G145" s="8"/>
       <c r="H145" s="3"/>
       <c r="I145" s="3"/>
     </row>
     <row r="146" spans="1:9">
       <c r="A146" s="3"/>
-      <c r="B146" s="8"/>
-      <c r="C146" s="8"/>
-      <c r="D146" s="8"/>
-      <c r="E146" s="8"/>
-      <c r="F146" s="8"/>
+      <c r="B146" s="8">
+        <v>145</v>
+      </c>
+      <c r="C146" s="8">
+        <v>10</v>
+      </c>
+      <c r="D146" s="8">
+        <v>4</v>
+      </c>
+      <c r="E146" s="8">
+        <v>3</v>
+      </c>
+      <c r="F146" s="8">
+        <v>4</v>
+      </c>
       <c r="G146" s="8"/>
       <c r="H146" s="3"/>
       <c r="I146" s="3"/>
     </row>
     <row r="147" spans="1:9">
       <c r="A147" s="3"/>
-      <c r="B147" s="8"/>
-      <c r="C147" s="8"/>
-      <c r="D147" s="8"/>
-      <c r="E147" s="8"/>
-      <c r="F147" s="8"/>
+      <c r="B147" s="8">
+        <v>146</v>
+      </c>
+      <c r="C147" s="8">
+        <v>10</v>
+      </c>
+      <c r="D147" s="8">
+        <v>3</v>
+      </c>
+      <c r="E147" s="8">
+        <v>3</v>
+      </c>
+      <c r="F147" s="8">
+        <v>4</v>
+      </c>
       <c r="G147" s="8"/>
       <c r="H147" s="3"/>
       <c r="I147" s="3"/>
     </row>
     <row r="148" spans="1:9">
       <c r="A148" s="3"/>
-      <c r="B148" s="8"/>
-      <c r="C148" s="8"/>
-      <c r="D148" s="8"/>
-      <c r="E148" s="8"/>
-      <c r="F148" s="8"/>
+      <c r="B148" s="8">
+        <v>147</v>
+      </c>
+      <c r="C148" s="8">
+        <v>10</v>
+      </c>
+      <c r="D148" s="8">
+        <v>2</v>
+      </c>
+      <c r="E148" s="8">
+        <v>3</v>
+      </c>
+      <c r="F148" s="8">
+        <v>4</v>
+      </c>
       <c r="G148" s="8"/>
       <c r="H148" s="3"/>
       <c r="I148" s="3"/>
     </row>
     <row r="149" spans="1:9">
       <c r="A149" s="3"/>
-      <c r="B149" s="8"/>
-      <c r="C149" s="8"/>
-      <c r="D149" s="8"/>
-      <c r="E149" s="8"/>
-      <c r="F149" s="8"/>
+      <c r="B149" s="8">
+        <v>148</v>
+      </c>
+      <c r="C149" s="8">
+        <v>10</v>
+      </c>
+      <c r="D149" s="8">
+        <v>1</v>
+      </c>
+      <c r="E149" s="8">
+        <v>3</v>
+      </c>
+      <c r="F149" s="8">
+        <v>4</v>
+      </c>
       <c r="G149" s="8"/>
       <c r="H149" s="3"/>
       <c r="I149" s="3"/>
     </row>
     <row r="150" spans="1:9">
       <c r="A150" s="3"/>
-      <c r="B150" s="8"/>
-      <c r="C150" s="8"/>
-      <c r="D150" s="8"/>
-      <c r="E150" s="8"/>
-      <c r="F150" s="8"/>
+      <c r="B150" s="8">
+        <v>149</v>
+      </c>
+      <c r="C150" s="8">
+        <v>10</v>
+      </c>
+      <c r="D150" s="8">
+        <v>8</v>
+      </c>
+      <c r="E150" s="8">
+        <v>3</v>
+      </c>
+      <c r="F150" s="8">
+        <v>3.5</v>
+      </c>
       <c r="G150" s="8"/>
       <c r="H150" s="3"/>
       <c r="I150" s="3"/>
     </row>
     <row r="151" spans="1:9">
       <c r="A151" s="3"/>
-      <c r="B151" s="8"/>
-      <c r="C151" s="8"/>
-      <c r="D151" s="8"/>
-      <c r="E151" s="8"/>
-      <c r="F151" s="8"/>
+      <c r="B151" s="8">
+        <v>150</v>
+      </c>
+      <c r="C151" s="8">
+        <v>10</v>
+      </c>
+      <c r="D151" s="8">
+        <v>7</v>
+      </c>
+      <c r="E151" s="8">
+        <v>3</v>
+      </c>
+      <c r="F151" s="8">
+        <v>3.5</v>
+      </c>
       <c r="G151" s="8"/>
       <c r="H151" s="3"/>
       <c r="I151" s="3"/>
     </row>
     <row r="152" spans="1:9">
       <c r="A152" s="3"/>
-      <c r="B152" s="8"/>
-      <c r="C152" s="8"/>
-      <c r="D152" s="8"/>
-      <c r="E152" s="8"/>
-      <c r="F152" s="8"/>
+      <c r="B152" s="8">
+        <v>151</v>
+      </c>
+      <c r="C152" s="8">
+        <v>10</v>
+      </c>
+      <c r="D152" s="8">
+        <v>6</v>
+      </c>
+      <c r="E152" s="8">
+        <v>3</v>
+      </c>
+      <c r="F152" s="8">
+        <v>3.5</v>
+      </c>
       <c r="G152" s="8"/>
       <c r="H152" s="3"/>
       <c r="I152" s="3"/>
     </row>
     <row r="153" spans="1:9">
       <c r="A153" s="3"/>
-      <c r="B153" s="8"/>
-      <c r="C153" s="8"/>
-      <c r="D153" s="8"/>
-      <c r="E153" s="8"/>
-      <c r="F153" s="8"/>
+      <c r="B153" s="8">
+        <v>152</v>
+      </c>
+      <c r="C153" s="8">
+        <v>10</v>
+      </c>
+      <c r="D153" s="8">
+        <v>5</v>
+      </c>
+      <c r="E153" s="8">
+        <v>3</v>
+      </c>
+      <c r="F153" s="8">
+        <v>3.5</v>
+      </c>
       <c r="G153" s="8"/>
       <c r="H153" s="3"/>
       <c r="I153" s="3"/>
     </row>
     <row r="154" spans="1:9">
       <c r="A154" s="3"/>
-      <c r="B154" s="8"/>
-      <c r="C154" s="8"/>
-      <c r="D154" s="8"/>
-      <c r="E154" s="8"/>
-      <c r="F154" s="8"/>
+      <c r="B154" s="8">
+        <v>153</v>
+      </c>
+      <c r="C154" s="8">
+        <v>10</v>
+      </c>
+      <c r="D154" s="8">
+        <v>4</v>
+      </c>
+      <c r="E154" s="8">
+        <v>3</v>
+      </c>
+      <c r="F154" s="8">
+        <v>3.5</v>
+      </c>
       <c r="G154" s="8"/>
       <c r="H154" s="3"/>
       <c r="I154" s="3"/>
     </row>
     <row r="155" spans="1:9">
       <c r="A155" s="3"/>
-      <c r="B155" s="8"/>
-      <c r="C155" s="8"/>
-      <c r="D155" s="8"/>
-      <c r="E155" s="8"/>
-      <c r="F155" s="8"/>
+      <c r="B155" s="8">
+        <v>154</v>
+      </c>
+      <c r="C155" s="8">
+        <v>10</v>
+      </c>
+      <c r="D155" s="8">
+        <v>3</v>
+      </c>
+      <c r="E155" s="8">
+        <v>3</v>
+      </c>
+      <c r="F155" s="8">
+        <v>3.5</v>
+      </c>
       <c r="G155" s="8"/>
       <c r="H155" s="3"/>
       <c r="I155" s="3"/>
     </row>
     <row r="156" spans="1:9">
       <c r="A156" s="3"/>
-      <c r="B156" s="8"/>
-      <c r="C156" s="8"/>
-      <c r="D156" s="8"/>
-      <c r="E156" s="8"/>
-      <c r="F156" s="8"/>
+      <c r="B156" s="8">
+        <v>155</v>
+      </c>
+      <c r="C156" s="8">
+        <v>10</v>
+      </c>
+      <c r="D156" s="8">
+        <v>2</v>
+      </c>
+      <c r="E156" s="8">
+        <v>3</v>
+      </c>
+      <c r="F156" s="8">
+        <v>3.5</v>
+      </c>
       <c r="G156" s="8"/>
       <c r="H156" s="3"/>
       <c r="I156" s="3"/>
     </row>
     <row r="157" spans="1:9">
       <c r="A157" s="3"/>
-      <c r="B157" s="8"/>
-      <c r="C157" s="8"/>
-      <c r="D157" s="8"/>
-      <c r="E157" s="8"/>
-      <c r="F157" s="8"/>
+      <c r="B157" s="8">
+        <v>156</v>
+      </c>
+      <c r="C157" s="8">
+        <v>10</v>
+      </c>
+      <c r="D157" s="8">
+        <v>1</v>
+      </c>
+      <c r="E157" s="8">
+        <v>3</v>
+      </c>
+      <c r="F157" s="8">
+        <v>3.5</v>
+      </c>
       <c r="G157" s="8"/>
       <c r="H157" s="3"/>
       <c r="I157" s="3"/>
     </row>
     <row r="158" spans="1:9">
       <c r="A158" s="3"/>
-      <c r="B158" s="8"/>
-      <c r="C158" s="8"/>
-      <c r="D158" s="8"/>
-      <c r="E158" s="8"/>
-      <c r="F158" s="8"/>
+      <c r="B158" s="8">
+        <v>157</v>
+      </c>
+      <c r="C158" s="8">
+        <v>10</v>
+      </c>
+      <c r="D158" s="8">
+        <v>1</v>
+      </c>
+      <c r="E158" s="8">
+        <v>3</v>
+      </c>
+      <c r="F158" s="8">
+        <v>3</v>
+      </c>
       <c r="G158" s="8"/>
       <c r="H158" s="3"/>
       <c r="I158" s="3"/>
     </row>
     <row r="159" spans="1:9">
       <c r="A159" s="3"/>
-      <c r="B159" s="8"/>
-      <c r="C159" s="8"/>
-      <c r="D159" s="8"/>
-      <c r="E159" s="8"/>
-      <c r="F159" s="8"/>
+      <c r="B159" s="8">
+        <v>158</v>
+      </c>
+      <c r="C159" s="8">
+        <v>10</v>
+      </c>
+      <c r="D159" s="8">
+        <v>2</v>
+      </c>
+      <c r="E159" s="8">
+        <v>3</v>
+      </c>
+      <c r="F159" s="8">
+        <v>3</v>
+      </c>
       <c r="G159" s="8"/>
       <c r="H159" s="3"/>
       <c r="I159" s="3"/>
     </row>
     <row r="160" spans="1:9">
       <c r="A160" s="3"/>
-      <c r="B160" s="8"/>
-      <c r="C160" s="8"/>
-      <c r="D160" s="8"/>
-      <c r="E160" s="8"/>
-      <c r="F160" s="8"/>
+      <c r="B160" s="8">
+        <v>159</v>
+      </c>
+      <c r="C160" s="8">
+        <v>10</v>
+      </c>
+      <c r="D160" s="8">
+        <v>3</v>
+      </c>
+      <c r="E160" s="8">
+        <v>3</v>
+      </c>
+      <c r="F160" s="8">
+        <v>3</v>
+      </c>
       <c r="G160" s="8"/>
       <c r="H160" s="3"/>
       <c r="I160" s="3"/>
     </row>
     <row r="161" spans="1:9">
       <c r="A161" s="3"/>
-      <c r="B161" s="8"/>
-      <c r="C161" s="8"/>
-      <c r="D161" s="8"/>
-      <c r="E161" s="8"/>
-      <c r="F161" s="8"/>
+      <c r="B161" s="8">
+        <v>160</v>
+      </c>
+      <c r="C161" s="8">
+        <v>10</v>
+      </c>
+      <c r="D161" s="8">
+        <v>4</v>
+      </c>
+      <c r="E161" s="8">
+        <v>3</v>
+      </c>
+      <c r="F161" s="8">
+        <v>3</v>
+      </c>
       <c r="G161" s="8"/>
       <c r="H161" s="3"/>
       <c r="I161" s="3"/>

--- a/database/data/raw/metadata/bioprint_metadata_template_v2.xlsx
+++ b/database/data/raw/metadata/bioprint_metadata_template_v2.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="15300"/>
+    <workbookView windowWidth="24750" windowHeight="11430"/>
   </bookViews>
   <sheets>
     <sheet name="metadata" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="26">
   <si>
     <t>image_path</t>
   </si>
@@ -204,6 +204,49 @@
   </si>
   <si>
     <t>重新补上</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>经测试发现</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>2.5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>无法打出</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>少打了一个</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>11</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -872,7 +915,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -895,6 +938,7 @@
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="49" applyFont="1"/>
   </cellXfs>
   <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1172,8 +1216,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MetadataTable" displayName="MetadataTable" ref="A1:I201" totalsRowShown="0">
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:I201" etc:filterBottomFollowUsedRange="0"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MetadataTable" displayName="MetadataTable" ref="A1:I552" totalsRowShown="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:I552" etc:filterBottomFollowUsedRange="0"/>
   <tableColumns count="9">
     <tableColumn id="1" name="image_path"/>
     <tableColumn id="9" name="编号"/>
@@ -1384,8 +1428,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I201"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <dimension ref="A1:I552"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
     <col min="2" max="7" width="20" customWidth="1"/>
@@ -1393,7 +1437,7 @@
     <col min="9" max="9" width="51.7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.4" spans="1:9">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1422,7 +1466,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" ht="14.4" spans="1:9">
+    <row r="2" spans="1:9">
       <c r="A2" s="3"/>
       <c r="B2" s="4">
         <v>1</v>
@@ -1447,7 +1491,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" ht="14.4" spans="1:9">
+    <row r="3" spans="1:9">
       <c r="A3" s="3"/>
       <c r="B3" s="7">
         <v>2</v>
@@ -1493,7 +1537,7 @@
       </c>
       <c r="I4" s="3"/>
     </row>
-    <row r="5" ht="14.4" spans="1:9">
+    <row r="5" spans="1:9">
       <c r="A5" s="3"/>
       <c r="B5" s="8">
         <v>4</v>
@@ -1564,7 +1608,7 @@
       </c>
       <c r="I7" s="3"/>
     </row>
-    <row r="8" ht="14.4" spans="1:9">
+    <row r="8" spans="1:9">
       <c r="A8" s="3"/>
       <c r="B8" s="8">
         <v>7</v>
@@ -1589,7 +1633,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" ht="14.4" spans="1:9">
+    <row r="9" spans="1:9">
       <c r="A9" s="3"/>
       <c r="B9" s="8">
         <v>8</v>
@@ -1660,7 +1704,7 @@
       </c>
       <c r="I11" s="3"/>
     </row>
-    <row r="12" ht="14.4" spans="1:9">
+    <row r="12" spans="1:9">
       <c r="A12" s="3"/>
       <c r="B12" s="8">
         <v>11</v>
@@ -1809,7 +1853,7 @@
       <c r="H18" s="3"/>
       <c r="I18" s="3"/>
     </row>
-    <row r="19" ht="14.4" spans="1:9">
+    <row r="19" spans="1:9">
       <c r="A19" s="3"/>
       <c r="B19" s="8">
         <v>18</v>
@@ -1874,7 +1918,7 @@
       <c r="H21" s="3"/>
       <c r="I21" s="3"/>
     </row>
-    <row r="22" ht="14.4" spans="1:9">
+    <row r="22" spans="1:9">
       <c r="A22" s="3"/>
       <c r="B22" s="8">
         <v>21</v>
@@ -1897,7 +1941,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="23" ht="14.4" spans="1:9">
+    <row r="23" spans="1:9">
       <c r="A23" s="3"/>
       <c r="B23" s="8">
         <v>22</v>
@@ -1920,7 +1964,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="24" ht="14.4" spans="1:9">
+    <row r="24" spans="1:9">
       <c r="A24" s="3"/>
       <c r="B24" s="8">
         <v>23</v>
@@ -2594,7 +2638,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="56" ht="14.4" spans="1:9">
+    <row r="56" spans="1:9">
       <c r="A56" s="3"/>
       <c r="B56" s="8">
         <v>55</v>
@@ -2827,7 +2871,7 @@
       <c r="H66" s="3"/>
       <c r="I66" s="3"/>
     </row>
-    <row r="67" ht="14.4" spans="1:9">
+    <row r="67" spans="1:9">
       <c r="A67" s="3"/>
       <c r="B67" s="8">
         <v>66</v>
@@ -2955,7 +2999,7 @@
       <c r="H72" s="3"/>
       <c r="I72" s="3"/>
     </row>
-    <row r="73" ht="14.4" spans="1:9">
+    <row r="73" spans="1:9">
       <c r="A73" s="3"/>
       <c r="B73" s="8">
         <v>72</v>
@@ -4028,7 +4072,7 @@
       <c r="H123" s="3"/>
       <c r="I123" s="3"/>
     </row>
-    <row r="124" ht="14.4" spans="1:9">
+    <row r="124" spans="1:9">
       <c r="A124" s="3"/>
       <c r="B124" s="8">
         <v>123</v>
@@ -4135,7 +4179,7 @@
       <c r="H128" s="3"/>
       <c r="I128" s="3"/>
     </row>
-    <row r="129" ht="14.4" spans="1:9">
+    <row r="129" spans="1:9">
       <c r="A129" s="3"/>
       <c r="B129" s="8">
         <v>128</v>
@@ -4832,443 +4876,6816 @@
     </row>
     <row r="162" spans="1:9">
       <c r="A162" s="3"/>
-      <c r="B162" s="8"/>
-      <c r="C162" s="8"/>
-      <c r="D162" s="8"/>
-      <c r="E162" s="8"/>
-      <c r="F162" s="8"/>
+      <c r="B162" s="8">
+        <v>161</v>
+      </c>
+      <c r="C162" s="8">
+        <v>10</v>
+      </c>
+      <c r="D162" s="8">
+        <v>5</v>
+      </c>
+      <c r="E162" s="8">
+        <v>3</v>
+      </c>
+      <c r="F162" s="8">
+        <v>3</v>
+      </c>
       <c r="G162" s="8"/>
       <c r="H162" s="3"/>
       <c r="I162" s="3"/>
     </row>
     <row r="163" spans="1:9">
       <c r="A163" s="3"/>
-      <c r="B163" s="8"/>
-      <c r="C163" s="8"/>
-      <c r="D163" s="8"/>
-      <c r="E163" s="8"/>
-      <c r="F163" s="8"/>
+      <c r="B163" s="8">
+        <v>162</v>
+      </c>
+      <c r="C163" s="8">
+        <v>10</v>
+      </c>
+      <c r="D163" s="8">
+        <v>6</v>
+      </c>
+      <c r="E163" s="8">
+        <v>3</v>
+      </c>
+      <c r="F163" s="8">
+        <v>3</v>
+      </c>
       <c r="G163" s="8"/>
       <c r="H163" s="3"/>
       <c r="I163" s="3"/>
     </row>
     <row r="164" spans="1:9">
       <c r="A164" s="3"/>
-      <c r="B164" s="8"/>
-      <c r="C164" s="8"/>
-      <c r="D164" s="8"/>
-      <c r="E164" s="8"/>
-      <c r="F164" s="8"/>
+      <c r="B164" s="8">
+        <v>163</v>
+      </c>
+      <c r="C164" s="8">
+        <v>10</v>
+      </c>
+      <c r="D164" s="8">
+        <v>7</v>
+      </c>
+      <c r="E164" s="8">
+        <v>3</v>
+      </c>
+      <c r="F164" s="8">
+        <v>3</v>
+      </c>
       <c r="G164" s="8"/>
       <c r="H164" s="3"/>
       <c r="I164" s="3"/>
     </row>
     <row r="165" spans="1:9">
       <c r="A165" s="3"/>
-      <c r="B165" s="8"/>
-      <c r="C165" s="8"/>
-      <c r="D165" s="8"/>
-      <c r="E165" s="8"/>
-      <c r="F165" s="8"/>
+      <c r="B165" s="8">
+        <v>164</v>
+      </c>
+      <c r="C165" s="8">
+        <v>10</v>
+      </c>
+      <c r="D165" s="8">
+        <v>8</v>
+      </c>
+      <c r="E165" s="8">
+        <v>3</v>
+      </c>
+      <c r="F165" s="8">
+        <v>3</v>
+      </c>
       <c r="G165" s="8"/>
       <c r="H165" s="3"/>
       <c r="I165" s="3"/>
     </row>
     <row r="166" spans="1:9">
       <c r="A166" s="3"/>
-      <c r="B166" s="8"/>
-      <c r="C166" s="8"/>
-      <c r="D166" s="8"/>
-      <c r="E166" s="8"/>
-      <c r="F166" s="8"/>
+      <c r="B166" s="8">
+        <v>165</v>
+      </c>
+      <c r="C166" s="8">
+        <v>10</v>
+      </c>
+      <c r="D166" s="8">
+        <v>9</v>
+      </c>
+      <c r="E166" s="8">
+        <v>3</v>
+      </c>
+      <c r="F166" s="8">
+        <v>3</v>
+      </c>
       <c r="G166" s="8"/>
       <c r="H166" s="3"/>
       <c r="I166" s="3"/>
     </row>
     <row r="167" spans="1:9">
       <c r="A167" s="3"/>
-      <c r="B167" s="8"/>
-      <c r="C167" s="8"/>
-      <c r="D167" s="8"/>
-      <c r="E167" s="8"/>
-      <c r="F167" s="8"/>
+      <c r="B167" s="8">
+        <v>166</v>
+      </c>
+      <c r="C167" s="8">
+        <v>10</v>
+      </c>
+      <c r="D167" s="8">
+        <v>10</v>
+      </c>
+      <c r="E167" s="8">
+        <v>3</v>
+      </c>
+      <c r="F167" s="8">
+        <v>3</v>
+      </c>
       <c r="G167" s="8"/>
       <c r="H167" s="3"/>
       <c r="I167" s="3"/>
     </row>
     <row r="168" spans="1:9">
       <c r="A168" s="3"/>
-      <c r="B168" s="8"/>
-      <c r="C168" s="8"/>
-      <c r="D168" s="8"/>
-      <c r="E168" s="8"/>
-      <c r="F168" s="8"/>
+      <c r="B168" s="8">
+        <v>167</v>
+      </c>
+      <c r="C168" s="8">
+        <v>10</v>
+      </c>
+      <c r="D168" s="8">
+        <v>11</v>
+      </c>
+      <c r="E168" s="8">
+        <v>3</v>
+      </c>
+      <c r="F168" s="8">
+        <v>3</v>
+      </c>
       <c r="G168" s="8"/>
       <c r="H168" s="3"/>
       <c r="I168" s="3"/>
     </row>
     <row r="169" spans="1:9">
       <c r="A169" s="3"/>
-      <c r="B169" s="8"/>
-      <c r="C169" s="8"/>
-      <c r="D169" s="8"/>
-      <c r="E169" s="8"/>
-      <c r="F169" s="8"/>
+      <c r="B169" s="8">
+        <v>168</v>
+      </c>
+      <c r="C169" s="8">
+        <v>10</v>
+      </c>
+      <c r="D169" s="8">
+        <v>1</v>
+      </c>
+      <c r="E169" s="8">
+        <v>3</v>
+      </c>
+      <c r="F169" s="8">
+        <v>2.5</v>
+      </c>
       <c r="G169" s="8"/>
       <c r="H169" s="3"/>
       <c r="I169" s="3"/>
     </row>
     <row r="170" spans="1:9">
       <c r="A170" s="3"/>
-      <c r="B170" s="8"/>
-      <c r="C170" s="8"/>
-      <c r="D170" s="8"/>
-      <c r="E170" s="8"/>
-      <c r="F170" s="8"/>
+      <c r="B170" s="8">
+        <v>169</v>
+      </c>
+      <c r="C170" s="8">
+        <v>10</v>
+      </c>
+      <c r="D170" s="8">
+        <v>2</v>
+      </c>
+      <c r="E170" s="8">
+        <v>3</v>
+      </c>
+      <c r="F170" s="8">
+        <v>2.5</v>
+      </c>
       <c r="G170" s="8"/>
       <c r="H170" s="3"/>
       <c r="I170" s="3"/>
     </row>
     <row r="171" spans="1:9">
       <c r="A171" s="3"/>
-      <c r="B171" s="8"/>
-      <c r="C171" s="8"/>
-      <c r="D171" s="8"/>
-      <c r="E171" s="8"/>
-      <c r="F171" s="8"/>
+      <c r="B171" s="8">
+        <v>170</v>
+      </c>
+      <c r="C171" s="8">
+        <v>10</v>
+      </c>
+      <c r="D171" s="8">
+        <v>3</v>
+      </c>
+      <c r="E171" s="8">
+        <v>3</v>
+      </c>
+      <c r="F171" s="8">
+        <v>2.5</v>
+      </c>
       <c r="G171" s="8"/>
       <c r="H171" s="3"/>
       <c r="I171" s="3"/>
     </row>
     <row r="172" spans="1:9">
       <c r="A172" s="3"/>
-      <c r="B172" s="8"/>
-      <c r="C172" s="8"/>
-      <c r="D172" s="8"/>
-      <c r="E172" s="8"/>
-      <c r="F172" s="8"/>
+      <c r="B172" s="8">
+        <v>171</v>
+      </c>
+      <c r="C172" s="8">
+        <v>10</v>
+      </c>
+      <c r="D172" s="8">
+        <v>4</v>
+      </c>
+      <c r="E172" s="8">
+        <v>3</v>
+      </c>
+      <c r="F172" s="8">
+        <v>2.5</v>
+      </c>
       <c r="G172" s="8"/>
       <c r="H172" s="3"/>
       <c r="I172" s="3"/>
     </row>
     <row r="173" spans="1:9">
       <c r="A173" s="3"/>
-      <c r="B173" s="8"/>
-      <c r="C173" s="8"/>
-      <c r="D173" s="8"/>
-      <c r="E173" s="8"/>
-      <c r="F173" s="8"/>
+      <c r="B173" s="8">
+        <v>172</v>
+      </c>
+      <c r="C173" s="8">
+        <v>10</v>
+      </c>
+      <c r="D173" s="8">
+        <v>5</v>
+      </c>
+      <c r="E173" s="8">
+        <v>3</v>
+      </c>
+      <c r="F173" s="8">
+        <v>2.5</v>
+      </c>
       <c r="G173" s="8"/>
       <c r="H173" s="3"/>
       <c r="I173" s="3"/>
     </row>
     <row r="174" spans="1:9">
       <c r="A174" s="3"/>
-      <c r="B174" s="8"/>
-      <c r="C174" s="8"/>
-      <c r="D174" s="8"/>
-      <c r="E174" s="8"/>
-      <c r="F174" s="8"/>
+      <c r="B174" s="8">
+        <v>173</v>
+      </c>
+      <c r="C174" s="8">
+        <v>10</v>
+      </c>
+      <c r="D174" s="8">
+        <v>6</v>
+      </c>
+      <c r="E174" s="8">
+        <v>3</v>
+      </c>
+      <c r="F174" s="8">
+        <v>2.5</v>
+      </c>
       <c r="G174" s="8"/>
       <c r="H174" s="3"/>
       <c r="I174" s="3"/>
     </row>
     <row r="175" spans="1:9">
       <c r="A175" s="3"/>
-      <c r="B175" s="8"/>
-      <c r="C175" s="8"/>
-      <c r="D175" s="8"/>
-      <c r="E175" s="8"/>
-      <c r="F175" s="8"/>
+      <c r="B175" s="8">
+        <v>174</v>
+      </c>
+      <c r="C175" s="8">
+        <v>10</v>
+      </c>
+      <c r="D175" s="8">
+        <v>7</v>
+      </c>
+      <c r="E175" s="8">
+        <v>3</v>
+      </c>
+      <c r="F175" s="8">
+        <v>2.5</v>
+      </c>
       <c r="G175" s="8"/>
       <c r="H175" s="3"/>
       <c r="I175" s="3"/>
     </row>
     <row r="176" spans="1:9">
       <c r="A176" s="3"/>
-      <c r="B176" s="8"/>
-      <c r="C176" s="8"/>
-      <c r="D176" s="8"/>
-      <c r="E176" s="8"/>
-      <c r="F176" s="8"/>
+      <c r="B176" s="8">
+        <v>175</v>
+      </c>
+      <c r="C176" s="8">
+        <v>10</v>
+      </c>
+      <c r="D176" s="8">
+        <v>8</v>
+      </c>
+      <c r="E176" s="8">
+        <v>3</v>
+      </c>
+      <c r="F176" s="8">
+        <v>2.5</v>
+      </c>
       <c r="G176" s="8"/>
       <c r="H176" s="3"/>
       <c r="I176" s="3"/>
     </row>
     <row r="177" spans="1:9">
       <c r="A177" s="3"/>
-      <c r="B177" s="8"/>
-      <c r="C177" s="8"/>
-      <c r="D177" s="8"/>
-      <c r="E177" s="8"/>
-      <c r="F177" s="8"/>
+      <c r="B177" s="8">
+        <v>176</v>
+      </c>
+      <c r="C177" s="8">
+        <v>10</v>
+      </c>
+      <c r="D177" s="8">
+        <v>9</v>
+      </c>
+      <c r="E177" s="8">
+        <v>3</v>
+      </c>
+      <c r="F177" s="8">
+        <v>2.5</v>
+      </c>
       <c r="G177" s="8"/>
       <c r="H177" s="3"/>
       <c r="I177" s="3"/>
     </row>
     <row r="178" spans="1:9">
       <c r="A178" s="3"/>
-      <c r="B178" s="8"/>
-      <c r="C178" s="8"/>
-      <c r="D178" s="8"/>
-      <c r="E178" s="8"/>
-      <c r="F178" s="8"/>
+      <c r="B178" s="8">
+        <v>177</v>
+      </c>
+      <c r="C178" s="8">
+        <v>15</v>
+      </c>
+      <c r="D178" s="8">
+        <v>1</v>
+      </c>
+      <c r="E178" s="8">
+        <v>3</v>
+      </c>
+      <c r="F178" s="8">
+        <v>2.5</v>
+      </c>
       <c r="G178" s="8"/>
       <c r="H178" s="3"/>
       <c r="I178" s="3"/>
     </row>
     <row r="179" spans="1:9">
       <c r="A179" s="3"/>
-      <c r="B179" s="8"/>
-      <c r="C179" s="8"/>
-      <c r="D179" s="8"/>
-      <c r="E179" s="8"/>
-      <c r="F179" s="8"/>
+      <c r="B179" s="8">
+        <v>178</v>
+      </c>
+      <c r="C179" s="8">
+        <v>15</v>
+      </c>
+      <c r="D179" s="8">
+        <v>2</v>
+      </c>
+      <c r="E179" s="8">
+        <v>3</v>
+      </c>
+      <c r="F179" s="8">
+        <v>2.5</v>
+      </c>
       <c r="G179" s="8"/>
       <c r="H179" s="3"/>
       <c r="I179" s="3"/>
     </row>
     <row r="180" spans="1:9">
       <c r="A180" s="3"/>
-      <c r="B180" s="8"/>
-      <c r="C180" s="8"/>
-      <c r="D180" s="8"/>
-      <c r="E180" s="8"/>
-      <c r="F180" s="8"/>
+      <c r="B180" s="8">
+        <v>179</v>
+      </c>
+      <c r="C180" s="8">
+        <v>15</v>
+      </c>
+      <c r="D180" s="8">
+        <v>3</v>
+      </c>
+      <c r="E180" s="8">
+        <v>3</v>
+      </c>
+      <c r="F180" s="8">
+        <v>2.5</v>
+      </c>
       <c r="G180" s="8"/>
       <c r="H180" s="3"/>
       <c r="I180" s="3"/>
     </row>
     <row r="181" spans="1:9">
       <c r="A181" s="3"/>
-      <c r="B181" s="8"/>
-      <c r="C181" s="8"/>
-      <c r="D181" s="8"/>
-      <c r="E181" s="8"/>
-      <c r="F181" s="8"/>
+      <c r="B181" s="8">
+        <v>180</v>
+      </c>
+      <c r="C181" s="8">
+        <v>15</v>
+      </c>
+      <c r="D181" s="8">
+        <v>4</v>
+      </c>
+      <c r="E181" s="8">
+        <v>3</v>
+      </c>
+      <c r="F181" s="8">
+        <v>2.5</v>
+      </c>
       <c r="G181" s="8"/>
       <c r="H181" s="3"/>
       <c r="I181" s="3"/>
     </row>
     <row r="182" spans="1:9">
       <c r="A182" s="3"/>
-      <c r="B182" s="8"/>
-      <c r="C182" s="8"/>
-      <c r="D182" s="8"/>
-      <c r="E182" s="8"/>
-      <c r="F182" s="8"/>
+      <c r="B182" s="8">
+        <v>181</v>
+      </c>
+      <c r="C182" s="8">
+        <v>15</v>
+      </c>
+      <c r="D182" s="8">
+        <v>5</v>
+      </c>
+      <c r="E182" s="8">
+        <v>3</v>
+      </c>
+      <c r="F182" s="8">
+        <v>2.5</v>
+      </c>
       <c r="G182" s="8"/>
       <c r="H182" s="3"/>
       <c r="I182" s="3"/>
     </row>
     <row r="183" spans="1:9">
       <c r="A183" s="3"/>
-      <c r="B183" s="8"/>
-      <c r="C183" s="8"/>
-      <c r="D183" s="8"/>
-      <c r="E183" s="8"/>
-      <c r="F183" s="8"/>
+      <c r="B183" s="8">
+        <v>182</v>
+      </c>
+      <c r="C183" s="8">
+        <v>15</v>
+      </c>
+      <c r="D183" s="8">
+        <v>6</v>
+      </c>
+      <c r="E183" s="8">
+        <v>3</v>
+      </c>
+      <c r="F183" s="8">
+        <v>2.5</v>
+      </c>
       <c r="G183" s="8"/>
       <c r="H183" s="3"/>
       <c r="I183" s="3"/>
     </row>
     <row r="184" spans="1:9">
       <c r="A184" s="3"/>
-      <c r="B184" s="8"/>
-      <c r="C184" s="8"/>
-      <c r="D184" s="8"/>
-      <c r="E184" s="8"/>
-      <c r="F184" s="8"/>
+      <c r="B184" s="8">
+        <v>183</v>
+      </c>
+      <c r="C184" s="8">
+        <v>15</v>
+      </c>
+      <c r="D184" s="8">
+        <v>7</v>
+      </c>
+      <c r="E184" s="8">
+        <v>3</v>
+      </c>
+      <c r="F184" s="8">
+        <v>2.5</v>
+      </c>
       <c r="G184" s="8"/>
       <c r="H184" s="3"/>
       <c r="I184" s="3"/>
     </row>
     <row r="185" spans="1:9">
       <c r="A185" s="3"/>
-      <c r="B185" s="8"/>
-      <c r="C185" s="8"/>
-      <c r="D185" s="8"/>
-      <c r="E185" s="8"/>
-      <c r="F185" s="8"/>
+      <c r="B185" s="8">
+        <v>184</v>
+      </c>
+      <c r="C185" s="8">
+        <v>15</v>
+      </c>
+      <c r="D185" s="8">
+        <v>8</v>
+      </c>
+      <c r="E185" s="8">
+        <v>3</v>
+      </c>
+      <c r="F185" s="8">
+        <v>2.5</v>
+      </c>
       <c r="G185" s="8"/>
       <c r="H185" s="3"/>
       <c r="I185" s="3"/>
     </row>
     <row r="186" spans="1:9">
       <c r="A186" s="3"/>
-      <c r="B186" s="8"/>
-      <c r="C186" s="8"/>
-      <c r="D186" s="8"/>
-      <c r="E186" s="8"/>
-      <c r="F186" s="8"/>
+      <c r="B186" s="8">
+        <v>185</v>
+      </c>
+      <c r="C186" s="8">
+        <v>15</v>
+      </c>
+      <c r="D186" s="8">
+        <v>9</v>
+      </c>
+      <c r="E186" s="8">
+        <v>3</v>
+      </c>
+      <c r="F186" s="8">
+        <v>2.5</v>
+      </c>
       <c r="G186" s="8"/>
       <c r="H186" s="3"/>
       <c r="I186" s="3"/>
     </row>
     <row r="187" spans="1:9">
       <c r="A187" s="3"/>
-      <c r="B187" s="8"/>
-      <c r="C187" s="8"/>
-      <c r="D187" s="8"/>
-      <c r="E187" s="8"/>
-      <c r="F187" s="8"/>
+      <c r="B187" s="8">
+        <v>186</v>
+      </c>
+      <c r="C187" s="8">
+        <v>15</v>
+      </c>
+      <c r="D187" s="8">
+        <v>10</v>
+      </c>
+      <c r="E187" s="8">
+        <v>3</v>
+      </c>
+      <c r="F187" s="8">
+        <v>2.5</v>
+      </c>
       <c r="G187" s="8"/>
       <c r="H187" s="3"/>
       <c r="I187" s="3"/>
     </row>
     <row r="188" spans="1:9">
       <c r="A188" s="3"/>
-      <c r="B188" s="8"/>
-      <c r="C188" s="8"/>
-      <c r="D188" s="8"/>
-      <c r="E188" s="8"/>
-      <c r="F188" s="8"/>
+      <c r="B188" s="8">
+        <v>187</v>
+      </c>
+      <c r="C188" s="8">
+        <v>15</v>
+      </c>
+      <c r="D188" s="8">
+        <v>11</v>
+      </c>
+      <c r="E188" s="8">
+        <v>3</v>
+      </c>
+      <c r="F188" s="8">
+        <v>2.5</v>
+      </c>
       <c r="G188" s="8"/>
       <c r="H188" s="3"/>
       <c r="I188" s="3"/>
     </row>
     <row r="189" spans="1:9">
       <c r="A189" s="3"/>
-      <c r="B189" s="8"/>
-      <c r="C189" s="8"/>
-      <c r="D189" s="8"/>
-      <c r="E189" s="8"/>
-      <c r="F189" s="8"/>
+      <c r="B189" s="8">
+        <v>188</v>
+      </c>
+      <c r="C189" s="8">
+        <v>15</v>
+      </c>
+      <c r="D189" s="8">
+        <v>12</v>
+      </c>
+      <c r="E189" s="8">
+        <v>3</v>
+      </c>
+      <c r="F189" s="8">
+        <v>2.5</v>
+      </c>
       <c r="G189" s="8"/>
       <c r="H189" s="3"/>
       <c r="I189" s="3"/>
     </row>
     <row r="190" spans="1:9">
       <c r="A190" s="3"/>
-      <c r="B190" s="8"/>
-      <c r="C190" s="8"/>
-      <c r="D190" s="8"/>
-      <c r="E190" s="8"/>
-      <c r="F190" s="8"/>
+      <c r="B190" s="8">
+        <v>189</v>
+      </c>
+      <c r="C190" s="8">
+        <v>15</v>
+      </c>
+      <c r="D190" s="8">
+        <v>1</v>
+      </c>
+      <c r="E190" s="8">
+        <v>3</v>
+      </c>
+      <c r="F190" s="8">
+        <v>3</v>
+      </c>
       <c r="G190" s="8"/>
       <c r="H190" s="3"/>
       <c r="I190" s="3"/>
     </row>
     <row r="191" spans="1:9">
       <c r="A191" s="3"/>
-      <c r="B191" s="8"/>
-      <c r="C191" s="8"/>
-      <c r="D191" s="8"/>
-      <c r="E191" s="8"/>
-      <c r="F191" s="8"/>
+      <c r="B191" s="8">
+        <v>190</v>
+      </c>
+      <c r="C191" s="8">
+        <v>15</v>
+      </c>
+      <c r="D191" s="8">
+        <v>2</v>
+      </c>
+      <c r="E191" s="8">
+        <v>3</v>
+      </c>
+      <c r="F191" s="8">
+        <v>3</v>
+      </c>
       <c r="G191" s="8"/>
       <c r="H191" s="3"/>
       <c r="I191" s="3"/>
     </row>
     <row r="192" spans="1:9">
       <c r="A192" s="3"/>
-      <c r="B192" s="8"/>
-      <c r="C192" s="8"/>
-      <c r="D192" s="8"/>
-      <c r="E192" s="8"/>
-      <c r="F192" s="8"/>
+      <c r="B192" s="8">
+        <v>191</v>
+      </c>
+      <c r="C192" s="8">
+        <v>15</v>
+      </c>
+      <c r="D192" s="8">
+        <v>3</v>
+      </c>
+      <c r="E192" s="8">
+        <v>3</v>
+      </c>
+      <c r="F192" s="8">
+        <v>3</v>
+      </c>
       <c r="G192" s="8"/>
       <c r="H192" s="3"/>
       <c r="I192" s="3"/>
     </row>
     <row r="193" spans="1:9">
       <c r="A193" s="3"/>
-      <c r="B193" s="8"/>
-      <c r="C193" s="8"/>
-      <c r="D193" s="8"/>
-      <c r="E193" s="8"/>
-      <c r="F193" s="8"/>
+      <c r="B193" s="8">
+        <v>192</v>
+      </c>
+      <c r="C193" s="8">
+        <v>15</v>
+      </c>
+      <c r="D193" s="8">
+        <v>4</v>
+      </c>
+      <c r="E193" s="8">
+        <v>3</v>
+      </c>
+      <c r="F193" s="8">
+        <v>3</v>
+      </c>
       <c r="G193" s="8"/>
       <c r="H193" s="3"/>
       <c r="I193" s="3"/>
     </row>
     <row r="194" spans="1:9">
       <c r="A194" s="3"/>
-      <c r="B194" s="8"/>
-      <c r="C194" s="8"/>
-      <c r="D194" s="8"/>
-      <c r="E194" s="8"/>
-      <c r="F194" s="8"/>
+      <c r="B194" s="8">
+        <v>193</v>
+      </c>
+      <c r="C194" s="8">
+        <v>15</v>
+      </c>
+      <c r="D194" s="8">
+        <v>5</v>
+      </c>
+      <c r="E194" s="8">
+        <v>3</v>
+      </c>
+      <c r="F194" s="8">
+        <v>3</v>
+      </c>
       <c r="G194" s="8"/>
       <c r="H194" s="3"/>
       <c r="I194" s="3"/>
     </row>
     <row r="195" spans="1:9">
       <c r="A195" s="3"/>
-      <c r="B195" s="8"/>
-      <c r="C195" s="8"/>
-      <c r="D195" s="8"/>
-      <c r="E195" s="8"/>
-      <c r="F195" s="8"/>
+      <c r="B195" s="8">
+        <v>194</v>
+      </c>
+      <c r="C195" s="8">
+        <v>15</v>
+      </c>
+      <c r="D195" s="8">
+        <v>6</v>
+      </c>
+      <c r="E195" s="8">
+        <v>3</v>
+      </c>
+      <c r="F195" s="8">
+        <v>3</v>
+      </c>
       <c r="G195" s="8"/>
       <c r="H195" s="3"/>
       <c r="I195" s="3"/>
     </row>
     <row r="196" spans="1:9">
       <c r="A196" s="3"/>
-      <c r="B196" s="8"/>
-      <c r="C196" s="8"/>
-      <c r="D196" s="8"/>
-      <c r="E196" s="8"/>
-      <c r="F196" s="8"/>
+      <c r="B196" s="8">
+        <v>195</v>
+      </c>
+      <c r="C196" s="8">
+        <v>15</v>
+      </c>
+      <c r="D196" s="8">
+        <v>7</v>
+      </c>
+      <c r="E196" s="8">
+        <v>3</v>
+      </c>
+      <c r="F196" s="8">
+        <v>3</v>
+      </c>
       <c r="G196" s="8"/>
       <c r="H196" s="3"/>
       <c r="I196" s="3"/>
     </row>
     <row r="197" spans="1:9">
       <c r="A197" s="3"/>
-      <c r="B197" s="8"/>
-      <c r="C197" s="8"/>
-      <c r="D197" s="8"/>
-      <c r="E197" s="8"/>
-      <c r="F197" s="8"/>
+      <c r="B197" s="8">
+        <v>196</v>
+      </c>
+      <c r="C197" s="8">
+        <v>15</v>
+      </c>
+      <c r="D197" s="8">
+        <v>8</v>
+      </c>
+      <c r="E197" s="8">
+        <v>3</v>
+      </c>
+      <c r="F197" s="8">
+        <v>3</v>
+      </c>
       <c r="G197" s="8"/>
       <c r="H197" s="3"/>
       <c r="I197" s="3"/>
     </row>
     <row r="198" spans="1:9">
       <c r="A198" s="3"/>
-      <c r="B198" s="8"/>
-      <c r="C198" s="8"/>
-      <c r="D198" s="8"/>
-      <c r="E198" s="8"/>
-      <c r="F198" s="8"/>
+      <c r="B198" s="8">
+        <v>197</v>
+      </c>
+      <c r="C198" s="8">
+        <v>15</v>
+      </c>
+      <c r="D198" s="8">
+        <v>9</v>
+      </c>
+      <c r="E198" s="8">
+        <v>3</v>
+      </c>
+      <c r="F198" s="8">
+        <v>3</v>
+      </c>
       <c r="G198" s="8"/>
       <c r="H198" s="3"/>
       <c r="I198" s="3"/>
     </row>
     <row r="199" spans="1:9">
       <c r="A199" s="3"/>
-      <c r="B199" s="8"/>
-      <c r="C199" s="8"/>
-      <c r="D199" s="8"/>
-      <c r="E199" s="8"/>
-      <c r="F199" s="8"/>
+      <c r="B199" s="8">
+        <v>198</v>
+      </c>
+      <c r="C199" s="8">
+        <v>15</v>
+      </c>
+      <c r="D199" s="8">
+        <v>10</v>
+      </c>
+      <c r="E199" s="8">
+        <v>3</v>
+      </c>
+      <c r="F199" s="8">
+        <v>3</v>
+      </c>
       <c r="G199" s="8"/>
       <c r="H199" s="3"/>
       <c r="I199" s="3"/>
     </row>
     <row r="200" spans="1:9">
       <c r="A200" s="3"/>
-      <c r="B200" s="8"/>
-      <c r="C200" s="8"/>
-      <c r="D200" s="8"/>
-      <c r="E200" s="8"/>
-      <c r="F200" s="8"/>
+      <c r="B200" s="8">
+        <v>199</v>
+      </c>
+      <c r="C200" s="8">
+        <v>15</v>
+      </c>
+      <c r="D200" s="8">
+        <v>11</v>
+      </c>
+      <c r="E200" s="8">
+        <v>3</v>
+      </c>
+      <c r="F200" s="8">
+        <v>3</v>
+      </c>
       <c r="G200" s="8"/>
       <c r="H200" s="3"/>
       <c r="I200" s="3"/>
     </row>
     <row r="201" spans="1:9">
       <c r="A201" s="3"/>
-      <c r="B201" s="8"/>
-      <c r="C201" s="8"/>
-      <c r="D201" s="8"/>
-      <c r="E201" s="8"/>
-      <c r="F201" s="8"/>
+      <c r="B201" s="8">
+        <v>200</v>
+      </c>
+      <c r="C201" s="8">
+        <v>15</v>
+      </c>
+      <c r="D201" s="8">
+        <v>12</v>
+      </c>
+      <c r="E201" s="8">
+        <v>3</v>
+      </c>
+      <c r="F201" s="8">
+        <v>3</v>
+      </c>
       <c r="G201" s="8"/>
       <c r="H201" s="3"/>
       <c r="I201" s="3"/>
+    </row>
+    <row r="202" spans="1:9">
+      <c r="B202">
+        <v>201</v>
+      </c>
+      <c r="C202">
+        <v>5</v>
+      </c>
+      <c r="D202">
+        <v>1</v>
+      </c>
+      <c r="E202">
+        <v>3</v>
+      </c>
+      <c r="F202">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="203" spans="1:9">
+      <c r="B203">
+        <v>202</v>
+      </c>
+      <c r="C203">
+        <v>5</v>
+      </c>
+      <c r="D203">
+        <v>2</v>
+      </c>
+      <c r="E203">
+        <v>3</v>
+      </c>
+      <c r="F203">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="204" spans="1:9">
+      <c r="B204">
+        <v>203</v>
+      </c>
+      <c r="C204">
+        <v>5</v>
+      </c>
+      <c r="D204">
+        <v>3</v>
+      </c>
+      <c r="E204">
+        <v>3</v>
+      </c>
+      <c r="F204">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="205" spans="1:9">
+      <c r="B205">
+        <v>204</v>
+      </c>
+      <c r="C205">
+        <v>5</v>
+      </c>
+      <c r="D205">
+        <v>4</v>
+      </c>
+      <c r="E205">
+        <v>3</v>
+      </c>
+      <c r="F205">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="206" spans="1:9">
+      <c r="B206">
+        <v>205</v>
+      </c>
+      <c r="C206">
+        <v>5</v>
+      </c>
+      <c r="D206">
+        <v>5</v>
+      </c>
+      <c r="E206">
+        <v>3</v>
+      </c>
+      <c r="F206">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="207" spans="1:9">
+      <c r="B207">
+        <v>206</v>
+      </c>
+      <c r="C207">
+        <v>5</v>
+      </c>
+      <c r="D207">
+        <v>1</v>
+      </c>
+      <c r="E207">
+        <v>3</v>
+      </c>
+      <c r="F207">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="208" spans="1:9">
+      <c r="B208">
+        <v>207</v>
+      </c>
+      <c r="C208">
+        <v>5</v>
+      </c>
+      <c r="D208">
+        <v>2</v>
+      </c>
+      <c r="E208">
+        <v>3</v>
+      </c>
+      <c r="F208">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="209" spans="2:6">
+      <c r="B209">
+        <v>208</v>
+      </c>
+      <c r="C209">
+        <v>5</v>
+      </c>
+      <c r="D209">
+        <v>3</v>
+      </c>
+      <c r="E209">
+        <v>3</v>
+      </c>
+      <c r="F209">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="210" spans="2:6">
+      <c r="B210">
+        <v>209</v>
+      </c>
+      <c r="C210">
+        <v>5</v>
+      </c>
+      <c r="D210">
+        <v>4</v>
+      </c>
+      <c r="E210">
+        <v>3</v>
+      </c>
+      <c r="F210">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="211" spans="2:6">
+      <c r="B211">
+        <v>210</v>
+      </c>
+      <c r="C211">
+        <v>5</v>
+      </c>
+      <c r="D211">
+        <v>1</v>
+      </c>
+      <c r="E211">
+        <v>3</v>
+      </c>
+      <c r="F211">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="212" spans="2:6">
+      <c r="B212">
+        <v>211</v>
+      </c>
+      <c r="C212">
+        <v>5</v>
+      </c>
+      <c r="D212">
+        <v>2</v>
+      </c>
+      <c r="E212">
+        <v>3</v>
+      </c>
+      <c r="F212">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="213" spans="2:6">
+      <c r="B213">
+        <v>212</v>
+      </c>
+      <c r="C213">
+        <v>5</v>
+      </c>
+      <c r="D213">
+        <v>3</v>
+      </c>
+      <c r="E213">
+        <v>3</v>
+      </c>
+      <c r="F213">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="214" spans="2:6">
+      <c r="B214">
+        <v>213</v>
+      </c>
+      <c r="C214">
+        <v>5</v>
+      </c>
+      <c r="D214">
+        <v>4</v>
+      </c>
+      <c r="E214">
+        <v>3</v>
+      </c>
+      <c r="F214">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="215" spans="2:6">
+      <c r="B215">
+        <v>214</v>
+      </c>
+      <c r="C215">
+        <v>5</v>
+      </c>
+      <c r="D215">
+        <v>2</v>
+      </c>
+      <c r="E215">
+        <v>3</v>
+      </c>
+      <c r="F215">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="216" spans="2:6">
+      <c r="B216">
+        <v>215</v>
+      </c>
+      <c r="C216">
+        <v>5</v>
+      </c>
+      <c r="D216">
+        <v>3</v>
+      </c>
+      <c r="E216">
+        <v>3</v>
+      </c>
+      <c r="F216">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="217" spans="2:6">
+      <c r="B217">
+        <v>216</v>
+      </c>
+      <c r="C217">
+        <v>5</v>
+      </c>
+      <c r="D217">
+        <v>4</v>
+      </c>
+      <c r="E217">
+        <v>3</v>
+      </c>
+      <c r="F217">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="218" spans="2:6">
+      <c r="B218">
+        <v>217</v>
+      </c>
+      <c r="C218">
+        <v>5</v>
+      </c>
+      <c r="D218">
+        <v>5</v>
+      </c>
+      <c r="E218">
+        <v>3</v>
+      </c>
+      <c r="F218">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="219" spans="2:6">
+      <c r="B219">
+        <v>218</v>
+      </c>
+      <c r="C219">
+        <v>5</v>
+      </c>
+      <c r="D219">
+        <v>2</v>
+      </c>
+      <c r="E219">
+        <v>3</v>
+      </c>
+      <c r="F219">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="220" spans="2:6">
+      <c r="B220">
+        <v>219</v>
+      </c>
+      <c r="C220">
+        <v>5</v>
+      </c>
+      <c r="D220">
+        <v>3</v>
+      </c>
+      <c r="E220">
+        <v>3</v>
+      </c>
+      <c r="F220">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="221" spans="2:6">
+      <c r="B221">
+        <v>220</v>
+      </c>
+      <c r="C221">
+        <v>5</v>
+      </c>
+      <c r="D221">
+        <v>4</v>
+      </c>
+      <c r="E221">
+        <v>3</v>
+      </c>
+      <c r="F221">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="222" spans="2:6">
+      <c r="B222">
+        <v>221</v>
+      </c>
+      <c r="C222">
+        <v>5</v>
+      </c>
+      <c r="D222">
+        <v>5</v>
+      </c>
+      <c r="E222">
+        <v>3</v>
+      </c>
+      <c r="F222">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="223" spans="2:6">
+      <c r="B223">
+        <v>222</v>
+      </c>
+      <c r="C223">
+        <v>5</v>
+      </c>
+      <c r="D223">
+        <v>1</v>
+      </c>
+      <c r="E223">
+        <v>4</v>
+      </c>
+      <c r="F223">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="224" spans="2:6">
+      <c r="B224">
+        <v>223</v>
+      </c>
+      <c r="C224">
+        <v>5</v>
+      </c>
+      <c r="D224">
+        <v>2</v>
+      </c>
+      <c r="E224">
+        <v>4</v>
+      </c>
+      <c r="F224">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="225" spans="2:6">
+      <c r="B225">
+        <v>224</v>
+      </c>
+      <c r="C225">
+        <v>5</v>
+      </c>
+      <c r="D225">
+        <v>3</v>
+      </c>
+      <c r="E225">
+        <v>4</v>
+      </c>
+      <c r="F225">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="226" spans="2:6">
+      <c r="B226">
+        <v>225</v>
+      </c>
+      <c r="C226">
+        <v>5</v>
+      </c>
+      <c r="D226">
+        <v>4</v>
+      </c>
+      <c r="E226">
+        <v>4</v>
+      </c>
+      <c r="F226">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="227" spans="2:6">
+      <c r="B227">
+        <v>226</v>
+      </c>
+      <c r="C227">
+        <v>5</v>
+      </c>
+      <c r="D227">
+        <v>5</v>
+      </c>
+      <c r="E227">
+        <v>4</v>
+      </c>
+      <c r="F227">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="228" spans="2:6">
+      <c r="B228">
+        <v>227</v>
+      </c>
+      <c r="C228">
+        <v>5</v>
+      </c>
+      <c r="D228">
+        <v>1</v>
+      </c>
+      <c r="E228">
+        <v>4</v>
+      </c>
+      <c r="F228">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="229" spans="2:6">
+      <c r="B229">
+        <v>228</v>
+      </c>
+      <c r="C229">
+        <v>5</v>
+      </c>
+      <c r="D229">
+        <v>2</v>
+      </c>
+      <c r="E229">
+        <v>4</v>
+      </c>
+      <c r="F229">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="230" spans="2:6">
+      <c r="B230">
+        <v>229</v>
+      </c>
+      <c r="C230">
+        <v>5</v>
+      </c>
+      <c r="D230">
+        <v>3</v>
+      </c>
+      <c r="E230">
+        <v>4</v>
+      </c>
+      <c r="F230">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="231" spans="2:6">
+      <c r="B231">
+        <v>230</v>
+      </c>
+      <c r="C231">
+        <v>5</v>
+      </c>
+      <c r="D231">
+        <v>4</v>
+      </c>
+      <c r="E231">
+        <v>4</v>
+      </c>
+      <c r="F231">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="232" spans="2:6">
+      <c r="B232">
+        <v>231</v>
+      </c>
+      <c r="C232">
+        <v>5</v>
+      </c>
+      <c r="D232">
+        <v>5</v>
+      </c>
+      <c r="E232">
+        <v>4</v>
+      </c>
+      <c r="F232">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="233" spans="2:6">
+      <c r="B233">
+        <v>232</v>
+      </c>
+      <c r="C233">
+        <v>5</v>
+      </c>
+      <c r="D233">
+        <v>1</v>
+      </c>
+      <c r="E233">
+        <v>4</v>
+      </c>
+      <c r="F233">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="234" spans="2:6">
+      <c r="B234">
+        <v>233</v>
+      </c>
+      <c r="C234">
+        <v>5</v>
+      </c>
+      <c r="D234">
+        <v>2</v>
+      </c>
+      <c r="E234">
+        <v>4</v>
+      </c>
+      <c r="F234">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="235" spans="2:6">
+      <c r="B235">
+        <v>234</v>
+      </c>
+      <c r="C235">
+        <v>5</v>
+      </c>
+      <c r="D235">
+        <v>3</v>
+      </c>
+      <c r="E235">
+        <v>4</v>
+      </c>
+      <c r="F235">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="236" spans="2:6">
+      <c r="B236">
+        <v>235</v>
+      </c>
+      <c r="C236">
+        <v>5</v>
+      </c>
+      <c r="D236">
+        <v>4</v>
+      </c>
+      <c r="E236">
+        <v>4</v>
+      </c>
+      <c r="F236">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="237" spans="2:6">
+      <c r="B237">
+        <v>236</v>
+      </c>
+      <c r="C237">
+        <v>5</v>
+      </c>
+      <c r="D237">
+        <v>5</v>
+      </c>
+      <c r="E237">
+        <v>4</v>
+      </c>
+      <c r="F237">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="238" spans="2:6">
+      <c r="B238">
+        <v>237</v>
+      </c>
+      <c r="C238">
+        <v>5</v>
+      </c>
+      <c r="D238">
+        <v>6</v>
+      </c>
+      <c r="E238">
+        <v>4</v>
+      </c>
+      <c r="F238">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="239" spans="2:6">
+      <c r="B239">
+        <v>238</v>
+      </c>
+      <c r="C239">
+        <v>5</v>
+      </c>
+      <c r="D239">
+        <v>1</v>
+      </c>
+      <c r="E239">
+        <v>4</v>
+      </c>
+      <c r="F239">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="240" spans="2:6">
+      <c r="B240">
+        <v>239</v>
+      </c>
+      <c r="C240">
+        <v>5</v>
+      </c>
+      <c r="D240">
+        <v>2</v>
+      </c>
+      <c r="E240">
+        <v>4</v>
+      </c>
+      <c r="F240">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="241" spans="2:6">
+      <c r="B241">
+        <v>240</v>
+      </c>
+      <c r="C241">
+        <v>5</v>
+      </c>
+      <c r="D241">
+        <v>3</v>
+      </c>
+      <c r="E241">
+        <v>4</v>
+      </c>
+      <c r="F241">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="242" spans="2:6">
+      <c r="B242">
+        <v>241</v>
+      </c>
+      <c r="C242">
+        <v>5</v>
+      </c>
+      <c r="D242">
+        <v>4</v>
+      </c>
+      <c r="E242">
+        <v>4</v>
+      </c>
+      <c r="F242">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="243" spans="2:6">
+      <c r="B243">
+        <v>242</v>
+      </c>
+      <c r="C243">
+        <v>5</v>
+      </c>
+      <c r="D243">
+        <v>5</v>
+      </c>
+      <c r="E243">
+        <v>4</v>
+      </c>
+      <c r="F243">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="244" spans="2:6">
+      <c r="B244">
+        <v>243</v>
+      </c>
+      <c r="C244">
+        <v>5</v>
+      </c>
+      <c r="D244">
+        <v>6</v>
+      </c>
+      <c r="E244">
+        <v>4</v>
+      </c>
+      <c r="F244">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="245" spans="2:6">
+      <c r="B245">
+        <v>244</v>
+      </c>
+      <c r="C245">
+        <v>5</v>
+      </c>
+      <c r="D245">
+        <v>1</v>
+      </c>
+      <c r="E245">
+        <v>4</v>
+      </c>
+      <c r="F245">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="246" spans="2:6">
+      <c r="B246">
+        <v>245</v>
+      </c>
+      <c r="C246">
+        <v>5</v>
+      </c>
+      <c r="D246">
+        <v>2</v>
+      </c>
+      <c r="E246">
+        <v>4</v>
+      </c>
+      <c r="F246">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="247" spans="2:6">
+      <c r="B247">
+        <v>246</v>
+      </c>
+      <c r="C247">
+        <v>5</v>
+      </c>
+      <c r="D247">
+        <v>3</v>
+      </c>
+      <c r="E247">
+        <v>4</v>
+      </c>
+      <c r="F247">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="248" spans="2:6">
+      <c r="B248">
+        <v>247</v>
+      </c>
+      <c r="C248">
+        <v>5</v>
+      </c>
+      <c r="D248">
+        <v>4</v>
+      </c>
+      <c r="E248">
+        <v>4</v>
+      </c>
+      <c r="F248">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="249" spans="2:6">
+      <c r="B249">
+        <v>248</v>
+      </c>
+      <c r="C249">
+        <v>5</v>
+      </c>
+      <c r="D249">
+        <v>4</v>
+      </c>
+      <c r="E249">
+        <v>4</v>
+      </c>
+      <c r="F249">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="250" spans="2:6">
+      <c r="B250">
+        <v>249</v>
+      </c>
+      <c r="C250">
+        <v>5</v>
+      </c>
+      <c r="D250">
+        <v>5</v>
+      </c>
+      <c r="E250">
+        <v>4</v>
+      </c>
+      <c r="F250">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="251" spans="2:6">
+      <c r="B251">
+        <v>250</v>
+      </c>
+      <c r="C251">
+        <v>5</v>
+      </c>
+      <c r="D251">
+        <v>6</v>
+      </c>
+      <c r="E251">
+        <v>4</v>
+      </c>
+      <c r="F251">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="252" spans="2:6">
+      <c r="B252">
+        <v>251</v>
+      </c>
+      <c r="C252">
+        <v>5</v>
+      </c>
+      <c r="D252">
+        <v>1</v>
+      </c>
+      <c r="E252">
+        <v>4</v>
+      </c>
+      <c r="F252">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="253" spans="2:6">
+      <c r="B253">
+        <v>252</v>
+      </c>
+      <c r="C253">
+        <v>5</v>
+      </c>
+      <c r="D253">
+        <v>2</v>
+      </c>
+      <c r="E253">
+        <v>4</v>
+      </c>
+      <c r="F253">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="254" spans="2:6">
+      <c r="B254">
+        <v>253</v>
+      </c>
+      <c r="C254">
+        <v>5</v>
+      </c>
+      <c r="D254">
+        <v>3</v>
+      </c>
+      <c r="E254">
+        <v>4</v>
+      </c>
+      <c r="F254">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="255" spans="2:6">
+      <c r="B255">
+        <v>254</v>
+      </c>
+      <c r="C255">
+        <v>5</v>
+      </c>
+      <c r="D255">
+        <v>4</v>
+      </c>
+      <c r="E255">
+        <v>4</v>
+      </c>
+      <c r="F255">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="256" spans="2:6">
+      <c r="B256">
+        <v>255</v>
+      </c>
+      <c r="C256">
+        <v>5</v>
+      </c>
+      <c r="D256">
+        <v>5</v>
+      </c>
+      <c r="E256">
+        <v>4</v>
+      </c>
+      <c r="F256">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="257" spans="2:9">
+      <c r="B257">
+        <v>256</v>
+      </c>
+      <c r="C257">
+        <v>5</v>
+      </c>
+      <c r="D257">
+        <v>6</v>
+      </c>
+      <c r="E257">
+        <v>4</v>
+      </c>
+      <c r="F257">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="258" spans="2:9">
+      <c r="B258">
+        <v>257</v>
+      </c>
+      <c r="C258">
+        <v>5</v>
+      </c>
+      <c r="D258">
+        <v>1</v>
+      </c>
+      <c r="E258">
+        <v>4</v>
+      </c>
+      <c r="F258">
+        <v>3</v>
+      </c>
+      <c r="I258" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="259" spans="2:9">
+      <c r="B259">
+        <v>258</v>
+      </c>
+      <c r="C259">
+        <v>10</v>
+      </c>
+      <c r="D259">
+        <v>2</v>
+      </c>
+      <c r="E259">
+        <v>4</v>
+      </c>
+      <c r="F259">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="260" spans="2:9">
+      <c r="B260">
+        <v>259</v>
+      </c>
+      <c r="C260">
+        <v>10</v>
+      </c>
+      <c r="D260">
+        <v>3</v>
+      </c>
+      <c r="E260">
+        <v>4</v>
+      </c>
+      <c r="F260">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="261" spans="2:9">
+      <c r="B261">
+        <v>260</v>
+      </c>
+      <c r="C261">
+        <v>10</v>
+      </c>
+      <c r="D261">
+        <v>4</v>
+      </c>
+      <c r="E261">
+        <v>4</v>
+      </c>
+      <c r="F261">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="262" spans="2:9">
+      <c r="B262">
+        <v>261</v>
+      </c>
+      <c r="C262">
+        <v>10</v>
+      </c>
+      <c r="D262">
+        <v>4</v>
+      </c>
+      <c r="E262">
+        <v>4</v>
+      </c>
+      <c r="F262">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="263" spans="2:9">
+      <c r="B263">
+        <v>262</v>
+      </c>
+      <c r="C263">
+        <v>10</v>
+      </c>
+      <c r="D263">
+        <v>5</v>
+      </c>
+      <c r="E263">
+        <v>4</v>
+      </c>
+      <c r="F263">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="264" spans="2:9">
+      <c r="B264">
+        <v>263</v>
+      </c>
+      <c r="C264">
+        <v>10</v>
+      </c>
+      <c r="D264">
+        <v>6</v>
+      </c>
+      <c r="E264">
+        <v>4</v>
+      </c>
+      <c r="F264">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="265" spans="2:9">
+      <c r="B265">
+        <v>264</v>
+      </c>
+      <c r="C265">
+        <v>10</v>
+      </c>
+      <c r="D265">
+        <v>7</v>
+      </c>
+      <c r="E265">
+        <v>4</v>
+      </c>
+      <c r="F265">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="266" spans="2:9">
+      <c r="B266">
+        <v>265</v>
+      </c>
+      <c r="C266">
+        <v>10</v>
+      </c>
+      <c r="D266">
+        <v>7</v>
+      </c>
+      <c r="E266">
+        <v>4</v>
+      </c>
+      <c r="F266">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="267" spans="2:9">
+      <c r="B267">
+        <v>266</v>
+      </c>
+      <c r="C267">
+        <v>10</v>
+      </c>
+      <c r="D267">
+        <v>8</v>
+      </c>
+      <c r="E267">
+        <v>4</v>
+      </c>
+      <c r="F267">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="268" spans="2:9">
+      <c r="B268">
+        <v>267</v>
+      </c>
+      <c r="C268">
+        <v>10</v>
+      </c>
+      <c r="D268">
+        <v>1</v>
+      </c>
+      <c r="E268">
+        <v>4</v>
+      </c>
+      <c r="F268">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="269" spans="2:9">
+      <c r="B269">
+        <v>268</v>
+      </c>
+      <c r="C269">
+        <v>10</v>
+      </c>
+      <c r="D269">
+        <v>2</v>
+      </c>
+      <c r="E269">
+        <v>4</v>
+      </c>
+      <c r="F269">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="270" spans="2:9">
+      <c r="B270">
+        <v>269</v>
+      </c>
+      <c r="C270">
+        <v>10</v>
+      </c>
+      <c r="D270">
+        <v>3</v>
+      </c>
+      <c r="E270">
+        <v>4</v>
+      </c>
+      <c r="F270">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="271" spans="2:9">
+      <c r="B271">
+        <v>270</v>
+      </c>
+      <c r="C271">
+        <v>10</v>
+      </c>
+      <c r="D271">
+        <v>4</v>
+      </c>
+      <c r="E271">
+        <v>4</v>
+      </c>
+      <c r="F271">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="272" spans="2:9">
+      <c r="B272">
+        <v>271</v>
+      </c>
+      <c r="C272">
+        <v>10</v>
+      </c>
+      <c r="D272">
+        <v>5</v>
+      </c>
+      <c r="E272">
+        <v>4</v>
+      </c>
+      <c r="F272">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="273" spans="2:6">
+      <c r="B273">
+        <v>272</v>
+      </c>
+      <c r="C273">
+        <v>10</v>
+      </c>
+      <c r="D273">
+        <v>6</v>
+      </c>
+      <c r="E273">
+        <v>4</v>
+      </c>
+      <c r="F273">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="274" spans="2:6">
+      <c r="B274">
+        <v>273</v>
+      </c>
+      <c r="C274">
+        <v>10</v>
+      </c>
+      <c r="D274">
+        <v>7</v>
+      </c>
+      <c r="E274">
+        <v>4</v>
+      </c>
+      <c r="F274">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="275" spans="2:6">
+      <c r="B275">
+        <v>274</v>
+      </c>
+      <c r="C275">
+        <v>10</v>
+      </c>
+      <c r="D275">
+        <v>8</v>
+      </c>
+      <c r="E275">
+        <v>4</v>
+      </c>
+      <c r="F275">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="276" spans="2:6">
+      <c r="B276">
+        <v>275</v>
+      </c>
+      <c r="C276">
+        <v>10</v>
+      </c>
+      <c r="D276">
+        <v>1</v>
+      </c>
+      <c r="E276">
+        <v>4</v>
+      </c>
+      <c r="F276">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="277" spans="2:6">
+      <c r="B277">
+        <v>276</v>
+      </c>
+      <c r="C277">
+        <v>10</v>
+      </c>
+      <c r="D277">
+        <v>2</v>
+      </c>
+      <c r="E277">
+        <v>4</v>
+      </c>
+      <c r="F277">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="278" spans="2:6">
+      <c r="B278">
+        <v>277</v>
+      </c>
+      <c r="C278">
+        <v>10</v>
+      </c>
+      <c r="D278">
+        <v>3</v>
+      </c>
+      <c r="E278">
+        <v>4</v>
+      </c>
+      <c r="F278">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="279" spans="2:6">
+      <c r="B279">
+        <v>278</v>
+      </c>
+      <c r="C279">
+        <v>10</v>
+      </c>
+      <c r="D279">
+        <v>4</v>
+      </c>
+      <c r="E279">
+        <v>4</v>
+      </c>
+      <c r="F279">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="280" spans="2:6">
+      <c r="B280">
+        <v>279</v>
+      </c>
+      <c r="C280">
+        <v>10</v>
+      </c>
+      <c r="D280">
+        <v>5</v>
+      </c>
+      <c r="E280">
+        <v>4</v>
+      </c>
+      <c r="F280">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="281" spans="2:6">
+      <c r="B281">
+        <v>280</v>
+      </c>
+      <c r="C281">
+        <v>10</v>
+      </c>
+      <c r="D281">
+        <v>6</v>
+      </c>
+      <c r="E281">
+        <v>4</v>
+      </c>
+      <c r="F281">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="282" spans="2:6">
+      <c r="B282">
+        <v>281</v>
+      </c>
+      <c r="C282">
+        <v>10</v>
+      </c>
+      <c r="D282">
+        <v>7</v>
+      </c>
+      <c r="E282">
+        <v>4</v>
+      </c>
+      <c r="F282">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="283" spans="2:6">
+      <c r="B283">
+        <v>282</v>
+      </c>
+      <c r="C283">
+        <v>10</v>
+      </c>
+      <c r="D283">
+        <v>8</v>
+      </c>
+      <c r="E283">
+        <v>4</v>
+      </c>
+      <c r="F283">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="284" spans="2:6">
+      <c r="B284">
+        <v>283</v>
+      </c>
+      <c r="C284">
+        <v>10</v>
+      </c>
+      <c r="D284">
+        <v>9</v>
+      </c>
+      <c r="E284">
+        <v>4</v>
+      </c>
+      <c r="F284">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="285" spans="2:6">
+      <c r="B285">
+        <v>284</v>
+      </c>
+      <c r="C285">
+        <v>10</v>
+      </c>
+      <c r="D285">
+        <v>10</v>
+      </c>
+      <c r="E285">
+        <v>4</v>
+      </c>
+      <c r="F285">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="286" spans="2:6">
+      <c r="B286">
+        <v>285</v>
+      </c>
+      <c r="C286">
+        <v>10</v>
+      </c>
+      <c r="D286">
+        <v>11</v>
+      </c>
+      <c r="E286">
+        <v>4</v>
+      </c>
+      <c r="F286">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="287" spans="2:6">
+      <c r="B287">
+        <v>286</v>
+      </c>
+      <c r="C287">
+        <v>10</v>
+      </c>
+      <c r="D287">
+        <v>12</v>
+      </c>
+      <c r="E287">
+        <v>4</v>
+      </c>
+      <c r="F287">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="288" spans="2:6">
+      <c r="B288">
+        <v>287</v>
+      </c>
+      <c r="C288">
+        <v>10</v>
+      </c>
+      <c r="D288">
+        <v>1</v>
+      </c>
+      <c r="E288">
+        <v>4</v>
+      </c>
+      <c r="F288">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="289" spans="2:6">
+      <c r="B289">
+        <v>288</v>
+      </c>
+      <c r="C289">
+        <v>10</v>
+      </c>
+      <c r="D289">
+        <v>2</v>
+      </c>
+      <c r="E289">
+        <v>4</v>
+      </c>
+      <c r="F289">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="290" spans="2:6">
+      <c r="B290">
+        <v>289</v>
+      </c>
+      <c r="C290">
+        <v>10</v>
+      </c>
+      <c r="D290">
+        <v>3</v>
+      </c>
+      <c r="E290">
+        <v>4</v>
+      </c>
+      <c r="F290">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="291" spans="2:6">
+      <c r="B291">
+        <v>290</v>
+      </c>
+      <c r="C291">
+        <v>10</v>
+      </c>
+      <c r="D291">
+        <v>4</v>
+      </c>
+      <c r="E291">
+        <v>4</v>
+      </c>
+      <c r="F291">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="292" spans="2:6">
+      <c r="B292">
+        <v>291</v>
+      </c>
+      <c r="C292">
+        <v>10</v>
+      </c>
+      <c r="D292">
+        <v>5</v>
+      </c>
+      <c r="E292">
+        <v>4</v>
+      </c>
+      <c r="F292">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="293" spans="2:6">
+      <c r="B293">
+        <v>292</v>
+      </c>
+      <c r="C293">
+        <v>10</v>
+      </c>
+      <c r="D293">
+        <v>6</v>
+      </c>
+      <c r="E293">
+        <v>4</v>
+      </c>
+      <c r="F293">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="294" spans="2:6">
+      <c r="B294">
+        <v>293</v>
+      </c>
+      <c r="C294">
+        <v>10</v>
+      </c>
+      <c r="D294">
+        <v>7</v>
+      </c>
+      <c r="E294">
+        <v>4</v>
+      </c>
+      <c r="F294">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="295" spans="2:6">
+      <c r="B295">
+        <v>294</v>
+      </c>
+      <c r="C295">
+        <v>10</v>
+      </c>
+      <c r="D295">
+        <v>8</v>
+      </c>
+      <c r="E295">
+        <v>4</v>
+      </c>
+      <c r="F295">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="296" spans="2:6">
+      <c r="B296">
+        <v>295</v>
+      </c>
+      <c r="C296">
+        <v>10</v>
+      </c>
+      <c r="D296">
+        <v>9</v>
+      </c>
+      <c r="E296">
+        <v>4</v>
+      </c>
+      <c r="F296">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="297" spans="2:6">
+      <c r="B297">
+        <v>296</v>
+      </c>
+      <c r="C297">
+        <v>10</v>
+      </c>
+      <c r="D297">
+        <v>10</v>
+      </c>
+      <c r="E297">
+        <v>4</v>
+      </c>
+      <c r="F297">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="298" spans="2:6">
+      <c r="B298">
+        <v>297</v>
+      </c>
+      <c r="C298">
+        <v>10</v>
+      </c>
+      <c r="D298">
+        <v>11</v>
+      </c>
+      <c r="E298">
+        <v>4</v>
+      </c>
+      <c r="F298">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="299" spans="2:6">
+      <c r="B299">
+        <v>298</v>
+      </c>
+      <c r="C299">
+        <v>10</v>
+      </c>
+      <c r="D299">
+        <v>12</v>
+      </c>
+      <c r="E299">
+        <v>4</v>
+      </c>
+      <c r="F299">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="300" spans="2:6">
+      <c r="B300">
+        <v>299</v>
+      </c>
+      <c r="C300">
+        <v>10</v>
+      </c>
+      <c r="D300">
+        <v>3</v>
+      </c>
+      <c r="E300">
+        <v>4</v>
+      </c>
+      <c r="F300">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="301" spans="2:6">
+      <c r="B301">
+        <v>300</v>
+      </c>
+      <c r="C301">
+        <v>10</v>
+      </c>
+      <c r="D301">
+        <v>4</v>
+      </c>
+      <c r="E301">
+        <v>4</v>
+      </c>
+      <c r="F301">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="302" spans="2:6">
+      <c r="B302">
+        <v>301</v>
+      </c>
+      <c r="C302">
+        <v>10</v>
+      </c>
+      <c r="D302">
+        <v>5</v>
+      </c>
+      <c r="E302">
+        <v>4</v>
+      </c>
+      <c r="F302">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="303" spans="2:6">
+      <c r="B303">
+        <v>302</v>
+      </c>
+      <c r="C303">
+        <v>10</v>
+      </c>
+      <c r="D303">
+        <v>6</v>
+      </c>
+      <c r="E303">
+        <v>4</v>
+      </c>
+      <c r="F303">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="304" spans="2:6">
+      <c r="B304">
+        <v>303</v>
+      </c>
+      <c r="C304">
+        <v>10</v>
+      </c>
+      <c r="D304">
+        <v>7</v>
+      </c>
+      <c r="E304">
+        <v>4</v>
+      </c>
+      <c r="F304">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="305" spans="2:6">
+      <c r="B305">
+        <v>304</v>
+      </c>
+      <c r="C305">
+        <v>10</v>
+      </c>
+      <c r="D305">
+        <v>8</v>
+      </c>
+      <c r="E305">
+        <v>4</v>
+      </c>
+      <c r="F305">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="306" spans="2:6">
+      <c r="B306">
+        <v>305</v>
+      </c>
+      <c r="C306">
+        <v>10</v>
+      </c>
+      <c r="D306">
+        <v>9</v>
+      </c>
+      <c r="E306">
+        <v>4</v>
+      </c>
+      <c r="F306">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="307" spans="2:6">
+      <c r="B307">
+        <v>306</v>
+      </c>
+      <c r="C307">
+        <v>10</v>
+      </c>
+      <c r="D307">
+        <v>10</v>
+      </c>
+      <c r="E307">
+        <v>4</v>
+      </c>
+      <c r="F307">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="308" spans="2:6">
+      <c r="B308">
+        <v>307</v>
+      </c>
+      <c r="C308">
+        <v>10</v>
+      </c>
+      <c r="D308">
+        <v>11</v>
+      </c>
+      <c r="E308">
+        <v>4</v>
+      </c>
+      <c r="F308">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="309" spans="2:6">
+      <c r="B309">
+        <v>308</v>
+      </c>
+      <c r="C309">
+        <v>10</v>
+      </c>
+      <c r="D309">
+        <v>12</v>
+      </c>
+      <c r="E309">
+        <v>4</v>
+      </c>
+      <c r="F309">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="310" spans="2:6">
+      <c r="B310">
+        <v>309</v>
+      </c>
+      <c r="C310">
+        <v>15</v>
+      </c>
+      <c r="D310">
+        <v>3</v>
+      </c>
+      <c r="E310">
+        <v>4</v>
+      </c>
+      <c r="F310">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="311" spans="2:6">
+      <c r="B311">
+        <v>310</v>
+      </c>
+      <c r="C311">
+        <v>15</v>
+      </c>
+      <c r="D311">
+        <v>4</v>
+      </c>
+      <c r="E311">
+        <v>4</v>
+      </c>
+      <c r="F311">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="312" spans="2:6">
+      <c r="B312">
+        <v>311</v>
+      </c>
+      <c r="C312">
+        <v>15</v>
+      </c>
+      <c r="D312">
+        <v>5</v>
+      </c>
+      <c r="E312">
+        <v>4</v>
+      </c>
+      <c r="F312">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="313" spans="2:6">
+      <c r="B313">
+        <v>312</v>
+      </c>
+      <c r="C313">
+        <v>15</v>
+      </c>
+      <c r="D313">
+        <v>6</v>
+      </c>
+      <c r="E313">
+        <v>4</v>
+      </c>
+      <c r="F313">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="314" spans="2:6">
+      <c r="B314">
+        <v>313</v>
+      </c>
+      <c r="C314">
+        <v>15</v>
+      </c>
+      <c r="D314">
+        <v>7</v>
+      </c>
+      <c r="E314">
+        <v>4</v>
+      </c>
+      <c r="F314">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="315" spans="2:6">
+      <c r="B315">
+        <v>314</v>
+      </c>
+      <c r="C315">
+        <v>15</v>
+      </c>
+      <c r="D315">
+        <v>1</v>
+      </c>
+      <c r="E315">
+        <v>4</v>
+      </c>
+      <c r="F315">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="316" spans="2:6">
+      <c r="B316">
+        <v>315</v>
+      </c>
+      <c r="C316">
+        <v>15</v>
+      </c>
+      <c r="D316">
+        <v>2</v>
+      </c>
+      <c r="E316">
+        <v>4</v>
+      </c>
+      <c r="F316">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="317" spans="2:6">
+      <c r="B317">
+        <v>316</v>
+      </c>
+      <c r="C317">
+        <v>15</v>
+      </c>
+      <c r="D317">
+        <v>1</v>
+      </c>
+      <c r="E317">
+        <v>4</v>
+      </c>
+      <c r="F317">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="318" spans="2:6">
+      <c r="B318">
+        <v>317</v>
+      </c>
+      <c r="C318">
+        <v>15</v>
+      </c>
+      <c r="D318">
+        <v>2</v>
+      </c>
+      <c r="E318">
+        <v>4</v>
+      </c>
+      <c r="F318">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="319" spans="2:6">
+      <c r="B319">
+        <v>318</v>
+      </c>
+      <c r="C319">
+        <v>15</v>
+      </c>
+      <c r="D319">
+        <v>3</v>
+      </c>
+      <c r="E319">
+        <v>4</v>
+      </c>
+      <c r="F319">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="320" spans="2:6">
+      <c r="B320">
+        <v>319</v>
+      </c>
+      <c r="C320">
+        <v>15</v>
+      </c>
+      <c r="D320">
+        <v>4</v>
+      </c>
+      <c r="E320">
+        <v>4</v>
+      </c>
+      <c r="F320">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="321" spans="2:6">
+      <c r="B321">
+        <v>320</v>
+      </c>
+      <c r="C321">
+        <v>15</v>
+      </c>
+      <c r="D321">
+        <v>5</v>
+      </c>
+      <c r="E321">
+        <v>4</v>
+      </c>
+      <c r="F321">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="322" spans="2:6">
+      <c r="B322">
+        <v>321</v>
+      </c>
+      <c r="C322">
+        <v>15</v>
+      </c>
+      <c r="D322">
+        <v>6</v>
+      </c>
+      <c r="E322">
+        <v>4</v>
+      </c>
+      <c r="F322">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="323" spans="2:6">
+      <c r="B323">
+        <v>322</v>
+      </c>
+      <c r="C323">
+        <v>15</v>
+      </c>
+      <c r="D323">
+        <v>7</v>
+      </c>
+      <c r="E323">
+        <v>4</v>
+      </c>
+      <c r="F323">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="324" spans="2:6">
+      <c r="B324">
+        <v>323</v>
+      </c>
+      <c r="C324">
+        <v>15</v>
+      </c>
+      <c r="D324">
+        <v>8</v>
+      </c>
+      <c r="E324">
+        <v>4</v>
+      </c>
+      <c r="F324">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="325" spans="2:6">
+      <c r="B325">
+        <v>324</v>
+      </c>
+      <c r="C325">
+        <v>15</v>
+      </c>
+      <c r="D325">
+        <v>9</v>
+      </c>
+      <c r="E325">
+        <v>4</v>
+      </c>
+      <c r="F325">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="326" spans="2:6">
+      <c r="B326">
+        <v>325</v>
+      </c>
+      <c r="C326">
+        <v>15</v>
+      </c>
+      <c r="D326">
+        <v>10</v>
+      </c>
+      <c r="E326">
+        <v>4</v>
+      </c>
+      <c r="F326">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="327" spans="2:6">
+      <c r="B327">
+        <v>326</v>
+      </c>
+      <c r="C327">
+        <v>15</v>
+      </c>
+      <c r="D327">
+        <v>11</v>
+      </c>
+      <c r="E327">
+        <v>4</v>
+      </c>
+      <c r="F327">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="328" spans="2:6">
+      <c r="B328">
+        <v>327</v>
+      </c>
+      <c r="C328">
+        <v>15</v>
+      </c>
+      <c r="D328">
+        <v>12</v>
+      </c>
+      <c r="E328">
+        <v>4</v>
+      </c>
+      <c r="F328">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="329" spans="2:6">
+      <c r="B329">
+        <v>328</v>
+      </c>
+      <c r="C329">
+        <v>15</v>
+      </c>
+      <c r="D329">
+        <v>13</v>
+      </c>
+      <c r="E329">
+        <v>4</v>
+      </c>
+      <c r="F329">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="330" spans="2:6">
+      <c r="B330">
+        <v>329</v>
+      </c>
+      <c r="C330">
+        <v>15</v>
+      </c>
+      <c r="D330">
+        <v>14</v>
+      </c>
+      <c r="E330">
+        <v>4</v>
+      </c>
+      <c r="F330">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="331" spans="2:6">
+      <c r="B331">
+        <v>330</v>
+      </c>
+      <c r="C331">
+        <v>15</v>
+      </c>
+      <c r="D331">
+        <v>15</v>
+      </c>
+      <c r="E331">
+        <v>4</v>
+      </c>
+      <c r="F331">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="332" spans="2:6">
+      <c r="B332">
+        <v>331</v>
+      </c>
+      <c r="C332">
+        <v>15</v>
+      </c>
+      <c r="D332">
+        <v>1</v>
+      </c>
+      <c r="E332">
+        <v>4</v>
+      </c>
+      <c r="F332">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="333" spans="2:6">
+      <c r="B333">
+        <v>332</v>
+      </c>
+      <c r="C333">
+        <v>15</v>
+      </c>
+      <c r="D333">
+        <v>2</v>
+      </c>
+      <c r="E333">
+        <v>4</v>
+      </c>
+      <c r="F333">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="334" spans="2:6">
+      <c r="B334">
+        <v>333</v>
+      </c>
+      <c r="C334">
+        <v>15</v>
+      </c>
+      <c r="D334">
+        <v>3</v>
+      </c>
+      <c r="E334">
+        <v>4</v>
+      </c>
+      <c r="F334">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="335" spans="2:6">
+      <c r="B335">
+        <v>334</v>
+      </c>
+      <c r="C335">
+        <v>15</v>
+      </c>
+      <c r="D335">
+        <v>4</v>
+      </c>
+      <c r="E335">
+        <v>4</v>
+      </c>
+      <c r="F335">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="336" spans="2:6">
+      <c r="B336">
+        <v>335</v>
+      </c>
+      <c r="C336">
+        <v>15</v>
+      </c>
+      <c r="D336">
+        <v>5</v>
+      </c>
+      <c r="E336">
+        <v>4</v>
+      </c>
+      <c r="F336">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="337" spans="2:6">
+      <c r="B337">
+        <v>336</v>
+      </c>
+      <c r="C337">
+        <v>15</v>
+      </c>
+      <c r="D337">
+        <v>6</v>
+      </c>
+      <c r="E337">
+        <v>4</v>
+      </c>
+      <c r="F337">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="338" spans="2:6">
+      <c r="B338">
+        <v>337</v>
+      </c>
+      <c r="C338">
+        <v>15</v>
+      </c>
+      <c r="D338">
+        <v>7</v>
+      </c>
+      <c r="E338">
+        <v>4</v>
+      </c>
+      <c r="F338">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="339" spans="2:6">
+      <c r="B339">
+        <v>338</v>
+      </c>
+      <c r="C339">
+        <v>15</v>
+      </c>
+      <c r="D339">
+        <v>8</v>
+      </c>
+      <c r="E339">
+        <v>4</v>
+      </c>
+      <c r="F339">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="340" spans="2:6">
+      <c r="B340">
+        <v>339</v>
+      </c>
+      <c r="C340">
+        <v>15</v>
+      </c>
+      <c r="D340">
+        <v>9</v>
+      </c>
+      <c r="E340">
+        <v>4</v>
+      </c>
+      <c r="F340">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="341" spans="2:6">
+      <c r="B341">
+        <v>340</v>
+      </c>
+      <c r="C341">
+        <v>15</v>
+      </c>
+      <c r="D341">
+        <v>10</v>
+      </c>
+      <c r="E341">
+        <v>4</v>
+      </c>
+      <c r="F341">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="342" spans="2:6">
+      <c r="B342">
+        <v>341</v>
+      </c>
+      <c r="C342">
+        <v>15</v>
+      </c>
+      <c r="D342">
+        <v>11</v>
+      </c>
+      <c r="E342">
+        <v>4</v>
+      </c>
+      <c r="F342">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="343" spans="2:6">
+      <c r="B343">
+        <v>342</v>
+      </c>
+      <c r="C343">
+        <v>15</v>
+      </c>
+      <c r="D343">
+        <v>12</v>
+      </c>
+      <c r="E343">
+        <v>4</v>
+      </c>
+      <c r="F343">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="344" spans="2:6">
+      <c r="B344">
+        <v>343</v>
+      </c>
+      <c r="C344">
+        <v>15</v>
+      </c>
+      <c r="D344">
+        <v>13</v>
+      </c>
+      <c r="E344">
+        <v>4</v>
+      </c>
+      <c r="F344">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="345" spans="2:6">
+      <c r="B345">
+        <v>344</v>
+      </c>
+      <c r="C345">
+        <v>15</v>
+      </c>
+      <c r="D345">
+        <v>14</v>
+      </c>
+      <c r="E345">
+        <v>4</v>
+      </c>
+      <c r="F345">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="346" spans="2:6">
+      <c r="B346">
+        <v>345</v>
+      </c>
+      <c r="C346">
+        <v>15</v>
+      </c>
+      <c r="D346">
+        <v>15</v>
+      </c>
+      <c r="E346">
+        <v>4</v>
+      </c>
+      <c r="F346">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="347" spans="2:6">
+      <c r="B347">
+        <v>346</v>
+      </c>
+      <c r="C347">
+        <v>15</v>
+      </c>
+      <c r="D347">
+        <v>1</v>
+      </c>
+      <c r="E347">
+        <v>4</v>
+      </c>
+      <c r="F347">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="348" spans="2:6">
+      <c r="B348">
+        <v>347</v>
+      </c>
+      <c r="C348">
+        <v>15</v>
+      </c>
+      <c r="D348">
+        <v>3</v>
+      </c>
+      <c r="E348">
+        <v>4</v>
+      </c>
+      <c r="F348">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="349" spans="2:6">
+      <c r="B349">
+        <v>348</v>
+      </c>
+      <c r="C349">
+        <v>15</v>
+      </c>
+      <c r="D349">
+        <v>4</v>
+      </c>
+      <c r="E349">
+        <v>4</v>
+      </c>
+      <c r="F349">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="350" spans="2:6">
+      <c r="B350">
+        <v>349</v>
+      </c>
+      <c r="C350">
+        <v>15</v>
+      </c>
+      <c r="D350">
+        <v>5</v>
+      </c>
+      <c r="E350">
+        <v>4</v>
+      </c>
+      <c r="F350">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="351" spans="2:6">
+      <c r="B351">
+        <v>350</v>
+      </c>
+      <c r="C351">
+        <v>15</v>
+      </c>
+      <c r="D351">
+        <v>6</v>
+      </c>
+      <c r="E351">
+        <v>4</v>
+      </c>
+      <c r="F351">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="352" spans="2:6">
+      <c r="B352">
+        <v>351</v>
+      </c>
+      <c r="C352">
+        <v>15</v>
+      </c>
+      <c r="D352">
+        <v>7</v>
+      </c>
+      <c r="E352">
+        <v>4</v>
+      </c>
+      <c r="F352">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="353" spans="2:6">
+      <c r="B353">
+        <v>352</v>
+      </c>
+      <c r="C353">
+        <v>15</v>
+      </c>
+      <c r="D353">
+        <v>8</v>
+      </c>
+      <c r="E353">
+        <v>4</v>
+      </c>
+      <c r="F353">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="354" spans="2:6">
+      <c r="B354">
+        <v>353</v>
+      </c>
+      <c r="C354">
+        <v>15</v>
+      </c>
+      <c r="D354">
+        <v>9</v>
+      </c>
+      <c r="E354">
+        <v>4</v>
+      </c>
+      <c r="F354">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="355" spans="2:6">
+      <c r="B355">
+        <v>354</v>
+      </c>
+      <c r="C355">
+        <v>15</v>
+      </c>
+      <c r="D355">
+        <v>10</v>
+      </c>
+      <c r="E355">
+        <v>4</v>
+      </c>
+      <c r="F355">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="356" spans="2:6">
+      <c r="B356">
+        <v>355</v>
+      </c>
+      <c r="C356">
+        <v>15</v>
+      </c>
+      <c r="D356">
+        <v>11</v>
+      </c>
+      <c r="E356">
+        <v>4</v>
+      </c>
+      <c r="F356">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="357" spans="2:6">
+      <c r="B357">
+        <v>356</v>
+      </c>
+      <c r="C357">
+        <v>15</v>
+      </c>
+      <c r="D357">
+        <v>12</v>
+      </c>
+      <c r="E357">
+        <v>4</v>
+      </c>
+      <c r="F357">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="358" spans="2:6">
+      <c r="B358">
+        <v>357</v>
+      </c>
+      <c r="C358">
+        <v>15</v>
+      </c>
+      <c r="D358">
+        <v>13</v>
+      </c>
+      <c r="E358">
+        <v>4</v>
+      </c>
+      <c r="F358">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="359" spans="2:6">
+      <c r="B359">
+        <v>358</v>
+      </c>
+      <c r="C359">
+        <v>15</v>
+      </c>
+      <c r="D359">
+        <v>14</v>
+      </c>
+      <c r="E359">
+        <v>4</v>
+      </c>
+      <c r="F359">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="360" spans="2:6">
+      <c r="B360">
+        <v>359</v>
+      </c>
+      <c r="C360">
+        <v>15</v>
+      </c>
+      <c r="D360">
+        <v>15</v>
+      </c>
+      <c r="E360">
+        <v>4</v>
+      </c>
+      <c r="F360">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="361" spans="2:6">
+      <c r="B361">
+        <v>360</v>
+      </c>
+      <c r="C361">
+        <v>15</v>
+      </c>
+      <c r="D361">
+        <v>4</v>
+      </c>
+      <c r="E361">
+        <v>4</v>
+      </c>
+      <c r="F361">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="362" spans="2:6">
+      <c r="B362">
+        <v>361</v>
+      </c>
+      <c r="C362">
+        <v>15</v>
+      </c>
+      <c r="D362">
+        <v>5</v>
+      </c>
+      <c r="E362">
+        <v>4</v>
+      </c>
+      <c r="F362">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="363" spans="2:6">
+      <c r="B363">
+        <v>362</v>
+      </c>
+      <c r="C363">
+        <v>15</v>
+      </c>
+      <c r="D363">
+        <v>6</v>
+      </c>
+      <c r="E363">
+        <v>4</v>
+      </c>
+      <c r="F363">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="364" spans="2:6">
+      <c r="B364">
+        <v>363</v>
+      </c>
+      <c r="C364">
+        <v>15</v>
+      </c>
+      <c r="D364">
+        <v>7</v>
+      </c>
+      <c r="E364">
+        <v>4</v>
+      </c>
+      <c r="F364">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="365" spans="2:6">
+      <c r="B365">
+        <v>364</v>
+      </c>
+      <c r="C365">
+        <v>15</v>
+      </c>
+      <c r="D365">
+        <v>8</v>
+      </c>
+      <c r="E365">
+        <v>4</v>
+      </c>
+      <c r="F365">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="366" spans="2:6">
+      <c r="B366">
+        <v>365</v>
+      </c>
+      <c r="C366">
+        <v>15</v>
+      </c>
+      <c r="D366">
+        <v>9</v>
+      </c>
+      <c r="E366">
+        <v>4</v>
+      </c>
+      <c r="F366">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="367" spans="2:6">
+      <c r="B367">
+        <v>366</v>
+      </c>
+      <c r="C367">
+        <v>15</v>
+      </c>
+      <c r="D367">
+        <v>10</v>
+      </c>
+      <c r="E367">
+        <v>4</v>
+      </c>
+      <c r="F367">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="368" spans="2:6">
+      <c r="B368">
+        <v>367</v>
+      </c>
+      <c r="C368">
+        <v>15</v>
+      </c>
+      <c r="D368">
+        <v>11</v>
+      </c>
+      <c r="E368">
+        <v>4</v>
+      </c>
+      <c r="F368">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="369" spans="2:6">
+      <c r="B369">
+        <v>368</v>
+      </c>
+      <c r="C369">
+        <v>15</v>
+      </c>
+      <c r="D369">
+        <v>12</v>
+      </c>
+      <c r="E369">
+        <v>4</v>
+      </c>
+      <c r="F369">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="370" spans="2:6">
+      <c r="B370">
+        <v>369</v>
+      </c>
+      <c r="C370">
+        <v>15</v>
+      </c>
+      <c r="D370">
+        <v>13</v>
+      </c>
+      <c r="E370">
+        <v>4</v>
+      </c>
+      <c r="F370">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="371" spans="2:6">
+      <c r="B371">
+        <v>370</v>
+      </c>
+      <c r="C371">
+        <v>15</v>
+      </c>
+      <c r="D371">
+        <v>14</v>
+      </c>
+      <c r="E371">
+        <v>4</v>
+      </c>
+      <c r="F371">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="372" spans="2:6">
+      <c r="B372">
+        <v>371</v>
+      </c>
+      <c r="C372">
+        <v>15</v>
+      </c>
+      <c r="D372">
+        <v>15</v>
+      </c>
+      <c r="E372">
+        <v>4</v>
+      </c>
+      <c r="F372">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="373" spans="2:6">
+      <c r="B373">
+        <v>372</v>
+      </c>
+      <c r="C373">
+        <v>15</v>
+      </c>
+      <c r="D373">
+        <v>3</v>
+      </c>
+      <c r="E373">
+        <v>4</v>
+      </c>
+      <c r="F373">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="374" spans="2:6">
+      <c r="B374">
+        <v>373</v>
+      </c>
+      <c r="C374">
+        <v>15</v>
+      </c>
+      <c r="D374">
+        <v>4</v>
+      </c>
+      <c r="E374">
+        <v>4</v>
+      </c>
+      <c r="F374">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="375" spans="2:6">
+      <c r="B375">
+        <v>374</v>
+      </c>
+      <c r="C375">
+        <v>15</v>
+      </c>
+      <c r="D375">
+        <v>5</v>
+      </c>
+      <c r="E375">
+        <v>4</v>
+      </c>
+      <c r="F375">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="376" spans="2:6">
+      <c r="B376">
+        <v>375</v>
+      </c>
+      <c r="C376">
+        <v>15</v>
+      </c>
+      <c r="D376">
+        <v>6</v>
+      </c>
+      <c r="E376">
+        <v>4</v>
+      </c>
+      <c r="F376">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="377" spans="2:6">
+      <c r="B377">
+        <v>376</v>
+      </c>
+      <c r="C377">
+        <v>15</v>
+      </c>
+      <c r="D377">
+        <v>7</v>
+      </c>
+      <c r="E377">
+        <v>4</v>
+      </c>
+      <c r="F377">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="378" spans="2:6">
+      <c r="B378">
+        <v>377</v>
+      </c>
+      <c r="C378">
+        <v>15</v>
+      </c>
+      <c r="D378">
+        <v>8</v>
+      </c>
+      <c r="E378">
+        <v>4</v>
+      </c>
+      <c r="F378">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="379" spans="2:6">
+      <c r="B379">
+        <v>378</v>
+      </c>
+      <c r="C379">
+        <v>15</v>
+      </c>
+      <c r="D379">
+        <v>9</v>
+      </c>
+      <c r="E379">
+        <v>4</v>
+      </c>
+      <c r="F379">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="380" spans="2:6">
+      <c r="B380">
+        <v>379</v>
+      </c>
+      <c r="C380">
+        <v>15</v>
+      </c>
+      <c r="D380">
+        <v>10</v>
+      </c>
+      <c r="E380">
+        <v>4</v>
+      </c>
+      <c r="F380">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="381" spans="2:6">
+      <c r="B381">
+        <v>380</v>
+      </c>
+      <c r="C381">
+        <v>15</v>
+      </c>
+      <c r="D381">
+        <v>11</v>
+      </c>
+      <c r="E381">
+        <v>4</v>
+      </c>
+      <c r="F381">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="382" spans="2:6">
+      <c r="B382">
+        <v>381</v>
+      </c>
+      <c r="C382">
+        <v>15</v>
+      </c>
+      <c r="D382">
+        <v>12</v>
+      </c>
+      <c r="E382">
+        <v>4</v>
+      </c>
+      <c r="F382">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="383" spans="2:6">
+      <c r="B383">
+        <v>382</v>
+      </c>
+      <c r="C383">
+        <v>15</v>
+      </c>
+      <c r="D383">
+        <v>13</v>
+      </c>
+      <c r="E383">
+        <v>4</v>
+      </c>
+      <c r="F383">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="384" spans="2:6">
+      <c r="B384">
+        <v>383</v>
+      </c>
+      <c r="C384">
+        <v>15</v>
+      </c>
+      <c r="D384">
+        <v>14</v>
+      </c>
+      <c r="E384">
+        <v>4</v>
+      </c>
+      <c r="F384">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="385" spans="2:6">
+      <c r="B385">
+        <v>384</v>
+      </c>
+      <c r="C385">
+        <v>15</v>
+      </c>
+      <c r="D385">
+        <v>15</v>
+      </c>
+      <c r="E385">
+        <v>4</v>
+      </c>
+      <c r="F385">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="386" spans="2:6">
+      <c r="B386">
+        <v>385</v>
+      </c>
+      <c r="C386">
+        <v>20</v>
+      </c>
+      <c r="D386">
+        <v>1</v>
+      </c>
+      <c r="E386">
+        <v>4</v>
+      </c>
+      <c r="F386">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="387" spans="2:6">
+      <c r="B387">
+        <v>386</v>
+      </c>
+      <c r="C387">
+        <v>20</v>
+      </c>
+      <c r="D387">
+        <v>2</v>
+      </c>
+      <c r="E387">
+        <v>4</v>
+      </c>
+      <c r="F387">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="388" spans="2:6">
+      <c r="B388">
+        <v>387</v>
+      </c>
+      <c r="C388">
+        <v>20</v>
+      </c>
+      <c r="D388">
+        <v>4</v>
+      </c>
+      <c r="E388">
+        <v>4</v>
+      </c>
+      <c r="F388">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="389" spans="2:6">
+      <c r="B389">
+        <v>388</v>
+      </c>
+      <c r="C389">
+        <v>20</v>
+      </c>
+      <c r="D389">
+        <v>3</v>
+      </c>
+      <c r="E389">
+        <v>4</v>
+      </c>
+      <c r="F389">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="390" spans="2:6">
+      <c r="B390">
+        <v>389</v>
+      </c>
+      <c r="C390">
+        <v>20</v>
+      </c>
+      <c r="D390">
+        <v>5</v>
+      </c>
+      <c r="E390">
+        <v>4</v>
+      </c>
+      <c r="F390">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="391" spans="2:6">
+      <c r="B391">
+        <v>390</v>
+      </c>
+      <c r="C391">
+        <v>20</v>
+      </c>
+      <c r="D391">
+        <v>6</v>
+      </c>
+      <c r="E391">
+        <v>4</v>
+      </c>
+      <c r="F391">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="392" spans="2:6">
+      <c r="B392">
+        <v>391</v>
+      </c>
+      <c r="C392">
+        <v>20</v>
+      </c>
+      <c r="D392">
+        <v>7</v>
+      </c>
+      <c r="E392">
+        <v>4</v>
+      </c>
+      <c r="F392">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="393" spans="2:6">
+      <c r="B393">
+        <v>392</v>
+      </c>
+      <c r="C393">
+        <v>20</v>
+      </c>
+      <c r="D393">
+        <v>8</v>
+      </c>
+      <c r="E393">
+        <v>4</v>
+      </c>
+      <c r="F393">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="394" spans="2:6">
+      <c r="B394">
+        <v>393</v>
+      </c>
+      <c r="C394">
+        <v>20</v>
+      </c>
+      <c r="D394">
+        <v>9</v>
+      </c>
+      <c r="E394">
+        <v>4</v>
+      </c>
+      <c r="F394">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="395" spans="2:6">
+      <c r="B395">
+        <v>394</v>
+      </c>
+      <c r="C395">
+        <v>20</v>
+      </c>
+      <c r="D395">
+        <v>10</v>
+      </c>
+      <c r="E395">
+        <v>4</v>
+      </c>
+      <c r="F395">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="396" spans="2:6">
+      <c r="B396">
+        <v>395</v>
+      </c>
+      <c r="C396">
+        <v>20</v>
+      </c>
+      <c r="D396">
+        <v>11</v>
+      </c>
+      <c r="E396">
+        <v>4</v>
+      </c>
+      <c r="F396">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="397" spans="2:6">
+      <c r="B397">
+        <v>396</v>
+      </c>
+      <c r="C397">
+        <v>20</v>
+      </c>
+      <c r="D397">
+        <v>12</v>
+      </c>
+      <c r="E397">
+        <v>4</v>
+      </c>
+      <c r="F397">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="398" spans="2:6">
+      <c r="B398">
+        <v>397</v>
+      </c>
+      <c r="C398">
+        <v>20</v>
+      </c>
+      <c r="D398">
+        <v>13</v>
+      </c>
+      <c r="E398">
+        <v>4</v>
+      </c>
+      <c r="F398">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="399" spans="2:6">
+      <c r="B399">
+        <v>398</v>
+      </c>
+      <c r="C399">
+        <v>20</v>
+      </c>
+      <c r="D399">
+        <v>1</v>
+      </c>
+      <c r="E399">
+        <v>4</v>
+      </c>
+      <c r="F399">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="400" spans="2:6">
+      <c r="B400">
+        <v>399</v>
+      </c>
+      <c r="C400">
+        <v>20</v>
+      </c>
+      <c r="D400">
+        <v>2</v>
+      </c>
+      <c r="E400">
+        <v>4</v>
+      </c>
+      <c r="F400">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="401" spans="2:6">
+      <c r="B401">
+        <v>400</v>
+      </c>
+      <c r="C401">
+        <v>20</v>
+      </c>
+      <c r="D401">
+        <v>3</v>
+      </c>
+      <c r="E401">
+        <v>4</v>
+      </c>
+      <c r="F401">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="402" spans="2:6">
+      <c r="B402">
+        <v>401</v>
+      </c>
+      <c r="C402">
+        <v>20</v>
+      </c>
+      <c r="D402">
+        <v>4</v>
+      </c>
+      <c r="E402">
+        <v>4</v>
+      </c>
+      <c r="F402">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="403" spans="2:6">
+      <c r="B403">
+        <v>402</v>
+      </c>
+      <c r="C403">
+        <v>20</v>
+      </c>
+      <c r="D403">
+        <v>5</v>
+      </c>
+      <c r="E403">
+        <v>4</v>
+      </c>
+      <c r="F403">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="404" spans="2:6">
+      <c r="B404">
+        <v>403</v>
+      </c>
+      <c r="C404">
+        <v>20</v>
+      </c>
+      <c r="D404">
+        <v>6</v>
+      </c>
+      <c r="E404">
+        <v>4</v>
+      </c>
+      <c r="F404">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="405" spans="2:6">
+      <c r="B405">
+        <v>404</v>
+      </c>
+      <c r="C405">
+        <v>20</v>
+      </c>
+      <c r="D405">
+        <v>7</v>
+      </c>
+      <c r="E405">
+        <v>4</v>
+      </c>
+      <c r="F405">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="406" spans="2:6">
+      <c r="B406">
+        <v>405</v>
+      </c>
+      <c r="C406">
+        <v>20</v>
+      </c>
+      <c r="D406">
+        <v>8</v>
+      </c>
+      <c r="E406">
+        <v>4</v>
+      </c>
+      <c r="F406">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="407" spans="2:6">
+      <c r="B407">
+        <v>406</v>
+      </c>
+      <c r="C407">
+        <v>20</v>
+      </c>
+      <c r="D407">
+        <v>9</v>
+      </c>
+      <c r="E407">
+        <v>4</v>
+      </c>
+      <c r="F407">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="408" spans="2:6">
+      <c r="B408">
+        <v>407</v>
+      </c>
+      <c r="C408">
+        <v>20</v>
+      </c>
+      <c r="D408">
+        <v>10</v>
+      </c>
+      <c r="E408">
+        <v>4</v>
+      </c>
+      <c r="F408">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="409" spans="2:6">
+      <c r="B409">
+        <v>408</v>
+      </c>
+      <c r="C409">
+        <v>20</v>
+      </c>
+      <c r="D409">
+        <v>11</v>
+      </c>
+      <c r="E409">
+        <v>4</v>
+      </c>
+      <c r="F409">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="410" spans="2:6">
+      <c r="B410">
+        <v>409</v>
+      </c>
+      <c r="C410">
+        <v>20</v>
+      </c>
+      <c r="D410">
+        <v>12</v>
+      </c>
+      <c r="E410">
+        <v>4</v>
+      </c>
+      <c r="F410">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="411" spans="2:6">
+      <c r="B411">
+        <v>410</v>
+      </c>
+      <c r="C411">
+        <v>20</v>
+      </c>
+      <c r="D411">
+        <v>13</v>
+      </c>
+      <c r="E411">
+        <v>4</v>
+      </c>
+      <c r="F411">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="412" spans="2:6">
+      <c r="B412">
+        <v>411</v>
+      </c>
+      <c r="C412">
+        <v>20</v>
+      </c>
+      <c r="D412">
+        <v>14</v>
+      </c>
+      <c r="E412">
+        <v>4</v>
+      </c>
+      <c r="F412">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="413" spans="2:6">
+      <c r="B413">
+        <v>412</v>
+      </c>
+      <c r="C413">
+        <v>20</v>
+      </c>
+      <c r="D413">
+        <v>1</v>
+      </c>
+      <c r="E413">
+        <v>4</v>
+      </c>
+      <c r="F413">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="414" spans="2:6">
+      <c r="B414">
+        <v>413</v>
+      </c>
+      <c r="C414">
+        <v>20</v>
+      </c>
+      <c r="D414">
+        <v>2</v>
+      </c>
+      <c r="E414">
+        <v>4</v>
+      </c>
+      <c r="F414">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="415" spans="2:6">
+      <c r="B415">
+        <v>414</v>
+      </c>
+      <c r="C415">
+        <v>20</v>
+      </c>
+      <c r="D415">
+        <v>3</v>
+      </c>
+      <c r="E415">
+        <v>4</v>
+      </c>
+      <c r="F415">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="416" spans="2:6">
+      <c r="B416">
+        <v>415</v>
+      </c>
+      <c r="C416">
+        <v>20</v>
+      </c>
+      <c r="D416">
+        <v>4</v>
+      </c>
+      <c r="E416">
+        <v>4</v>
+      </c>
+      <c r="F416">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="417" spans="2:6">
+      <c r="B417">
+        <v>416</v>
+      </c>
+      <c r="C417">
+        <v>20</v>
+      </c>
+      <c r="D417">
+        <v>5</v>
+      </c>
+      <c r="E417">
+        <v>4</v>
+      </c>
+      <c r="F417">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="418" spans="2:6">
+      <c r="B418">
+        <v>417</v>
+      </c>
+      <c r="C418">
+        <v>20</v>
+      </c>
+      <c r="D418">
+        <v>6</v>
+      </c>
+      <c r="E418">
+        <v>4</v>
+      </c>
+      <c r="F418">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="419" spans="2:6">
+      <c r="B419">
+        <v>418</v>
+      </c>
+      <c r="C419">
+        <v>20</v>
+      </c>
+      <c r="D419">
+        <v>7</v>
+      </c>
+      <c r="E419">
+        <v>4</v>
+      </c>
+      <c r="F419">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="420" spans="2:6">
+      <c r="B420">
+        <v>419</v>
+      </c>
+      <c r="C420">
+        <v>20</v>
+      </c>
+      <c r="D420">
+        <v>8</v>
+      </c>
+      <c r="E420">
+        <v>4</v>
+      </c>
+      <c r="F420">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="421" spans="2:6">
+      <c r="B421">
+        <v>420</v>
+      </c>
+      <c r="C421">
+        <v>20</v>
+      </c>
+      <c r="D421">
+        <v>9</v>
+      </c>
+      <c r="E421">
+        <v>4</v>
+      </c>
+      <c r="F421">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="422" spans="2:6">
+      <c r="B422">
+        <v>421</v>
+      </c>
+      <c r="C422">
+        <v>20</v>
+      </c>
+      <c r="D422">
+        <v>10</v>
+      </c>
+      <c r="E422">
+        <v>4</v>
+      </c>
+      <c r="F422">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="423" spans="2:6">
+      <c r="B423">
+        <v>422</v>
+      </c>
+      <c r="C423">
+        <v>20</v>
+      </c>
+      <c r="D423">
+        <v>11</v>
+      </c>
+      <c r="E423">
+        <v>4</v>
+      </c>
+      <c r="F423">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="424" spans="2:6">
+      <c r="B424">
+        <v>423</v>
+      </c>
+      <c r="C424">
+        <v>20</v>
+      </c>
+      <c r="D424">
+        <v>12</v>
+      </c>
+      <c r="E424">
+        <v>4</v>
+      </c>
+      <c r="F424">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="425" spans="2:6">
+      <c r="B425">
+        <v>424</v>
+      </c>
+      <c r="C425">
+        <v>20</v>
+      </c>
+      <c r="D425">
+        <v>13</v>
+      </c>
+      <c r="E425">
+        <v>4</v>
+      </c>
+      <c r="F425">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="426" spans="2:6">
+      <c r="B426">
+        <v>425</v>
+      </c>
+      <c r="C426">
+        <v>20</v>
+      </c>
+      <c r="D426">
+        <v>14</v>
+      </c>
+      <c r="E426">
+        <v>4</v>
+      </c>
+      <c r="F426">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="427" spans="2:6">
+      <c r="B427">
+        <v>426</v>
+      </c>
+      <c r="C427">
+        <v>20</v>
+      </c>
+      <c r="D427">
+        <v>15</v>
+      </c>
+      <c r="E427">
+        <v>4</v>
+      </c>
+      <c r="F427">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="428" spans="2:6">
+      <c r="B428">
+        <v>427</v>
+      </c>
+      <c r="C428">
+        <v>20</v>
+      </c>
+      <c r="D428">
+        <v>1</v>
+      </c>
+      <c r="E428">
+        <v>4</v>
+      </c>
+      <c r="F428">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="429" spans="2:6">
+      <c r="B429">
+        <v>428</v>
+      </c>
+      <c r="C429">
+        <v>20</v>
+      </c>
+      <c r="D429">
+        <v>2</v>
+      </c>
+      <c r="E429">
+        <v>4</v>
+      </c>
+      <c r="F429">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="430" spans="2:6">
+      <c r="B430">
+        <v>429</v>
+      </c>
+      <c r="C430">
+        <v>20</v>
+      </c>
+      <c r="D430">
+        <v>3</v>
+      </c>
+      <c r="E430">
+        <v>4</v>
+      </c>
+      <c r="F430">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="431" spans="2:6">
+      <c r="B431">
+        <v>430</v>
+      </c>
+      <c r="C431">
+        <v>20</v>
+      </c>
+      <c r="D431">
+        <v>4</v>
+      </c>
+      <c r="E431">
+        <v>4</v>
+      </c>
+      <c r="F431">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="432" spans="2:6">
+      <c r="B432">
+        <v>431</v>
+      </c>
+      <c r="C432">
+        <v>20</v>
+      </c>
+      <c r="D432">
+        <v>5</v>
+      </c>
+      <c r="E432">
+        <v>4</v>
+      </c>
+      <c r="F432">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="433" spans="2:6">
+      <c r="B433">
+        <v>432</v>
+      </c>
+      <c r="C433">
+        <v>20</v>
+      </c>
+      <c r="D433">
+        <v>6</v>
+      </c>
+      <c r="E433">
+        <v>4</v>
+      </c>
+      <c r="F433">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="434" spans="2:6">
+      <c r="B434">
+        <v>433</v>
+      </c>
+      <c r="C434">
+        <v>20</v>
+      </c>
+      <c r="D434">
+        <v>7</v>
+      </c>
+      <c r="E434">
+        <v>4</v>
+      </c>
+      <c r="F434">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="435" spans="2:6">
+      <c r="B435">
+        <v>434</v>
+      </c>
+      <c r="C435">
+        <v>20</v>
+      </c>
+      <c r="D435">
+        <v>8</v>
+      </c>
+      <c r="E435">
+        <v>4</v>
+      </c>
+      <c r="F435">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="436" spans="2:6">
+      <c r="B436">
+        <v>435</v>
+      </c>
+      <c r="C436">
+        <v>20</v>
+      </c>
+      <c r="D436">
+        <v>9</v>
+      </c>
+      <c r="E436">
+        <v>4</v>
+      </c>
+      <c r="F436">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="437" spans="2:6">
+      <c r="B437">
+        <v>436</v>
+      </c>
+      <c r="C437">
+        <v>20</v>
+      </c>
+      <c r="D437">
+        <v>10</v>
+      </c>
+      <c r="E437">
+        <v>4</v>
+      </c>
+      <c r="F437">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="438" spans="2:6">
+      <c r="B438">
+        <v>437</v>
+      </c>
+      <c r="C438">
+        <v>20</v>
+      </c>
+      <c r="D438">
+        <v>11</v>
+      </c>
+      <c r="E438">
+        <v>4</v>
+      </c>
+      <c r="F438">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="439" spans="2:6">
+      <c r="B439">
+        <v>438</v>
+      </c>
+      <c r="C439">
+        <v>20</v>
+      </c>
+      <c r="D439">
+        <v>12</v>
+      </c>
+      <c r="E439">
+        <v>4</v>
+      </c>
+      <c r="F439">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="440" spans="2:6">
+      <c r="B440">
+        <v>439</v>
+      </c>
+      <c r="C440">
+        <v>20</v>
+      </c>
+      <c r="D440">
+        <v>13</v>
+      </c>
+      <c r="E440">
+        <v>4</v>
+      </c>
+      <c r="F440">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="441" spans="2:6">
+      <c r="B441">
+        <v>440</v>
+      </c>
+      <c r="C441">
+        <v>20</v>
+      </c>
+      <c r="D441">
+        <v>14</v>
+      </c>
+      <c r="E441">
+        <v>4</v>
+      </c>
+      <c r="F441">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="442" spans="2:6">
+      <c r="B442">
+        <v>441</v>
+      </c>
+      <c r="C442">
+        <v>20</v>
+      </c>
+      <c r="D442">
+        <v>15</v>
+      </c>
+      <c r="E442">
+        <v>4</v>
+      </c>
+      <c r="F442">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="443" spans="2:6">
+      <c r="B443">
+        <v>442</v>
+      </c>
+      <c r="C443">
+        <v>20</v>
+      </c>
+      <c r="D443">
+        <v>16</v>
+      </c>
+      <c r="E443">
+        <v>4</v>
+      </c>
+      <c r="F443">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="444" spans="2:6">
+      <c r="B444">
+        <v>443</v>
+      </c>
+      <c r="C444">
+        <v>20</v>
+      </c>
+      <c r="D444">
+        <v>8</v>
+      </c>
+      <c r="E444">
+        <v>4</v>
+      </c>
+      <c r="F444">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="445" spans="2:6">
+      <c r="B445">
+        <v>444</v>
+      </c>
+      <c r="C445">
+        <v>20</v>
+      </c>
+      <c r="D445">
+        <v>7</v>
+      </c>
+      <c r="E445">
+        <v>4</v>
+      </c>
+      <c r="F445">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="446" spans="2:6">
+      <c r="B446">
+        <v>445</v>
+      </c>
+      <c r="C446">
+        <v>20</v>
+      </c>
+      <c r="D446">
+        <v>6</v>
+      </c>
+      <c r="E446">
+        <v>4</v>
+      </c>
+      <c r="F446">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="447" spans="2:6">
+      <c r="B447">
+        <v>446</v>
+      </c>
+      <c r="C447">
+        <v>20</v>
+      </c>
+      <c r="D447">
+        <v>5</v>
+      </c>
+      <c r="E447">
+        <v>4</v>
+      </c>
+      <c r="F447">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="448" spans="2:6">
+      <c r="B448">
+        <v>447</v>
+      </c>
+      <c r="C448">
+        <v>20</v>
+      </c>
+      <c r="D448">
+        <v>4</v>
+      </c>
+      <c r="E448">
+        <v>4</v>
+      </c>
+      <c r="F448">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="449" spans="2:6">
+      <c r="B449">
+        <v>448</v>
+      </c>
+      <c r="C449">
+        <v>20</v>
+      </c>
+      <c r="D449">
+        <v>9</v>
+      </c>
+      <c r="E449">
+        <v>4</v>
+      </c>
+      <c r="F449">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="450" spans="2:6">
+      <c r="B450">
+        <v>449</v>
+      </c>
+      <c r="C450">
+        <v>20</v>
+      </c>
+      <c r="D450">
+        <v>10</v>
+      </c>
+      <c r="E450">
+        <v>4</v>
+      </c>
+      <c r="F450">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="451" spans="2:6">
+      <c r="B451">
+        <v>450</v>
+      </c>
+      <c r="C451">
+        <v>20</v>
+      </c>
+      <c r="D451">
+        <v>11</v>
+      </c>
+      <c r="E451">
+        <v>4</v>
+      </c>
+      <c r="F451">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="452" spans="2:6">
+      <c r="B452">
+        <v>451</v>
+      </c>
+      <c r="C452">
+        <v>20</v>
+      </c>
+      <c r="D452">
+        <v>8</v>
+      </c>
+      <c r="E452">
+        <v>4</v>
+      </c>
+      <c r="F452">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="453" spans="2:6">
+      <c r="B453">
+        <v>452</v>
+      </c>
+      <c r="C453">
+        <v>20</v>
+      </c>
+      <c r="D453">
+        <v>9</v>
+      </c>
+      <c r="E453">
+        <v>4</v>
+      </c>
+      <c r="F453">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="454" spans="2:6">
+      <c r="B454">
+        <v>453</v>
+      </c>
+      <c r="C454">
+        <v>20</v>
+      </c>
+      <c r="D454">
+        <v>10</v>
+      </c>
+      <c r="E454">
+        <v>4</v>
+      </c>
+      <c r="F454">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="455" spans="2:6">
+      <c r="B455">
+        <v>454</v>
+      </c>
+      <c r="C455">
+        <v>20</v>
+      </c>
+      <c r="D455">
+        <v>11</v>
+      </c>
+      <c r="E455">
+        <v>4</v>
+      </c>
+      <c r="F455">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="456" spans="2:6">
+      <c r="B456">
+        <v>455</v>
+      </c>
+      <c r="C456">
+        <v>20</v>
+      </c>
+      <c r="D456">
+        <v>12</v>
+      </c>
+      <c r="E456">
+        <v>4</v>
+      </c>
+      <c r="F456">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="457" spans="2:6">
+      <c r="B457">
+        <v>456</v>
+      </c>
+      <c r="C457">
+        <v>20</v>
+      </c>
+      <c r="D457">
+        <v>13</v>
+      </c>
+      <c r="E457">
+        <v>4</v>
+      </c>
+      <c r="F457">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="458" spans="2:6">
+      <c r="B458">
+        <v>457</v>
+      </c>
+      <c r="C458">
+        <v>20</v>
+      </c>
+      <c r="D458">
+        <v>14</v>
+      </c>
+      <c r="E458">
+        <v>4</v>
+      </c>
+      <c r="F458">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="459" spans="2:6">
+      <c r="B459">
+        <v>458</v>
+      </c>
+      <c r="C459">
+        <v>20</v>
+      </c>
+      <c r="D459">
+        <v>15</v>
+      </c>
+      <c r="E459">
+        <v>4</v>
+      </c>
+      <c r="F459">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="460" spans="2:6">
+      <c r="B460">
+        <v>459</v>
+      </c>
+      <c r="C460">
+        <v>20</v>
+      </c>
+      <c r="D460">
+        <v>16</v>
+      </c>
+      <c r="E460">
+        <v>4</v>
+      </c>
+      <c r="F460">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="461" spans="2:6">
+      <c r="B461">
+        <v>460</v>
+      </c>
+      <c r="C461">
+        <v>20</v>
+      </c>
+      <c r="D461">
+        <v>17</v>
+      </c>
+      <c r="E461">
+        <v>4</v>
+      </c>
+      <c r="F461">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="462" spans="2:6">
+      <c r="B462">
+        <v>461</v>
+      </c>
+      <c r="C462">
+        <v>20</v>
+      </c>
+      <c r="D462">
+        <v>18</v>
+      </c>
+      <c r="E462">
+        <v>4</v>
+      </c>
+      <c r="F462">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="463" spans="2:6">
+      <c r="B463">
+        <v>462</v>
+      </c>
+      <c r="C463">
+        <v>20</v>
+      </c>
+      <c r="D463">
+        <v>7</v>
+      </c>
+      <c r="E463">
+        <v>4</v>
+      </c>
+      <c r="F463">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="464" spans="2:6">
+      <c r="B464">
+        <v>463</v>
+      </c>
+      <c r="C464">
+        <v>20</v>
+      </c>
+      <c r="D464">
+        <v>6</v>
+      </c>
+      <c r="E464">
+        <v>4</v>
+      </c>
+      <c r="F464">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="465" spans="2:6">
+      <c r="B465">
+        <v>464</v>
+      </c>
+      <c r="C465">
+        <v>20</v>
+      </c>
+      <c r="D465">
+        <v>5</v>
+      </c>
+      <c r="E465">
+        <v>4</v>
+      </c>
+      <c r="F465">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="466" spans="2:6">
+      <c r="B466">
+        <v>465</v>
+      </c>
+      <c r="C466">
+        <v>20</v>
+      </c>
+      <c r="D466">
+        <v>4</v>
+      </c>
+      <c r="E466">
+        <v>4</v>
+      </c>
+      <c r="F466">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="467" spans="2:6">
+      <c r="B467">
+        <v>466</v>
+      </c>
+      <c r="C467">
+        <v>20</v>
+      </c>
+      <c r="D467">
+        <v>3</v>
+      </c>
+      <c r="E467">
+        <v>4</v>
+      </c>
+      <c r="F467">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="468" spans="2:6">
+      <c r="B468">
+        <v>467</v>
+      </c>
+      <c r="C468">
+        <v>20</v>
+      </c>
+      <c r="D468">
+        <v>2</v>
+      </c>
+      <c r="E468">
+        <v>4</v>
+      </c>
+      <c r="F468">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="469" spans="2:6">
+      <c r="B469">
+        <v>468</v>
+      </c>
+      <c r="C469">
+        <v>20</v>
+      </c>
+      <c r="D469">
+        <v>12</v>
+      </c>
+      <c r="E469">
+        <v>4</v>
+      </c>
+      <c r="F469">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="470" spans="2:6">
+      <c r="B470">
+        <v>469</v>
+      </c>
+      <c r="C470">
+        <v>20</v>
+      </c>
+      <c r="D470">
+        <v>13</v>
+      </c>
+      <c r="E470">
+        <v>4</v>
+      </c>
+      <c r="F470">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="471" spans="2:6">
+      <c r="B471">
+        <v>470</v>
+      </c>
+      <c r="C471">
+        <v>20</v>
+      </c>
+      <c r="D471">
+        <v>14</v>
+      </c>
+      <c r="E471">
+        <v>4</v>
+      </c>
+      <c r="F471">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="472" spans="2:6">
+      <c r="B472">
+        <v>471</v>
+      </c>
+      <c r="C472">
+        <v>20</v>
+      </c>
+      <c r="D472">
+        <v>15</v>
+      </c>
+      <c r="E472">
+        <v>4</v>
+      </c>
+      <c r="F472">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="473" spans="2:6">
+      <c r="B473">
+        <v>472</v>
+      </c>
+      <c r="C473">
+        <v>20</v>
+      </c>
+      <c r="D473">
+        <v>16</v>
+      </c>
+      <c r="E473">
+        <v>4</v>
+      </c>
+      <c r="F473">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="474" spans="2:6">
+      <c r="B474">
+        <v>473</v>
+      </c>
+      <c r="C474">
+        <v>20</v>
+      </c>
+      <c r="D474">
+        <v>3</v>
+      </c>
+      <c r="E474">
+        <v>4</v>
+      </c>
+      <c r="F474">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="475" spans="2:6">
+      <c r="B475">
+        <v>474</v>
+      </c>
+      <c r="C475">
+        <v>20</v>
+      </c>
+      <c r="D475">
+        <v>2</v>
+      </c>
+      <c r="E475">
+        <v>4</v>
+      </c>
+      <c r="F475">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="476" spans="2:6">
+      <c r="B476">
+        <v>475</v>
+      </c>
+      <c r="C476">
+        <v>20</v>
+      </c>
+      <c r="D476">
+        <v>2</v>
+      </c>
+      <c r="E476">
+        <v>5</v>
+      </c>
+      <c r="F476">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="477" spans="2:6">
+      <c r="B477">
+        <v>476</v>
+      </c>
+      <c r="C477">
+        <v>20</v>
+      </c>
+      <c r="D477">
+        <v>1</v>
+      </c>
+      <c r="E477">
+        <v>5</v>
+      </c>
+      <c r="F477">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="478" spans="2:6">
+      <c r="B478">
+        <v>477</v>
+      </c>
+      <c r="C478">
+        <v>20</v>
+      </c>
+      <c r="D478">
+        <v>3</v>
+      </c>
+      <c r="E478">
+        <v>5</v>
+      </c>
+      <c r="F478">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="479" spans="2:6">
+      <c r="B479">
+        <v>478</v>
+      </c>
+      <c r="C479">
+        <v>20</v>
+      </c>
+      <c r="D479">
+        <v>4</v>
+      </c>
+      <c r="E479">
+        <v>5</v>
+      </c>
+      <c r="F479">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="480" spans="2:6">
+      <c r="B480">
+        <v>479</v>
+      </c>
+      <c r="C480">
+        <v>20</v>
+      </c>
+      <c r="D480">
+        <v>5</v>
+      </c>
+      <c r="E480">
+        <v>5</v>
+      </c>
+      <c r="F480">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="481" spans="2:6">
+      <c r="B481">
+        <v>480</v>
+      </c>
+      <c r="C481">
+        <v>20</v>
+      </c>
+      <c r="D481">
+        <v>6</v>
+      </c>
+      <c r="E481">
+        <v>5</v>
+      </c>
+      <c r="F481">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="482" spans="2:6">
+      <c r="B482">
+        <v>481</v>
+      </c>
+      <c r="C482">
+        <v>20</v>
+      </c>
+      <c r="D482">
+        <v>7</v>
+      </c>
+      <c r="E482">
+        <v>5</v>
+      </c>
+      <c r="F482">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="483" spans="2:6">
+      <c r="B483">
+        <v>482</v>
+      </c>
+      <c r="C483">
+        <v>20</v>
+      </c>
+      <c r="D483">
+        <v>8</v>
+      </c>
+      <c r="E483">
+        <v>5</v>
+      </c>
+      <c r="F483">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="484" spans="2:6">
+      <c r="B484">
+        <v>483</v>
+      </c>
+      <c r="C484">
+        <v>20</v>
+      </c>
+      <c r="D484">
+        <v>9</v>
+      </c>
+      <c r="E484">
+        <v>5</v>
+      </c>
+      <c r="F484">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="485" spans="2:6">
+      <c r="B485">
+        <v>484</v>
+      </c>
+      <c r="C485">
+        <v>20</v>
+      </c>
+      <c r="D485">
+        <v>10</v>
+      </c>
+      <c r="E485">
+        <v>5</v>
+      </c>
+      <c r="F485">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="486" spans="2:6">
+      <c r="B486">
+        <v>485</v>
+      </c>
+      <c r="C486">
+        <v>20</v>
+      </c>
+      <c r="D486">
+        <v>11</v>
+      </c>
+      <c r="E486">
+        <v>5</v>
+      </c>
+      <c r="F486">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="487" spans="2:6">
+      <c r="B487">
+        <v>486</v>
+      </c>
+      <c r="C487">
+        <v>20</v>
+      </c>
+      <c r="D487">
+        <v>12</v>
+      </c>
+      <c r="E487">
+        <v>5</v>
+      </c>
+      <c r="F487">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="488" spans="2:6">
+      <c r="B488">
+        <v>487</v>
+      </c>
+      <c r="C488">
+        <v>20</v>
+      </c>
+      <c r="D488">
+        <v>13</v>
+      </c>
+      <c r="E488">
+        <v>5</v>
+      </c>
+      <c r="F488">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="489" spans="2:6">
+      <c r="B489">
+        <v>488</v>
+      </c>
+      <c r="C489">
+        <v>20</v>
+      </c>
+      <c r="D489">
+        <v>14</v>
+      </c>
+      <c r="E489">
+        <v>5</v>
+      </c>
+      <c r="F489">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="490" spans="2:6">
+      <c r="B490">
+        <v>489</v>
+      </c>
+      <c r="C490">
+        <v>20</v>
+      </c>
+      <c r="D490">
+        <v>15</v>
+      </c>
+      <c r="E490">
+        <v>5</v>
+      </c>
+      <c r="F490">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="491" spans="2:6">
+      <c r="B491">
+        <v>490</v>
+      </c>
+      <c r="C491">
+        <v>20</v>
+      </c>
+      <c r="D491">
+        <v>16</v>
+      </c>
+      <c r="E491">
+        <v>5</v>
+      </c>
+      <c r="F491">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="492" spans="2:6">
+      <c r="B492">
+        <v>491</v>
+      </c>
+      <c r="C492">
+        <v>20</v>
+      </c>
+      <c r="D492">
+        <v>16</v>
+      </c>
+      <c r="E492">
+        <v>5</v>
+      </c>
+      <c r="F492">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="493" spans="2:6">
+      <c r="B493">
+        <v>492</v>
+      </c>
+      <c r="C493">
+        <v>20</v>
+      </c>
+      <c r="D493">
+        <v>15</v>
+      </c>
+      <c r="E493">
+        <v>5</v>
+      </c>
+      <c r="F493">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="494" spans="2:6">
+      <c r="B494">
+        <v>493</v>
+      </c>
+      <c r="C494">
+        <v>20</v>
+      </c>
+      <c r="D494">
+        <v>14</v>
+      </c>
+      <c r="E494">
+        <v>5</v>
+      </c>
+      <c r="F494">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="495" spans="2:6">
+      <c r="B495">
+        <v>494</v>
+      </c>
+      <c r="C495">
+        <v>20</v>
+      </c>
+      <c r="D495">
+        <v>13</v>
+      </c>
+      <c r="E495">
+        <v>5</v>
+      </c>
+      <c r="F495">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="496" spans="2:6">
+      <c r="B496">
+        <v>495</v>
+      </c>
+      <c r="C496">
+        <v>20</v>
+      </c>
+      <c r="D496">
+        <v>12</v>
+      </c>
+      <c r="E496">
+        <v>5</v>
+      </c>
+      <c r="F496">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="497" spans="2:6">
+      <c r="B497">
+        <v>496</v>
+      </c>
+      <c r="C497">
+        <v>20</v>
+      </c>
+      <c r="D497">
+        <v>11</v>
+      </c>
+      <c r="E497">
+        <v>5</v>
+      </c>
+      <c r="F497">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="498" spans="2:6">
+      <c r="B498">
+        <v>497</v>
+      </c>
+      <c r="C498">
+        <v>20</v>
+      </c>
+      <c r="D498">
+        <v>10</v>
+      </c>
+      <c r="E498">
+        <v>5</v>
+      </c>
+      <c r="F498">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="499" spans="2:6">
+      <c r="B499">
+        <v>498</v>
+      </c>
+      <c r="C499">
+        <v>20</v>
+      </c>
+      <c r="D499">
+        <v>9</v>
+      </c>
+      <c r="E499">
+        <v>5</v>
+      </c>
+      <c r="F499">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="500" spans="2:6">
+      <c r="B500">
+        <v>499</v>
+      </c>
+      <c r="C500">
+        <v>20</v>
+      </c>
+      <c r="D500">
+        <v>8</v>
+      </c>
+      <c r="E500">
+        <v>5</v>
+      </c>
+      <c r="F500">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="501" spans="2:6">
+      <c r="B501">
+        <v>500</v>
+      </c>
+      <c r="C501">
+        <v>20</v>
+      </c>
+      <c r="D501">
+        <v>7</v>
+      </c>
+      <c r="E501">
+        <v>5</v>
+      </c>
+      <c r="F501">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="502" spans="2:6">
+      <c r="B502">
+        <v>501</v>
+      </c>
+      <c r="C502">
+        <v>20</v>
+      </c>
+      <c r="D502">
+        <v>6</v>
+      </c>
+      <c r="E502">
+        <v>5</v>
+      </c>
+      <c r="F502">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="503" spans="2:6">
+      <c r="B503">
+        <v>502</v>
+      </c>
+      <c r="C503">
+        <v>20</v>
+      </c>
+      <c r="D503">
+        <v>5</v>
+      </c>
+      <c r="E503">
+        <v>5</v>
+      </c>
+      <c r="F503">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="504" spans="2:6">
+      <c r="B504">
+        <v>503</v>
+      </c>
+      <c r="C504">
+        <v>20</v>
+      </c>
+      <c r="D504">
+        <v>4</v>
+      </c>
+      <c r="E504">
+        <v>5</v>
+      </c>
+      <c r="F504">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="505" spans="2:6">
+      <c r="B505">
+        <v>504</v>
+      </c>
+      <c r="C505">
+        <v>20</v>
+      </c>
+      <c r="D505">
+        <v>3</v>
+      </c>
+      <c r="E505">
+        <v>5</v>
+      </c>
+      <c r="F505">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="506" spans="2:6">
+      <c r="B506">
+        <v>505</v>
+      </c>
+      <c r="C506">
+        <v>20</v>
+      </c>
+      <c r="D506">
+        <v>2</v>
+      </c>
+      <c r="E506">
+        <v>5</v>
+      </c>
+      <c r="F506">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="507" spans="2:6">
+      <c r="B507">
+        <v>506</v>
+      </c>
+      <c r="C507">
+        <v>20</v>
+      </c>
+      <c r="D507">
+        <v>1</v>
+      </c>
+      <c r="E507">
+        <v>5</v>
+      </c>
+      <c r="F507">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="508" spans="2:6">
+      <c r="B508">
+        <v>507</v>
+      </c>
+      <c r="C508">
+        <v>20</v>
+      </c>
+      <c r="D508">
+        <v>1</v>
+      </c>
+      <c r="E508">
+        <v>5</v>
+      </c>
+      <c r="F508">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="509" spans="2:6">
+      <c r="B509">
+        <v>508</v>
+      </c>
+      <c r="C509">
+        <v>20</v>
+      </c>
+      <c r="D509">
+        <v>2</v>
+      </c>
+      <c r="E509">
+        <v>5</v>
+      </c>
+      <c r="F509">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="510" spans="2:6">
+      <c r="B510">
+        <v>509</v>
+      </c>
+      <c r="C510">
+        <v>20</v>
+      </c>
+      <c r="D510">
+        <v>3</v>
+      </c>
+      <c r="E510">
+        <v>5</v>
+      </c>
+      <c r="F510">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="511" spans="2:6">
+      <c r="B511">
+        <v>510</v>
+      </c>
+      <c r="C511">
+        <v>20</v>
+      </c>
+      <c r="D511">
+        <v>4</v>
+      </c>
+      <c r="E511">
+        <v>5</v>
+      </c>
+      <c r="F511">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="512" spans="2:6">
+      <c r="B512">
+        <v>511</v>
+      </c>
+      <c r="C512">
+        <v>20</v>
+      </c>
+      <c r="D512">
+        <v>5</v>
+      </c>
+      <c r="E512">
+        <v>5</v>
+      </c>
+      <c r="F512">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="513" spans="2:6">
+      <c r="B513">
+        <v>513</v>
+      </c>
+      <c r="C513">
+        <v>20</v>
+      </c>
+      <c r="D513">
+        <v>6</v>
+      </c>
+      <c r="E513">
+        <v>5</v>
+      </c>
+      <c r="F513">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="514" spans="2:6">
+      <c r="B514">
+        <v>512</v>
+      </c>
+      <c r="C514">
+        <v>20</v>
+      </c>
+      <c r="D514">
+        <v>7</v>
+      </c>
+      <c r="E514">
+        <v>5</v>
+      </c>
+      <c r="F514">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="515" spans="2:6">
+      <c r="B515">
+        <v>513</v>
+      </c>
+      <c r="C515">
+        <v>20</v>
+      </c>
+      <c r="D515">
+        <v>8</v>
+      </c>
+      <c r="E515">
+        <v>5</v>
+      </c>
+      <c r="F515">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="516" spans="2:6">
+      <c r="B516">
+        <v>514</v>
+      </c>
+      <c r="C516">
+        <v>20</v>
+      </c>
+      <c r="D516">
+        <v>9</v>
+      </c>
+      <c r="E516">
+        <v>5</v>
+      </c>
+      <c r="F516">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="517" spans="2:6">
+      <c r="B517">
+        <v>515</v>
+      </c>
+      <c r="C517">
+        <v>20</v>
+      </c>
+      <c r="D517">
+        <v>10</v>
+      </c>
+      <c r="E517">
+        <v>5</v>
+      </c>
+      <c r="F517">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="518" spans="2:6">
+      <c r="B518">
+        <v>516</v>
+      </c>
+      <c r="C518">
+        <v>20</v>
+      </c>
+      <c r="D518">
+        <v>11</v>
+      </c>
+      <c r="E518">
+        <v>5</v>
+      </c>
+      <c r="F518">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="519" spans="2:6">
+      <c r="B519">
+        <v>517</v>
+      </c>
+      <c r="C519">
+        <v>20</v>
+      </c>
+      <c r="D519">
+        <v>12</v>
+      </c>
+      <c r="E519">
+        <v>5</v>
+      </c>
+      <c r="F519">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="520" spans="2:6">
+      <c r="B520">
+        <v>518</v>
+      </c>
+      <c r="C520">
+        <v>20</v>
+      </c>
+      <c r="D520">
+        <v>13</v>
+      </c>
+      <c r="E520">
+        <v>5</v>
+      </c>
+      <c r="F520">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="521" spans="2:6">
+      <c r="B521">
+        <v>519</v>
+      </c>
+      <c r="C521">
+        <v>20</v>
+      </c>
+      <c r="D521">
+        <v>14</v>
+      </c>
+      <c r="E521">
+        <v>5</v>
+      </c>
+      <c r="F521">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="522" spans="2:6">
+      <c r="B522">
+        <v>520</v>
+      </c>
+      <c r="C522">
+        <v>20</v>
+      </c>
+      <c r="D522">
+        <v>15</v>
+      </c>
+      <c r="E522">
+        <v>5</v>
+      </c>
+      <c r="F522">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="523" spans="2:6">
+      <c r="B523">
+        <v>521</v>
+      </c>
+      <c r="C523">
+        <v>20</v>
+      </c>
+      <c r="D523">
+        <v>15</v>
+      </c>
+      <c r="E523">
+        <v>5</v>
+      </c>
+      <c r="F523">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="524" spans="2:6">
+      <c r="B524">
+        <v>522</v>
+      </c>
+      <c r="C524">
+        <v>20</v>
+      </c>
+      <c r="D524">
+        <v>14</v>
+      </c>
+      <c r="E524">
+        <v>5</v>
+      </c>
+      <c r="F524">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="525" spans="2:6">
+      <c r="B525">
+        <v>523</v>
+      </c>
+      <c r="C525">
+        <v>20</v>
+      </c>
+      <c r="D525">
+        <v>13</v>
+      </c>
+      <c r="E525">
+        <v>5</v>
+      </c>
+      <c r="F525">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="526" spans="2:6">
+      <c r="B526">
+        <v>524</v>
+      </c>
+      <c r="C526">
+        <v>20</v>
+      </c>
+      <c r="D526">
+        <v>12</v>
+      </c>
+      <c r="E526">
+        <v>5</v>
+      </c>
+      <c r="F526">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="527" spans="2:6">
+      <c r="B527">
+        <v>525</v>
+      </c>
+      <c r="C527">
+        <v>20</v>
+      </c>
+      <c r="D527">
+        <v>11</v>
+      </c>
+      <c r="E527">
+        <v>5</v>
+      </c>
+      <c r="F527">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="528" spans="2:6">
+      <c r="B528">
+        <v>526</v>
+      </c>
+      <c r="C528">
+        <v>20</v>
+      </c>
+      <c r="D528">
+        <v>11</v>
+      </c>
+      <c r="E528">
+        <v>5</v>
+      </c>
+      <c r="F528">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="529" spans="2:6">
+      <c r="B529">
+        <v>527</v>
+      </c>
+      <c r="C529">
+        <v>20</v>
+      </c>
+      <c r="D529">
+        <v>10</v>
+      </c>
+      <c r="E529">
+        <v>5</v>
+      </c>
+      <c r="F529">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="530" spans="2:6">
+      <c r="B530">
+        <v>528</v>
+      </c>
+      <c r="C530">
+        <v>20</v>
+      </c>
+      <c r="D530">
+        <v>9</v>
+      </c>
+      <c r="E530">
+        <v>5</v>
+      </c>
+      <c r="F530">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="531" spans="2:6">
+      <c r="B531">
+        <v>529</v>
+      </c>
+      <c r="C531">
+        <v>20</v>
+      </c>
+      <c r="D531">
+        <v>8</v>
+      </c>
+      <c r="E531">
+        <v>5</v>
+      </c>
+      <c r="F531">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="532" spans="2:6">
+      <c r="B532">
+        <v>530</v>
+      </c>
+      <c r="C532">
+        <v>20</v>
+      </c>
+      <c r="D532">
+        <v>7</v>
+      </c>
+      <c r="E532">
+        <v>5</v>
+      </c>
+      <c r="F532">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="533" spans="2:6">
+      <c r="B533">
+        <v>531</v>
+      </c>
+      <c r="C533">
+        <v>20</v>
+      </c>
+      <c r="D533">
+        <v>6</v>
+      </c>
+      <c r="E533">
+        <v>5</v>
+      </c>
+      <c r="F533">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="534" spans="2:6">
+      <c r="B534">
+        <v>532</v>
+      </c>
+      <c r="C534">
+        <v>20</v>
+      </c>
+      <c r="D534">
+        <v>5</v>
+      </c>
+      <c r="E534">
+        <v>5</v>
+      </c>
+      <c r="F534">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="535" spans="2:6">
+      <c r="B535">
+        <v>533</v>
+      </c>
+      <c r="C535">
+        <v>20</v>
+      </c>
+      <c r="D535">
+        <v>4</v>
+      </c>
+      <c r="E535">
+        <v>5</v>
+      </c>
+      <c r="F535">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="536" spans="2:6">
+      <c r="B536">
+        <v>534</v>
+      </c>
+      <c r="C536">
+        <v>20</v>
+      </c>
+      <c r="D536">
+        <v>3</v>
+      </c>
+      <c r="E536">
+        <v>5</v>
+      </c>
+      <c r="F536">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="537" spans="2:6">
+      <c r="B537">
+        <v>535</v>
+      </c>
+      <c r="C537">
+        <v>20</v>
+      </c>
+      <c r="D537">
+        <v>2</v>
+      </c>
+      <c r="E537">
+        <v>5</v>
+      </c>
+      <c r="F537">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="538" spans="2:6">
+      <c r="B538">
+        <v>536</v>
+      </c>
+      <c r="C538">
+        <v>20</v>
+      </c>
+      <c r="D538">
+        <v>1</v>
+      </c>
+      <c r="E538">
+        <v>5</v>
+      </c>
+      <c r="F538">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="539" spans="2:6">
+      <c r="B539">
+        <v>537</v>
+      </c>
+      <c r="C539">
+        <v>20</v>
+      </c>
+      <c r="D539">
+        <v>1</v>
+      </c>
+      <c r="E539">
+        <v>5</v>
+      </c>
+      <c r="F539">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="540" spans="2:6">
+      <c r="B540">
+        <v>538</v>
+      </c>
+      <c r="C540">
+        <v>20</v>
+      </c>
+      <c r="D540">
+        <v>2</v>
+      </c>
+      <c r="E540">
+        <v>5</v>
+      </c>
+      <c r="F540">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="541" spans="2:6">
+      <c r="B541">
+        <v>539</v>
+      </c>
+      <c r="C541">
+        <v>20</v>
+      </c>
+      <c r="D541">
+        <v>3</v>
+      </c>
+      <c r="E541">
+        <v>5</v>
+      </c>
+      <c r="F541">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="542" spans="2:6">
+      <c r="B542">
+        <v>540</v>
+      </c>
+      <c r="C542">
+        <v>20</v>
+      </c>
+      <c r="D542">
+        <v>4</v>
+      </c>
+      <c r="E542">
+        <v>5</v>
+      </c>
+      <c r="F542">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="543" spans="2:6">
+      <c r="B543">
+        <v>541</v>
+      </c>
+      <c r="C543">
+        <v>20</v>
+      </c>
+      <c r="D543">
+        <v>5</v>
+      </c>
+      <c r="E543">
+        <v>5</v>
+      </c>
+      <c r="F543">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="544" spans="2:6">
+      <c r="B544">
+        <v>542</v>
+      </c>
+      <c r="C544">
+        <v>20</v>
+      </c>
+      <c r="D544">
+        <v>6</v>
+      </c>
+      <c r="E544">
+        <v>5</v>
+      </c>
+      <c r="F544">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="545" spans="2:9">
+      <c r="B545">
+        <v>543</v>
+      </c>
+      <c r="C545">
+        <v>20</v>
+      </c>
+      <c r="D545">
+        <v>7</v>
+      </c>
+      <c r="E545">
+        <v>5</v>
+      </c>
+      <c r="F545">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="546" spans="2:9">
+      <c r="B546">
+        <v>544</v>
+      </c>
+      <c r="C546">
+        <v>20</v>
+      </c>
+      <c r="D546">
+        <v>8</v>
+      </c>
+      <c r="E546">
+        <v>5</v>
+      </c>
+      <c r="F546">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="547" spans="2:9">
+      <c r="B547">
+        <v>545</v>
+      </c>
+      <c r="C547">
+        <v>20</v>
+      </c>
+      <c r="D547">
+        <v>9</v>
+      </c>
+      <c r="E547">
+        <v>5</v>
+      </c>
+      <c r="F547">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="548" spans="2:9">
+      <c r="B548">
+        <v>546</v>
+      </c>
+      <c r="C548">
+        <v>20</v>
+      </c>
+      <c r="D548">
+        <v>10</v>
+      </c>
+      <c r="E548">
+        <v>5</v>
+      </c>
+      <c r="F548">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="549" spans="2:9">
+      <c r="B549">
+        <v>547</v>
+      </c>
+      <c r="C549">
+        <v>20</v>
+      </c>
+      <c r="D549">
+        <v>12</v>
+      </c>
+      <c r="E549">
+        <v>5</v>
+      </c>
+      <c r="F549">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="550" spans="2:9">
+      <c r="B550">
+        <v>548</v>
+      </c>
+      <c r="C550">
+        <v>20</v>
+      </c>
+      <c r="D550">
+        <v>13</v>
+      </c>
+      <c r="E550">
+        <v>5</v>
+      </c>
+      <c r="F550">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="551" spans="2:9">
+      <c r="B551">
+        <v>549</v>
+      </c>
+      <c r="C551">
+        <v>20</v>
+      </c>
+      <c r="D551">
+        <v>14</v>
+      </c>
+      <c r="E551">
+        <v>5</v>
+      </c>
+      <c r="F551">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="552" spans="2:9">
+      <c r="B552">
+        <v>550</v>
+      </c>
+      <c r="C552">
+        <v>20</v>
+      </c>
+      <c r="D552">
+        <v>15</v>
+      </c>
+      <c r="E552">
+        <v>5</v>
+      </c>
+      <c r="F552">
+        <v>4.5</v>
+      </c>
+      <c r="I552" s="10" t="s">
+        <v>25</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/database/data/raw/metadata/bioprint_metadata_template_v2.xlsx
+++ b/database/data/raw/metadata/bioprint_metadata_template_v2.xlsx
@@ -1259,7 +1259,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S552"/>
+  <dimension ref="A1:V552"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="0"/>
   <cols>
     <col width="34" customWidth="1" style="12" min="1" max="1"/>
@@ -1364,6 +1364,21 @@
           <t>线宽结果CSV路径</t>
         </is>
       </c>
+      <c r="T1" s="0" t="inlineStr">
+        <is>
+          <t>线宽最大值(mm)</t>
+        </is>
+      </c>
+      <c r="U1" s="0" t="inlineStr">
+        <is>
+          <t>线宽最小值(mm)</t>
+        </is>
+      </c>
+      <c r="V1" s="0" t="inlineStr">
+        <is>
+          <t>线宽随机测点值(mm)</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="14.4" customHeight="1" s="12">
       <c r="A2" s="3" t="n"/>
@@ -1883,6 +1898,55 @@
           <t>从此开始拍照</t>
         </is>
       </c>
+      <c r="J24" s="0" t="n">
+        <v>1.855460306421182</v>
+      </c>
+      <c r="K24" s="0" t="n">
+        <v>1.819078731785473</v>
+      </c>
+      <c r="L24" s="0" t="n">
+        <v>0.8016288673015978</v>
+      </c>
+      <c r="M24" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="N24" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="O24" s="0" t="inlineStr">
+        <is>
+          <t>2,3,4,5,6,7</t>
+        </is>
+      </c>
+      <c r="P24" s="0" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="Q24" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-09 14:27:40</t>
+        </is>
+      </c>
+      <c r="R24" s="0" t="inlineStr">
+        <is>
+          <t>D:\bio-print\database\data\raw\images\annotated_pictures\annotated_23.png</t>
+        </is>
+      </c>
+      <c r="S24" s="0" t="inlineStr">
+        <is>
+          <t>D:\bio-print\database\data\raw\images\annotated_pictures\result_23.csv</t>
+        </is>
+      </c>
+      <c r="T24" t="n">
+        <v>2.182894478142567</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.697806816333108</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.697806816333108</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n"/>
@@ -1904,6 +1968,21 @@
       <c r="G25" s="8" t="n"/>
       <c r="H25" s="3" t="n"/>
       <c r="I25" s="3" t="n"/>
+      <c r="J25" s="0" t="n">
+        <v>2.345620325770487</v>
+      </c>
+      <c r="K25" s="0" t="n">
+        <v>2.426503785279814</v>
+      </c>
+      <c r="T25" s="0" t="n">
+        <v>3.518430488655731</v>
+      </c>
+      <c r="U25" s="0" t="n">
+        <v>0.7279511355839443</v>
+      </c>
+      <c r="V25" s="0" t="n">
+        <v>1.69855264969587</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="n"/>
